--- a/app_notas.xlsx
+++ b/app_notas.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="233">
   <si>
     <t>No</t>
   </si>
@@ -29,7 +29,7 @@
     <t>P2</t>
   </si>
   <si>
-    <t>PQT</t>
+    <t>PQT1</t>
   </si>
   <si>
     <t>1CTE</t>
@@ -59,6 +59,9 @@
     <t>P4</t>
   </si>
   <si>
+    <t>PQT2</t>
+  </si>
+  <si>
     <t>PA</t>
   </si>
   <si>
@@ -110,9 +113,6 @@
     <t>ALVAREZ FLOREZ, YAJART D.</t>
   </si>
   <si>
-    <t>5.0</t>
-  </si>
-  <si>
     <t>U00190869</t>
   </si>
   <si>
@@ -131,12 +131,6 @@
     <t>CARVAJAL FONTALVO, JUAN S.</t>
   </si>
   <si>
-    <t>0.6</t>
-  </si>
-  <si>
-    <t>3.0</t>
-  </si>
-  <si>
     <t>U00188544</t>
   </si>
   <si>
@@ -242,15 +236,9 @@
     <t>U00165906</t>
   </si>
   <si>
-    <t>PQT1</t>
-  </si>
-  <si>
     <t>CN</t>
   </si>
   <si>
-    <t>PQT2</t>
-  </si>
-  <si>
     <t>BOADA MANZANO, ANGELO</t>
   </si>
   <si>
@@ -260,9 +248,6 @@
     <t>CACERES DAZA, NICOLAS</t>
   </si>
   <si>
-    <t>0.0</t>
-  </si>
-  <si>
     <t>U00193956</t>
   </si>
   <si>
@@ -347,21 +332,12 @@
     <t>RUSSI PICO, LUIGI D.</t>
   </si>
   <si>
-    <t>2.0</t>
-  </si>
-  <si>
     <t>U00193142</t>
   </si>
   <si>
     <t>SANTOYO JAIMES, JUAN D.</t>
   </si>
   <si>
-    <t>0.1</t>
-  </si>
-  <si>
-    <t>0.2</t>
-  </si>
-  <si>
     <t>U00186645</t>
   </si>
   <si>
@@ -437,9 +413,6 @@
     <t>HERNANDEZ YEPEZ, LUIS F.</t>
   </si>
   <si>
-    <t>4.0</t>
-  </si>
-  <si>
     <t>U00190971</t>
   </si>
   <si>
@@ -720,9 +693,6 @@
   </si>
   <si>
     <t>ORDUZ FERNANDEZ, KALETH Z.</t>
-  </si>
-  <si>
-    <t>0.3</t>
   </si>
   <si>
     <t>U00190611</t>
@@ -751,7 +721,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="d.m"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -780,7 +750,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -797,8 +767,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1087,43 +1061,43 @@
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
@@ -1131,26 +1105,40 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" s="3">
-        <v>46144.0</v>
-      </c>
-      <c r="D2" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1vS2gE-mc1A6CX14zq-8uhU927dLafFRogBm_03E8occ"",""MAT2_A!C2:L24"")"),2.46)</f>
+        <v>2.46</v>
+      </c>
+      <c r="D2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E2" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="3">
-        <v>46269.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="F2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
+      <c r="G2" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="H2" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="I2" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="J2" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="I2" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="J2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
@@ -1167,7 +1155,7 @@
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
       <c r="Z2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA2" s="1">
         <v>60299.0</v>
@@ -1178,26 +1166,40 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" s="3">
-        <v>46084.0</v>
-      </c>
-      <c r="D3" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.34)</f>
+        <v>3.34</v>
+      </c>
+      <c r="D3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E3" s="3">
-        <v>46205.0</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="3">
-        <v>46085.0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>46237.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
+      <c r="F3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
+        <v>1.8</v>
+      </c>
+      <c r="G3" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="H3" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="I3" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J3" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
@@ -1214,7 +1216,7 @@
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
       <c r="Z3" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA3" s="1">
         <v>60299.0</v>
@@ -1225,26 +1227,40 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="C4" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="D4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E4" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="F4" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="F4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
+      </c>
       <c r="G4" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="H4" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="I4" s="3">
-        <v>46085.0</v>
-      </c>
-      <c r="J4" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="H4" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="I4" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="J4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
@@ -1274,24 +1290,38 @@
       <c r="B5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="4"/>
+      <c r="C5" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.966666666666667)</f>
+        <v>4.966666667</v>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E5" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>46269.0</v>
-      </c>
-      <c r="I5" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="J5" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
+      </c>
+      <c r="F5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
+      </c>
+      <c r="G5" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H5" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="I5" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="J5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -1321,24 +1351,38 @@
       <c r="B6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="4"/>
+      <c r="C6" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="D6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E6" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="H6" s="3">
-        <v>46177.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="F6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
+      </c>
+      <c r="G6" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H6" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="I6" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J6" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="J6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -1368,24 +1412,38 @@
       <c r="B7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="3">
-        <v>46207.0</v>
+      <c r="C7" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6000000000000001)</f>
+        <v>0.6</v>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E7" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
+      <c r="F7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9)</f>
+        <v>0.9</v>
+      </c>
+      <c r="G7" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="H7" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>46085.0</v>
-      </c>
-      <c r="J7" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="J7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
@@ -1402,7 +1460,7 @@
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
       <c r="Z7" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA7" s="1">
         <v>60299.0</v>
@@ -1413,26 +1471,40 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" s="3">
-        <v>46115.0</v>
-      </c>
-      <c r="D8" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4466666666666663)</f>
+        <v>3.446666667</v>
+      </c>
+      <c r="D8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E8" s="3">
-        <v>46056.0</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="3">
-        <v>46269.0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>46238.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="F8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="H8" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="I8" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J8" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
@@ -1449,7 +1521,7 @@
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
       <c r="Z8" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA8" s="1">
         <v>60299.0</v>
@@ -1460,26 +1532,40 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C9" s="3">
-        <v>46269.0</v>
-      </c>
-      <c r="D9" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.86)</f>
+        <v>4.86</v>
+      </c>
+      <c r="D9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E9" s="3">
-        <v>46084.0</v>
-      </c>
-      <c r="F9" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="F9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="G9" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>46269.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="H9" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="I9" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J9" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
@@ -1496,7 +1582,7 @@
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
       <c r="Z9" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA9" s="1">
         <v>60299.0</v>
@@ -1507,26 +1593,40 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C10" s="3">
-        <v>46025.0</v>
-      </c>
-      <c r="D10" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.066666666666667)</f>
+        <v>3.066666667</v>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E10" s="3">
-        <v>46236.0</v>
-      </c>
-      <c r="F10" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
+      <c r="F10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
+      </c>
       <c r="G10" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="H10" s="3">
-        <v>46146.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
+      <c r="H10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="I10" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J10" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
@@ -1543,7 +1643,7 @@
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
       <c r="Z10" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AA10" s="1">
         <v>60299.0</v>
@@ -1554,26 +1654,40 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C11" s="3">
-        <v>46114.0</v>
-      </c>
-      <c r="D11" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4066666666666667)</f>
+        <v>2.406666667</v>
+      </c>
+      <c r="D11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E11" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="H11" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="I11" s="3">
-        <v>46177.0</v>
-      </c>
-      <c r="J11" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
+      </c>
+      <c r="F11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
+      <c r="G11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="H11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="I11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
+      <c r="J11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -1590,7 +1704,7 @@
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
       <c r="Z11" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA11" s="1">
         <v>60299.0</v>
@@ -1601,26 +1715,40 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C12" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="D12" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.486666666666666)</f>
+        <v>4.486666667</v>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E12" s="3">
-        <v>46269.0</v>
-      </c>
-      <c r="F12" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
+      </c>
+      <c r="F12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
+      </c>
       <c r="G12" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="H12" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="I12" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="J12" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="I12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="J12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -1637,7 +1765,7 @@
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
       <c r="Z12" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA12" s="1">
         <v>60299.0</v>
@@ -1648,26 +1776,40 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="4"/>
+        <v>49</v>
+      </c>
+      <c r="C13" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0033333333333334)</f>
+        <v>3.003333333</v>
+      </c>
+      <c r="D13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E13" s="3">
-        <v>46085.0</v>
-      </c>
-      <c r="F13" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
+      </c>
+      <c r="F13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G13" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="H13" s="3">
-        <v>46085.0</v>
-      </c>
-      <c r="I13" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="J13" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
+      <c r="H13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="I13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="J13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
@@ -1684,7 +1826,7 @@
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
       <c r="Z13" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AA13" s="1">
         <v>60299.0</v>
@@ -1695,26 +1837,40 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C14" s="3">
-        <v>46026.0</v>
-      </c>
-      <c r="D14" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.073333333333333)</f>
+        <v>4.073333333</v>
+      </c>
+      <c r="D14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E14" s="3">
-        <v>46267.0</v>
-      </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>46026.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
+      <c r="F14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
+      <c r="G14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="H14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="I14" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J14" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -1731,7 +1887,7 @@
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
       <c r="Z14" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AA14" s="1">
         <v>60299.0</v>
@@ -1742,26 +1898,40 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C15" s="3">
-        <v>46084.0</v>
-      </c>
-      <c r="D15" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3133333333333335)</f>
+        <v>3.313333333</v>
+      </c>
+      <c r="D15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E15" s="3">
-        <v>46177.0</v>
-      </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>46269.0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>46085.0</v>
-      </c>
-      <c r="J15" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
+      <c r="F15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
+      <c r="G15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="H15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="I15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="J15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -1778,7 +1948,7 @@
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
       <c r="Z15" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AA15" s="1">
         <v>60299.0</v>
@@ -1789,26 +1959,40 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C16" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="D16" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.486666666666666)</f>
+        <v>4.486666667</v>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E16" s="3">
-        <v>46269.0</v>
-      </c>
-      <c r="F16" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
+      </c>
+      <c r="F16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
+      </c>
       <c r="G16" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="H16" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="I16" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="J16" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="I16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="J16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -1825,7 +2009,7 @@
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
       <c r="Z16" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AA16" s="1">
         <v>60299.0</v>
@@ -1836,26 +2020,40 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C17" s="3">
-        <v>46085.0</v>
-      </c>
-      <c r="D17" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.306666666666667)</f>
+        <v>4.306666667</v>
+      </c>
+      <c r="D17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E17" s="3">
-        <v>46144.0</v>
-      </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="3">
-        <v>46236.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
+      <c r="F17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
+      <c r="G17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
       </c>
       <c r="H17" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I17" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="J17" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="J17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -1872,7 +2070,7 @@
       <c r="X17" s="4"/>
       <c r="Y17" s="4"/>
       <c r="Z17" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="AA17" s="1">
         <v>60299.0</v>
@@ -1883,26 +2081,40 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="H18" s="3">
-        <v>46085.0</v>
+        <v>59</v>
+      </c>
+      <c r="C18" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="D18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E18" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
+      <c r="F18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
+      <c r="G18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
+      <c r="H18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="I18" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J18" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -1919,7 +2131,7 @@
       <c r="X18" s="4"/>
       <c r="Y18" s="4"/>
       <c r="Z18" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AA18" s="1">
         <v>60299.0</v>
@@ -1930,26 +2142,40 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C19" s="3">
-        <v>46175.0</v>
-      </c>
-      <c r="D19" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.64)</f>
+        <v>2.64</v>
+      </c>
+      <c r="D19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E19" s="3">
-        <v>46057.0</v>
-      </c>
-      <c r="F19" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
+      </c>
+      <c r="F19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
       <c r="G19" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="H19" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="I19" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="J19" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="H19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="I19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="J19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -1966,7 +2192,7 @@
       <c r="X19" s="4"/>
       <c r="Y19" s="4"/>
       <c r="Z19" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="AA19" s="1">
         <v>60299.0</v>
@@ -1977,26 +2203,40 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C20" s="3">
-        <v>46085.0</v>
-      </c>
-      <c r="D20" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="D20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E20" s="3">
-        <v>46144.0</v>
-      </c>
-      <c r="F20" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
+      <c r="F20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
       <c r="G20" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>46176.0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>46268.0</v>
-      </c>
-      <c r="J20" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="I20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
+      </c>
+      <c r="J20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -2013,7 +2253,7 @@
       <c r="X20" s="4"/>
       <c r="Y20" s="4"/>
       <c r="Z20" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AA20" s="1">
         <v>60299.0</v>
@@ -2024,26 +2264,40 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C21" s="3">
-        <v>46177.0</v>
-      </c>
-      <c r="D21" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.62)</f>
+        <v>4.62</v>
+      </c>
+      <c r="D21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E21" s="3">
-        <v>46174.0</v>
-      </c>
-      <c r="F21" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
+        <v>1.2</v>
+      </c>
+      <c r="F21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G21" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="J21" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="J21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -2060,7 +2314,7 @@
       <c r="X21" s="4"/>
       <c r="Y21" s="4"/>
       <c r="Z21" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AA21" s="1">
         <v>60299.0</v>
@@ -2071,26 +2325,40 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D22" s="4"/>
+        <v>67</v>
+      </c>
+      <c r="C22" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="D22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E22" s="3">
-        <v>46177.0</v>
-      </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="3">
-        <v>46237.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
+      <c r="F22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
+      </c>
+      <c r="G22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="H22" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="I22" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J22" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="J22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -2107,7 +2375,7 @@
       <c r="X22" s="4"/>
       <c r="Y22" s="4"/>
       <c r="Z22" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="AA22" s="1">
         <v>60299.0</v>
@@ -2118,26 +2386,40 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C23" s="3">
-        <v>46237.0</v>
-      </c>
-      <c r="D23" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8466666666666667)</f>
+        <v>3.846666667</v>
+      </c>
+      <c r="D23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E23" s="3">
-        <v>46056.0</v>
-      </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="H23" s="3">
-        <v>46269.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="F23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
+      <c r="G23" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H23" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="I23" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J23" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -2154,7 +2436,7 @@
       <c r="X23" s="4"/>
       <c r="Y23" s="4"/>
       <c r="Z23" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AA23" s="1">
         <v>60299.0</v>
@@ -2165,26 +2447,40 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" s="4"/>
+        <v>71</v>
+      </c>
+      <c r="C24" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="D24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E24" s="3">
-        <v>46204.0</v>
-      </c>
-      <c r="F24" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
+        <v>1.3</v>
+      </c>
+      <c r="F24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
       <c r="G24" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="H24" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I24" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J24" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -2201,36 +2497,36 @@
       <c r="X24" s="4"/>
       <c r="Y24" s="4"/>
       <c r="Z24" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AA24" s="1">
         <v>60299.0</v>
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
-      <c r="Q25" s="4"/>
-      <c r="R25" s="4"/>
-      <c r="S25" s="4"/>
-      <c r="T25" s="4"/>
-      <c r="U25" s="4"/>
-      <c r="V25" s="4"/>
-      <c r="W25" s="4"/>
-      <c r="X25" s="4"/>
-      <c r="Y25" s="4"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="5"/>
+      <c r="U25" s="5"/>
+      <c r="V25" s="5"/>
+      <c r="W25" s="5"/>
+      <c r="X25" s="5"/>
+      <c r="Y25" s="5"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -2254,10 +2550,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -2267,10 +2563,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -2300,63 +2596,73 @@
         <v>13</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="6" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="5">
+      <c r="A2" s="6">
         <v>1.0</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>78</v>
+      <c r="B2" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="C2" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="D2" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1vS2gE-mc1A6CX14zq-8uhU927dLafFRogBm_03E8occ"",""CDIF!C2:L24"")"),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="D2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="E2" s="3">
-        <v>46144.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3157894736842106)</f>
+        <v>1.315789474</v>
       </c>
       <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
+      <c r="G2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
+      </c>
       <c r="H2" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="I2" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -2374,34 +2680,44 @@
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
-      <c r="Z2" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="AA2" s="5">
+      <c r="Z2" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="AA2" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>2.0</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>80</v>
+      <c r="B3" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="C3" s="3">
-        <v>46143.0</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="1" t="s">
-        <v>81</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
+      <c r="D3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
+      <c r="G3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5)</f>
+        <v>0.5</v>
+      </c>
       <c r="H3" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -2419,34 +2735,44 @@
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
-      <c r="Z3" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA3" s="5">
+      <c r="Z3" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA3" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>3.0</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>83</v>
+      <c r="B4" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="C4" s="3">
-        <v>46144.0</v>
-      </c>
-      <c r="D4" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.46)</f>
+        <v>2.46</v>
+      </c>
+      <c r="D4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="E4" s="3">
-        <v>46238.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.526315789473684)</f>
+        <v>2.526315789</v>
       </c>
       <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="3">
-        <v>46177.0</v>
+      <c r="G4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
+        <v>1.2</v>
+      </c>
+      <c r="H4" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="I4" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
@@ -2464,34 +2790,44 @@
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
-      <c r="Z4" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA4" s="5">
+      <c r="Z4" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="AA4" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>4.0</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="4"/>
+      <c r="B5" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="E5" s="3">
-        <v>46238.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.526315789473684)</f>
+        <v>2.526315789</v>
       </c>
       <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="3">
-        <v>46177.0</v>
+      <c r="G5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+      <c r="H5" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="I5" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
@@ -2509,34 +2845,44 @@
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
-      <c r="Z5" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AA5" s="5">
+      <c r="Z5" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="AA5" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>5.0</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>87</v>
+      <c r="B6" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="C6" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="D6" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.48)</f>
+        <v>4.48</v>
+      </c>
+      <c r="D6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="E6" s="3">
-        <v>46269.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5789473684210527)</f>
+        <v>2.578947368</v>
       </c>
       <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="3">
-        <v>46238.0</v>
+      <c r="G6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
+      <c r="H6" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="I6" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
@@ -2554,34 +2900,44 @@
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
-      <c r="Z6" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="AA6" s="5">
+      <c r="Z6" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="AA6" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5">
+      <c r="A7" s="6">
         <v>6.0</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>89</v>
+      <c r="B7" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="C7" s="3">
-        <v>46115.0</v>
-      </c>
-      <c r="D7" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.42)</f>
+        <v>3.42</v>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="E7" s="3">
-        <v>46177.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4210526315789473)</f>
+        <v>2.421052632</v>
       </c>
       <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="3">
-        <v>46057.0</v>
+      <c r="G7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
+      <c r="H7" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
       </c>
       <c r="I7" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
@@ -2599,34 +2955,44 @@
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
-      <c r="Z7" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="AA7" s="5">
+      <c r="Z7" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AA7" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5">
+      <c r="A8" s="6">
         <v>7.0</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>91</v>
+      <c r="B8" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="C8" s="3">
-        <v>46145.0</v>
-      </c>
-      <c r="D8" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.46)</f>
+        <v>3.46</v>
+      </c>
+      <c r="D8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="E8" s="3">
-        <v>46083.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2105263157894737)</f>
+        <v>1.210526316</v>
       </c>
       <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="3">
-        <v>46177.0</v>
+      <c r="G8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
+        <v>1.3</v>
+      </c>
+      <c r="H8" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="I8" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
@@ -2644,34 +3010,44 @@
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
-      <c r="Z8" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA8" s="5">
+      <c r="Z8" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AA8" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5">
+      <c r="A9" s="6">
         <v>8.0</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="4"/>
+      <c r="B9" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="D9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="E9" s="3">
-        <v>46238.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.526315789473684)</f>
+        <v>2.526315789</v>
       </c>
       <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="I9" s="3">
-        <v>46207.0</v>
+      <c r="G9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+      <c r="H9" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="I9" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
@@ -2689,34 +3065,44 @@
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
-      <c r="Z9" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="AA9" s="5">
+      <c r="Z9" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AA9" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5">
+      <c r="A10" s="6">
         <v>9.0</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>95</v>
+      <c r="B10" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="C10" s="3">
-        <v>46266.0</v>
-      </c>
-      <c r="D10" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.92)</f>
+        <v>1.92</v>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="E10" s="3">
-        <v>46177.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4210526315789473)</f>
+        <v>2.421052632</v>
       </c>
       <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="3">
-        <v>46057.0</v>
+      <c r="G10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1)</f>
+        <v>1.1</v>
+      </c>
+      <c r="H10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
       </c>
       <c r="I10" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -2734,34 +3120,44 @@
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
-      <c r="Z10" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="AA10" s="5">
+      <c r="Z10" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AA10" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5">
+      <c r="A11" s="6">
         <v>10.0</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>97</v>
+      <c r="B11" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="C11" s="3">
-        <v>46176.0</v>
-      </c>
-      <c r="D11" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5700000000000003)</f>
+        <v>3.57</v>
+      </c>
+      <c r="D11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="E11" s="3">
-        <v>46269.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5789473684210527)</f>
+        <v>2.578947368</v>
       </c>
       <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+      <c r="G11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
+      </c>
       <c r="H11" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="I11" s="3">
-        <v>46207.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="I11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -2779,34 +3175,44 @@
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
-      <c r="Z11" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA11" s="5">
+      <c r="Z11" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA11" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5">
+      <c r="A12" s="6">
         <v>11.0</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>99</v>
+      <c r="B12" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="C12" s="3">
-        <v>46237.0</v>
-      </c>
-      <c r="D12" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.81)</f>
+        <v>3.81</v>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="E12" s="3">
-        <v>46177.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4210526315789473)</f>
+        <v>2.421052632</v>
       </c>
       <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="3">
-        <v>46116.0</v>
-      </c>
-      <c r="I12" s="3">
-        <v>46207.0</v>
+      <c r="G12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
+      </c>
+      <c r="H12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
+      </c>
+      <c r="I12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
@@ -2824,34 +3230,44 @@
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
-      <c r="Z12" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="AA12" s="5">
+      <c r="Z12" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA12" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5">
+      <c r="A13" s="6">
         <v>12.0</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>101</v>
+      <c r="B13" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="C13" s="3">
-        <v>46145.0</v>
-      </c>
-      <c r="D13" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.45)</f>
+        <v>3.45</v>
+      </c>
+      <c r="D13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="E13" s="3">
-        <v>46238.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.526315789473684)</f>
+        <v>2.526315789</v>
       </c>
       <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="I13" s="3">
-        <v>46207.0</v>
+      <c r="G13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
+      <c r="H13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="I13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
@@ -2869,34 +3285,44 @@
       <c r="W13" s="4"/>
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
-      <c r="Z13" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="AA13" s="5">
+      <c r="Z13" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="AA13" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5">
+      <c r="A14" s="6">
         <v>13.0</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>103</v>
+      <c r="B14" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="C14" s="3">
-        <v>46144.0</v>
-      </c>
-      <c r="D14" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.45)</f>
+        <v>2.45</v>
+      </c>
+      <c r="D14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="E14" s="3">
-        <v>46238.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.526315789473684)</f>
+        <v>2.526315789</v>
       </c>
       <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>46207.0</v>
+      <c r="G14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
+        <v>1.2</v>
+      </c>
+      <c r="H14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="I14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
@@ -2914,34 +3340,44 @@
       <c r="W14" s="4"/>
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
-      <c r="Z14" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA14" s="5">
+      <c r="Z14" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA14" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5">
+      <c r="A15" s="6">
         <v>14.0</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>105</v>
+      <c r="B15" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="C15" s="3">
-        <v>46145.0</v>
-      </c>
-      <c r="D15" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.54)</f>
+        <v>3.54</v>
+      </c>
+      <c r="D15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="E15" s="3">
-        <v>46207.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.473684210526316)</f>
+        <v>2.473684211</v>
       </c>
       <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="3">
-        <v>46116.0</v>
+      <c r="G15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
+      </c>
+      <c r="H15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="I15" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
@@ -2959,34 +3395,44 @@
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
-      <c r="Z15" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="AA15" s="5">
+      <c r="Z15" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="AA15" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5">
+      <c r="A16" s="6">
         <v>15.0</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>107</v>
+      <c r="B16" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="C16" s="3">
-        <v>46116.0</v>
-      </c>
-      <c r="D16" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.39)</f>
+        <v>4.39</v>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="E16" s="3">
-        <v>46146.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3684210526315788)</f>
+        <v>2.368421053</v>
       </c>
       <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="I16" s="3">
-        <v>46026.0</v>
+      <c r="G16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
+        <v>1.8</v>
+      </c>
+      <c r="H16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="I16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
@@ -3004,34 +3450,44 @@
       <c r="W16" s="4"/>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
-      <c r="Z16" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA16" s="5">
+      <c r="Z16" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="AA16" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5">
+      <c r="A17" s="6">
         <v>16.0</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" s="4"/>
+      <c r="B17" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0300000000000002)</f>
+        <v>2.03</v>
+      </c>
+      <c r="D17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="E17" s="3">
-        <v>46055.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1578947368421053)</f>
+        <v>1.157894737</v>
       </c>
       <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="3">
-        <v>46085.0</v>
+      <c r="G17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
+        <v>0.8</v>
+      </c>
+      <c r="H17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="I17" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
@@ -3049,34 +3505,44 @@
       <c r="W17" s="4"/>
       <c r="X17" s="4"/>
       <c r="Y17" s="4"/>
-      <c r="Z17" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA17" s="5">
+      <c r="Z17" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA17" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5">
+      <c r="A18" s="6">
         <v>17.0</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="1" t="s">
-        <v>113</v>
+      <c r="B18" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C18" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.02)</f>
+        <v>2.02</v>
+      </c>
+      <c r="D18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.05263157894736842)</f>
+        <v>0.05263157895</v>
       </c>
       <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="1" t="s">
-        <v>114</v>
+      <c r="G18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6)</f>
+        <v>0.6</v>
+      </c>
+      <c r="H18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.2)</f>
+        <v>0.2</v>
       </c>
       <c r="I18" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
@@ -3094,34 +3560,44 @@
       <c r="W18" s="4"/>
       <c r="X18" s="4"/>
       <c r="Y18" s="4"/>
-      <c r="Z18" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA18" s="5">
+      <c r="Z18" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA18" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5">
+      <c r="A19" s="6">
         <v>18.0</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="4"/>
+      <c r="B19" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="D19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="E19" s="3">
-        <v>46207.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.473684210526316)</f>
+        <v>2.473684211</v>
       </c>
       <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
+      <c r="G19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="H19" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="I19" s="3">
-        <v>46116.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="I19" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
@@ -3139,34 +3615,44 @@
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
       <c r="Y19" s="4"/>
-      <c r="Z19" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="AA19" s="5">
+      <c r="Z19" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="AA19" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5">
+      <c r="A20" s="6">
         <v>19.0</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>118</v>
+      <c r="B20" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="C20" s="3">
-        <v>46116.0</v>
-      </c>
-      <c r="D20" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.35)</f>
+        <v>4.35</v>
+      </c>
+      <c r="D20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="E20" s="3">
-        <v>46238.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.526315789473684)</f>
+        <v>2.526315789</v>
       </c>
       <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>46207.0</v>
+      <c r="G20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
+        <v>1.8</v>
+      </c>
+      <c r="H20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="I20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
@@ -3184,34 +3670,44 @@
       <c r="W20" s="4"/>
       <c r="X20" s="4"/>
       <c r="Y20" s="4"/>
-      <c r="Z20" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="AA20" s="5">
+      <c r="Z20" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA20" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5">
+      <c r="A21" s="6">
         <v>20.0</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>120</v>
+      <c r="B21" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="C21" s="3">
-        <v>46269.0</v>
-      </c>
-      <c r="D21" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="D21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="E21" s="3">
-        <v>46146.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3684210526315788)</f>
+        <v>2.368421053</v>
       </c>
       <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="3">
-        <v>46177.0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>46116.0</v>
+      <c r="G21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
+      <c r="H21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
+      <c r="I21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
@@ -3229,37 +3725,61 @@
       <c r="W21" s="4"/>
       <c r="X21" s="4"/>
       <c r="Y21" s="4"/>
-      <c r="Z21" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="AA21" s="5">
+      <c r="Z21" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA21" s="6">
         <v>55581.0</v>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4"/>
-      <c r="S22" s="4"/>
-      <c r="T22" s="4"/>
-      <c r="U22" s="4"/>
-      <c r="V22" s="4"/>
-      <c r="W22" s="4"/>
-      <c r="X22" s="4"/>
-      <c r="Y22" s="4"/>
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="5"/>
+    </row>
+    <row r="23">
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+    </row>
+    <row r="24">
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -3281,10 +3801,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -3324,70 +3844,84 @@
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="6" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="5">
+      <c r="A2" s="6">
         <v>1.0</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>122</v>
+      <c r="B2" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="C2" s="3">
-        <v>46114.0</v>
-      </c>
-      <c r="D2" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1vS2gE-mc1A6CX14zq-8uhU927dLafFRogBm_03E8occ"",""MAT2_B!C2:L26"")"),2.4266666666666667)</f>
+        <v>2.426666667</v>
+      </c>
+      <c r="D2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E2" s="3">
-        <v>46177.0</v>
-      </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="H2" s="3">
-        <v>46269.0</v>
-      </c>
-      <c r="I2" s="3">
-        <v>46057.0</v>
-      </c>
-      <c r="J2" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
+      <c r="F2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
+      <c r="G2" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H2" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="I2" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
+      <c r="J2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
@@ -3403,38 +3937,52 @@
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
-      <c r="Z2" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="AA2" s="5">
+      <c r="Z2" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA2" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>2.0</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>124</v>
+      <c r="B3" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="C3" s="3">
-        <v>46115.0</v>
-      </c>
-      <c r="D3" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.42)</f>
+        <v>3.42</v>
+      </c>
+      <c r="D3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E3" s="3">
-        <v>46177.0</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="I3" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="J3" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
+      <c r="F3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
+      <c r="G3" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="H3" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="I3" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="J3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
@@ -3450,38 +3998,52 @@
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
-      <c r="Z3" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA3" s="5">
+      <c r="Z3" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="AA3" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>3.0</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>126</v>
+      <c r="B4" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="C4" s="3">
-        <v>46115.0</v>
-      </c>
-      <c r="D4" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3666666666666667)</f>
+        <v>3.366666667</v>
+      </c>
+      <c r="D4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E4" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="3">
-        <v>46146.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
+      </c>
+      <c r="F4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
+      <c r="G4" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="H4" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="I4" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J4" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="J4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
@@ -3497,38 +4059,52 @@
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
-      <c r="Z4" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="AA4" s="5">
+      <c r="Z4" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AA4" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>4.0</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>128</v>
+      <c r="B5" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="C5" s="3">
-        <v>46056.0</v>
-      </c>
-      <c r="D5" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.166666666666667)</f>
+        <v>3.166666667</v>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E5" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="3">
-        <v>46146.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
+      </c>
+      <c r="F5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
+      <c r="G5" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="H5" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="I5" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J5" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="J5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -3544,34 +4120,46 @@
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
-      <c r="Z5" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="AA5" s="5">
+      <c r="Z5" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="AA5" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>5.0</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="1" t="s">
-        <v>113</v>
+      <c r="B6" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.12000000000000001)</f>
+        <v>0.12</v>
+      </c>
+      <c r="D6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E6" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
+      <c r="F6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
+      <c r="G6" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+      <c r="J6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -3587,35 +4175,49 @@
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
-      <c r="AA6" s="5">
+      <c r="AA6" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5">
+      <c r="A7" s="6">
         <v>6.0</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>131</v>
+      <c r="B7" s="6" t="s">
+        <v>123</v>
       </c>
       <c r="C7" s="3">
-        <v>46056.0</v>
-      </c>
-      <c r="D7" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.22)</f>
+        <v>3.22</v>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E7" s="3">
-        <v>46025.0</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="3">
-        <v>46146.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
+      <c r="F7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
+      <c r="G7" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="H7" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="J7" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="J7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
@@ -3631,38 +4233,52 @@
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
-      <c r="Z7" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="AA7" s="5">
+      <c r="Z7" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA7" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5">
+      <c r="A8" s="6">
         <v>7.0</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>133</v>
+      <c r="B8" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="C8" s="3">
-        <v>46057.0</v>
-      </c>
-      <c r="D8" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.24)</f>
+        <v>4.24</v>
+      </c>
+      <c r="D8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E8" s="3">
-        <v>46056.0</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>46238.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
+      <c r="F8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
+      <c r="G8" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H8" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="I8" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J8" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
@@ -3678,38 +4294,52 @@
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
-      <c r="Z8" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="AA8" s="5">
+      <c r="Z8" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="AA8" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5">
+      <c r="A9" s="6">
         <v>8.0</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="4"/>
+      <c r="B9" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="D9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E9" s="3">
-        <v>46269.0</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="3">
-        <v>46238.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
+      </c>
+      <c r="F9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
+      </c>
+      <c r="G9" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="H9" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="I9" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="J9" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="I9" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="J9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
@@ -3725,38 +4355,52 @@
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
-      <c r="Z9" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="AA9" s="5">
+      <c r="Z9" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="AA9" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5">
+      <c r="A10" s="6">
         <v>9.0</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="4"/>
+      <c r="B10" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.966666666666667)</f>
+        <v>4.966666667</v>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E10" s="3">
-        <v>46237.0</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="H10" s="3">
-        <v>46083.0</v>
-      </c>
-      <c r="I10" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="J10" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
+      </c>
+      <c r="F10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
+      </c>
+      <c r="G10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
+      <c r="H10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
+      <c r="I10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="J10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
@@ -3772,38 +4416,52 @@
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
-      <c r="Z10" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="AA10" s="5">
+      <c r="Z10" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="AA10" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5">
+      <c r="A11" s="6">
         <v>10.0</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>139</v>
+      <c r="B11" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="C11" s="3">
-        <v>46084.0</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="3">
-        <v>46237.0</v>
-      </c>
-      <c r="H11" s="3">
-        <v>46085.0</v>
-      </c>
-      <c r="I11" s="3">
-        <v>46237.0</v>
-      </c>
-      <c r="J11" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2933333333333334)</f>
+        <v>3.293333333</v>
+      </c>
+      <c r="D11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E11" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="F11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
+      <c r="G11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
+      <c r="H11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="I11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
+      <c r="J11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -3819,38 +4477,52 @@
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
-      <c r="Z11" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="AA11" s="5">
+      <c r="Z11" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="AA11" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5">
+      <c r="A12" s="6">
         <v>11.0</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>142</v>
+      <c r="B12" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="C12" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="H12" s="3">
-        <v>46116.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.493333333333333)</f>
+        <v>4.493333333</v>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E12" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
+      <c r="F12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
+      <c r="G12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="H12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="I12" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J12" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -3866,38 +4538,52 @@
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
-      <c r="Z12" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="AA12" s="5">
+      <c r="Z12" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA12" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5">
+      <c r="A13" s="6">
         <v>12.0</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>144</v>
+      <c r="B13" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="C13" s="3">
-        <v>46026.0</v>
-      </c>
-      <c r="D13" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.086666666666667)</f>
+        <v>4.086666667</v>
+      </c>
+      <c r="D13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E13" s="3">
-        <v>46267.0</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="3">
-        <v>46238.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
+      <c r="F13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
+      <c r="G13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="H13" s="1">
-        <v>4.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="I13" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J13" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
@@ -3913,38 +4599,52 @@
       <c r="W13" s="4"/>
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
-      <c r="Z13" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA13" s="5">
+      <c r="Z13" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA13" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5">
+      <c r="A14" s="6">
         <v>13.0</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>146</v>
+      <c r="B14" s="6" t="s">
+        <v>137</v>
       </c>
       <c r="C14" s="3">
-        <v>46114.0</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F14" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
+      <c r="D14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E14" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
+        <v>0.8</v>
+      </c>
       <c r="G14" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I14" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J14" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -3960,38 +4660,52 @@
       <c r="W14" s="4"/>
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
-      <c r="Z14" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="AA14" s="5">
+      <c r="Z14" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="AA14" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5">
+      <c r="A15" s="6">
         <v>14.0</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>148</v>
+      <c r="B15" s="6" t="s">
+        <v>139</v>
       </c>
       <c r="C15" s="3">
-        <v>46084.0</v>
-      </c>
-      <c r="D15" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3333333333333335)</f>
+        <v>3.333333333</v>
+      </c>
+      <c r="D15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E15" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>46146.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
+      <c r="F15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
+      <c r="G15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="H15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="I15" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J15" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="J15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -4007,38 +4721,52 @@
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
-      <c r="Z15" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="AA15" s="5">
+      <c r="Z15" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="AA15" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5">
+      <c r="A16" s="6">
         <v>15.0</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>150</v>
+      <c r="B16" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="C16" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="D16" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7133333333333334)</f>
+        <v>3.713333333</v>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E16" s="3">
-        <v>46176.0</v>
-      </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="3">
-        <v>46176.0</v>
-      </c>
-      <c r="H16" s="3">
-        <v>46025.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
+      </c>
+      <c r="F16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
+      <c r="G16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="H16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
+        <v>3.1</v>
       </c>
       <c r="I16" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="J16" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
+      <c r="J16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -4054,38 +4782,52 @@
       <c r="W16" s="4"/>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
-      <c r="Z16" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="AA16" s="5">
+      <c r="Z16" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="AA16" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5">
+      <c r="A17" s="6">
         <v>16.0</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>152</v>
+      <c r="B17" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="C17" s="3">
-        <v>46269.0</v>
-      </c>
-      <c r="D17" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.94)</f>
+        <v>4.94</v>
+      </c>
+      <c r="D17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E17" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="3">
-        <v>46146.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="F17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
+      </c>
+      <c r="G17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="H17" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="I17" s="3">
-        <v>46177.0</v>
-      </c>
-      <c r="J17" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="I17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
+      <c r="J17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -4101,38 +4843,52 @@
       <c r="W17" s="4"/>
       <c r="X17" s="4"/>
       <c r="Y17" s="4"/>
-      <c r="Z17" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="AA17" s="5">
+      <c r="Z17" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA17" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5">
+      <c r="A18" s="6">
         <v>17.0</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D18" s="4"/>
+      <c r="B18" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C18" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.966666666666667)</f>
+        <v>3.966666667</v>
+      </c>
+      <c r="D18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E18" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="H18" s="3">
-        <v>46269.0</v>
-      </c>
-      <c r="I18" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="J18" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
+      </c>
+      <c r="F18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="G18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="I18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="J18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -4148,38 +4904,52 @@
       <c r="W18" s="4"/>
       <c r="X18" s="4"/>
       <c r="Y18" s="4"/>
-      <c r="Z18" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="AA18" s="5">
+      <c r="Z18" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA18" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5">
+      <c r="A19" s="6">
         <v>18.0</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>156</v>
+      <c r="B19" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="C19" s="3">
-        <v>46205.0</v>
-      </c>
-      <c r="D19" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7333333333333334)</f>
+        <v>2.733333333</v>
+      </c>
+      <c r="D19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E19" s="3">
-        <v>46204.0</v>
-      </c>
-      <c r="F19" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
+        <v>1.3</v>
+      </c>
+      <c r="F19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
+        <v>1.4</v>
+      </c>
       <c r="G19" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="I19" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J19" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -4195,38 +4965,52 @@
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
       <c r="Y19" s="4"/>
-      <c r="Z19" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="AA19" s="5">
+      <c r="Z19" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="AA19" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5">
+      <c r="A20" s="6">
         <v>19.0</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>158</v>
+      <c r="B20" s="6" t="s">
+        <v>149</v>
       </c>
       <c r="C20" s="3">
-        <v>46269.0</v>
-      </c>
-      <c r="D20" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.873333333333333)</f>
+        <v>4.873333333</v>
+      </c>
+      <c r="D20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E20" s="3">
-        <v>46116.0</v>
-      </c>
-      <c r="F20" s="4"/>
-      <c r="G20" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>46057.0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>46026.0</v>
-      </c>
-      <c r="J20" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
+      </c>
+      <c r="F20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
+      </c>
+      <c r="G20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
+      <c r="I20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
+      </c>
+      <c r="J20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -4242,38 +5026,52 @@
       <c r="W20" s="4"/>
       <c r="X20" s="4"/>
       <c r="Y20" s="4"/>
-      <c r="Z20" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="AA20" s="5">
+      <c r="Z20" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="AA20" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5">
+      <c r="A21" s="6">
         <v>20.0</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>160</v>
+      <c r="B21" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="C21" s="3">
-        <v>46176.0</v>
-      </c>
-      <c r="D21" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6333333333333333)</f>
+        <v>3.633333333</v>
+      </c>
+      <c r="D21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E21" s="3">
-        <v>46056.0</v>
-      </c>
-      <c r="F21" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
+      <c r="F21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G21" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="H21" s="3">
-        <v>46146.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="H21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="I21" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J21" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -4289,38 +5087,52 @@
       <c r="W21" s="4"/>
       <c r="X21" s="4"/>
       <c r="Y21" s="4"/>
-      <c r="Z21" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="AA21" s="5">
+      <c r="Z21" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="AA21" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5">
+      <c r="A22" s="6">
         <v>21.0</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>162</v>
+      <c r="B22" s="6" t="s">
+        <v>153</v>
       </c>
       <c r="C22" s="3">
-        <v>46176.0</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="3">
-        <v>46085.0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>46238.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6066666666666665)</f>
+        <v>3.606666667</v>
+      </c>
+      <c r="D22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E22" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
+      <c r="F22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+      <c r="G22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="H22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="I22" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J22" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -4336,38 +5148,52 @@
       <c r="W22" s="4"/>
       <c r="X22" s="4"/>
       <c r="Y22" s="4"/>
-      <c r="Z22" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="AA22" s="5">
+      <c r="Z22" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="AA22" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5">
+      <c r="A23" s="6">
         <v>22.0</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D23" s="4"/>
+      <c r="B23" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C23" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.953333333333333)</f>
+        <v>4.953333333</v>
+      </c>
+      <c r="D23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E23" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="3">
-        <v>46085.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="F23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
+      </c>
+      <c r="G23" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="H23" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="I23" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J23" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="J23" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -4383,38 +5209,52 @@
       <c r="W23" s="4"/>
       <c r="X23" s="4"/>
       <c r="Y23" s="4"/>
-      <c r="Z23" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA23" s="5">
+      <c r="Z23" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="AA23" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5">
+      <c r="A24" s="6">
         <v>23.0</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>166</v>
+      <c r="B24" s="6" t="s">
+        <v>157</v>
       </c>
       <c r="C24" s="3">
-        <v>46267.0</v>
-      </c>
-      <c r="D24" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0366666666666666)</f>
+        <v>3.036666667</v>
+      </c>
+      <c r="D24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E24" s="3">
-        <v>46116.0</v>
-      </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>46085.0</v>
-      </c>
-      <c r="J24" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
+      </c>
+      <c r="F24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
+      <c r="G24" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="H24" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="I24" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="J24" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
@@ -4430,38 +5270,52 @@
       <c r="W24" s="4"/>
       <c r="X24" s="4"/>
       <c r="Y24" s="4"/>
-      <c r="Z24" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="AA24" s="5">
+      <c r="Z24" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="AA24" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5">
+      <c r="A25" s="6">
         <v>24.0</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D25" s="4"/>
+      <c r="B25" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.003333333333333)</f>
+        <v>3.003333333</v>
+      </c>
+      <c r="D25" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E25" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="H25" s="3">
-        <v>46238.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="F25" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
+      <c r="G25" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="H25" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="I25" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J25" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="J25" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
@@ -4477,38 +5331,52 @@
       <c r="W25" s="4"/>
       <c r="X25" s="4"/>
       <c r="Y25" s="4"/>
-      <c r="Z25" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="AA25" s="5">
+      <c r="Z25" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AA25" s="6">
         <v>55546.0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5">
+      <c r="A26" s="6">
         <v>25.0</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" s="4"/>
+      <c r="B26" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C26" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="D26" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E26" s="3">
-        <v>46084.0</v>
-      </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="3">
-        <v>46238.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="F26" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="G26" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="H26" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="I26" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J26" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
@@ -4524,10 +5392,10 @@
       <c r="W26" s="4"/>
       <c r="X26" s="4"/>
       <c r="Y26" s="4"/>
-      <c r="Z26" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="AA26" s="5">
+      <c r="Z26" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="AA26" s="6">
         <v>55546.0</v>
       </c>
     </row>
@@ -4576,10 +5444,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -4589,7 +5457,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -4619,66 +5487,79 @@
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="6" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="5">
+      <c r="A2" s="6">
         <v>1.0</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>172</v>
+      <c r="B2" s="6" t="s">
+        <v>163</v>
       </c>
       <c r="C2" s="3">
-        <v>46083.0</v>
-      </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="3">
-        <v>46145.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1vS2gE-mc1A6CX14zq-8uhU927dLafFRogBm_03E8occ"",""EST2!C2:L24"")"),2.3400000000000003)</f>
+        <v>2.34</v>
+      </c>
+      <c r="D2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="F2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
+      <c r="G2" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="H2" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="I2" s="3">
-        <v>46269.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="I2" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
@@ -4696,34 +5577,47 @@
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
-      <c r="Z2" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="AA2" s="5">
+      <c r="Z2" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="AA2" s="6">
         <v>63507.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>2.0</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="3">
-        <v>46085.0</v>
+      <c r="B3" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="D3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
+        <v>3.1</v>
+      </c>
+      <c r="F3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
+      </c>
+      <c r="G3" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="H3" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="I3" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
@@ -4741,34 +5635,47 @@
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
-      <c r="Z3" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="AA3" s="5">
+      <c r="Z3" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="AA3" s="6">
         <v>63507.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>3.0</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>176</v>
+      <c r="B4" s="6" t="s">
+        <v>167</v>
       </c>
       <c r="C4" s="3">
-        <v>46145.0</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.54)</f>
+        <v>3.54</v>
+      </c>
+      <c r="D4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
+      </c>
+      <c r="F4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
       <c r="G4" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="I4" s="3">
-        <v>46269.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="I4" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
@@ -4786,34 +5693,47 @@
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
-      <c r="Z4" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="AA4" s="5">
+      <c r="Z4" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="AA4" s="6">
         <v>63507.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>4.0</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>178</v>
+      <c r="B5" s="6" t="s">
+        <v>169</v>
       </c>
       <c r="C5" s="3">
-        <v>46177.0</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="3">
-        <v>46084.0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>46236.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.61)</f>
+        <v>4.61</v>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+      <c r="F5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
+      <c r="G5" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
+      </c>
+      <c r="H5" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
       </c>
       <c r="I5" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
@@ -4831,34 +5751,47 @@
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
-      <c r="Z5" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="AA5" s="5">
+      <c r="Z5" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="AA5" s="6">
         <v>63507.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>5.0</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>180</v>
+      <c r="B6" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="C6" s="3">
-        <v>46115.0</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="3">
-        <v>46085.0</v>
-      </c>
-      <c r="H6" s="3">
-        <v>46238.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.41)</f>
+        <v>3.41</v>
+      </c>
+      <c r="D6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
+      <c r="F6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
+      </c>
+      <c r="G6" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="H6" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="I6" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
@@ -4876,34 +5809,47 @@
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
-      <c r="Z6" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="AA6" s="5">
+      <c r="Z6" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA6" s="6">
         <v>63507.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5">
+      <c r="A7" s="6">
         <v>6.0</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>182</v>
+      <c r="B7" s="6" t="s">
+        <v>173</v>
       </c>
       <c r="C7" s="3">
-        <v>46116.0</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.43)</f>
+        <v>4.43</v>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
+        <v>1.4</v>
+      </c>
+      <c r="F7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G7" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H7" s="3">
-        <v>46085.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="I7" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
@@ -4921,34 +5867,47 @@
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
-      <c r="Z7" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="AA7" s="5">
+      <c r="Z7" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="AA7" s="6">
         <v>63507.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5">
+      <c r="A8" s="6">
         <v>7.0</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="3">
-        <v>46237.0</v>
+      <c r="B8" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="D8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
+      <c r="F8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
+        <v>3.1</v>
+      </c>
+      <c r="G8" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="H8" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="I8" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
@@ -4966,34 +5925,47 @@
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
-      <c r="Z8" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="AA8" s="5">
+      <c r="Z8" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="AA8" s="6">
         <v>63507.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5">
+      <c r="A9" s="6">
         <v>8.0</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>186</v>
+      <c r="B9" s="6" t="s">
+        <v>177</v>
       </c>
       <c r="C9" s="3">
-        <v>46116.0</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="3">
-        <v>46237.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.38)</f>
+        <v>4.38</v>
+      </c>
+      <c r="D9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
+      <c r="F9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
+      </c>
+      <c r="G9" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="H9" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="I9" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
@@ -5011,34 +5983,47 @@
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
-      <c r="Z9" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="AA9" s="5">
+      <c r="Z9" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="AA9" s="6">
         <v>63507.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5">
+      <c r="A10" s="6">
         <v>9.0</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>188</v>
+      <c r="B10" s="6" t="s">
+        <v>179</v>
       </c>
       <c r="C10" s="3">
-        <v>46115.0</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.43)</f>
+        <v>3.43</v>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
+        <v>1.4</v>
+      </c>
+      <c r="F10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
+      </c>
       <c r="G10" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H10" s="3">
-        <v>46085.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="I10" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
@@ -5056,34 +6041,47 @@
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
-      <c r="Z10" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="AA10" s="5">
+      <c r="Z10" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="AA10" s="6">
         <v>63507.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5">
+      <c r="A11" s="6">
         <v>10.0</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>190</v>
+      <c r="B11" s="6" t="s">
+        <v>181</v>
       </c>
       <c r="C11" s="3">
-        <v>46055.0</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="3">
-        <v>46145.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.15)</f>
+        <v>2.15</v>
+      </c>
+      <c r="D11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
+        <v>1.2</v>
+      </c>
+      <c r="F11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1)</f>
+        <v>1.1</v>
+      </c>
+      <c r="G11" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="H11" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I11" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
@@ -5101,34 +6099,47 @@
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
-      <c r="Z11" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA11" s="5">
+      <c r="Z11" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA11" s="6">
         <v>63507.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5">
+      <c r="A12" s="6">
         <v>11.0</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="B12" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C12" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="G12" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I12" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
@@ -5146,34 +6157,47 @@
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
-      <c r="Z12" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="AA12" s="5">
+      <c r="Z12" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="AA12" s="6">
         <v>63507.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5">
+      <c r="A13" s="6">
         <v>12.0</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>194</v>
+      <c r="B13" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="C13" s="3">
-        <v>46115.0</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
+      </c>
+      <c r="D13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
+        <v>1.2</v>
+      </c>
       <c r="G13" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I13" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
@@ -5191,34 +6215,47 @@
       <c r="W13" s="4"/>
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
-      <c r="Z13" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="AA13" s="5">
+      <c r="Z13" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="AA13" s="6">
         <v>63507.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5">
+      <c r="A14" s="6">
         <v>13.0</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>196</v>
+      <c r="B14" s="6" t="s">
+        <v>187</v>
       </c>
       <c r="C14" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="3">
-        <v>46084.0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>46237.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.71)</f>
+        <v>3.71</v>
+      </c>
+      <c r="D14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
+      <c r="F14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+      <c r="G14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
+      </c>
+      <c r="H14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="I14" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
@@ -5236,34 +6273,47 @@
       <c r="W14" s="4"/>
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
-      <c r="Z14" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="AA14" s="5">
+      <c r="Z14" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="AA14" s="6">
         <v>63507.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5">
+      <c r="A15" s="6">
         <v>14.0</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>198</v>
+      <c r="B15" s="6" t="s">
+        <v>189</v>
       </c>
       <c r="C15" s="3">
-        <v>46057.0</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="3">
-        <v>46237.0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>46145.0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>46146.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.18)</f>
+        <v>4.18</v>
+      </c>
+      <c r="D15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
+      </c>
+      <c r="F15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
+      </c>
+      <c r="G15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
+      <c r="H15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
+      <c r="I15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
@@ -5281,34 +6331,47 @@
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
-      <c r="Z15" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="AA15" s="5">
+      <c r="Z15" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="AA15" s="6">
         <v>63507.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5">
+      <c r="A16" s="6">
         <v>15.0</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="B16" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C16" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
+      <c r="F16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
+        <v>3.1</v>
+      </c>
       <c r="G16" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="H16" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="I16" s="3">
-        <v>46269.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
+      <c r="H16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="I16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
@@ -5326,12 +6389,108 @@
       <c r="W16" s="4"/>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
-      <c r="Z16" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="AA16" s="5">
+      <c r="Z16" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="AA16" s="6">
         <v>63507.0</v>
       </c>
+    </row>
+    <row r="17">
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+    </row>
+    <row r="18">
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+    </row>
+    <row r="20">
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+    </row>
+    <row r="21">
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+    </row>
+    <row r="22">
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+    </row>
+    <row r="23">
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+    </row>
+    <row r="24">
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -5353,10 +6512,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -5396,70 +6555,84 @@
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="Z1" s="6" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="6" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="5">
+      <c r="A2" s="6">
         <v>1.0</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>202</v>
+      <c r="B2" s="6" t="s">
+        <v>193</v>
       </c>
       <c r="C2" s="3">
-        <v>46056.0</v>
-      </c>
-      <c r="D2" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1vS2gE-mc1A6CX14zq-8uhU927dLafFRogBm_03E8occ"",""MAT2_C!C2:L24"")"),3.22)</f>
+        <v>3.22</v>
+      </c>
+      <c r="D2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E2" s="3">
-        <v>46025.0</v>
-      </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="H2" s="3">
-        <v>46146.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
+      <c r="F2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
+      <c r="G2" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H2" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="I2" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J2" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
@@ -5475,38 +6648,52 @@
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="4"/>
-      <c r="Z2" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="AA2" s="5">
+      <c r="Z2" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="AA2" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>2.0</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>204</v>
+      <c r="B3" s="6" t="s">
+        <v>195</v>
       </c>
       <c r="C3" s="3">
-        <v>46114.0</v>
-      </c>
-      <c r="D3" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.44)</f>
+        <v>2.44</v>
+      </c>
+      <c r="D3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E3" s="3">
-        <v>46056.0</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>46238.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
+      <c r="F3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
+      </c>
+      <c r="G3" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H3" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="I3" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J3" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
@@ -5522,38 +6709,52 @@
       <c r="W3" s="4"/>
       <c r="X3" s="4"/>
       <c r="Y3" s="4"/>
-      <c r="Z3" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="AA3" s="5">
+      <c r="Z3" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="AA3" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5">
+      <c r="A4" s="6">
         <v>3.0</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="4"/>
+      <c r="B4" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C4" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="D4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E4" s="3">
-        <v>46025.0</v>
-      </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="H4" s="3">
-        <v>46177.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
+      <c r="F4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="G4" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H4" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="I4" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J4" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
@@ -5569,38 +6770,52 @@
       <c r="W4" s="4"/>
       <c r="X4" s="4"/>
       <c r="Y4" s="4"/>
-      <c r="Z4" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="AA4" s="5">
+      <c r="Z4" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="AA4" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5">
+      <c r="A5" s="6">
         <v>4.0</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>208</v>
+      <c r="B5" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="C5" s="3">
-        <v>46176.0</v>
-      </c>
-      <c r="D5" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.64)</f>
+        <v>3.64</v>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E5" s="3">
-        <v>46056.0</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>46269.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
+      <c r="F5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+      <c r="G5" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
+      <c r="H5" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="I5" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J5" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
@@ -5616,38 +6831,52 @@
       <c r="W5" s="4"/>
       <c r="X5" s="4"/>
       <c r="Y5" s="4"/>
-      <c r="Z5" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="AA5" s="5">
+      <c r="Z5" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="AA5" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5">
+      <c r="A6" s="6">
         <v>5.0</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>210</v>
+      <c r="B6" s="6" t="s">
+        <v>201</v>
       </c>
       <c r="C6" s="3">
-        <v>46114.0</v>
-      </c>
-      <c r="D6" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.44)</f>
+        <v>2.44</v>
+      </c>
+      <c r="D6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E6" s="3">
-        <v>46056.0</v>
-      </c>
-      <c r="F6" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
+      <c r="F6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
+      </c>
       <c r="G6" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H6" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="I6" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="J6" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="I6" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="J6" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
@@ -5663,38 +6892,52 @@
       <c r="W6" s="4"/>
       <c r="X6" s="4"/>
       <c r="Y6" s="4"/>
-      <c r="Z6" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="AA6" s="5">
+      <c r="Z6" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="AA6" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5">
+      <c r="A7" s="6">
         <v>6.0</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>212</v>
+      <c r="B7" s="6" t="s">
+        <v>203</v>
       </c>
       <c r="C7" s="3">
-        <v>46025.0</v>
-      </c>
-      <c r="D7" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.086666666666667)</f>
+        <v>3.086666667</v>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E7" s="3">
-        <v>46116.0</v>
-      </c>
-      <c r="F7" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
+      </c>
+      <c r="F7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
       <c r="G7" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="H7" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="J7" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
+      <c r="H7" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="I7" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="J7" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
@@ -5710,38 +6953,52 @@
       <c r="W7" s="4"/>
       <c r="X7" s="4"/>
       <c r="Y7" s="4"/>
-      <c r="Z7" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="AA7" s="5">
+      <c r="Z7" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="AA7" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5">
+      <c r="A8" s="6">
         <v>7.0</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>214</v>
+      <c r="B8" s="6" t="s">
+        <v>205</v>
       </c>
       <c r="C8" s="3">
-        <v>46025.0</v>
-      </c>
-      <c r="D8" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.066666666666667)</f>
+        <v>3.066666667</v>
+      </c>
+      <c r="D8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E8" s="3">
-        <v>46085.0</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="3">
-        <v>46085.0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>46026.0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>46177.0</v>
-      </c>
-      <c r="J8" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
+      </c>
+      <c r="F8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
+      <c r="G8" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="H8" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
+      </c>
+      <c r="I8" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
+      <c r="J8" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
@@ -5757,38 +7014,52 @@
       <c r="W8" s="4"/>
       <c r="X8" s="4"/>
       <c r="Y8" s="4"/>
-      <c r="Z8" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA8" s="5">
+      <c r="Z8" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA8" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5">
+      <c r="A9" s="6">
         <v>8.0</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>216</v>
+      <c r="B9" s="6" t="s">
+        <v>207</v>
       </c>
       <c r="C9" s="3">
-        <v>46269.0</v>
-      </c>
-      <c r="D9" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.946666666666667)</f>
+        <v>4.946666667</v>
+      </c>
+      <c r="D9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E9" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>46116.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="F9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
+      </c>
+      <c r="G9" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H9" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="I9" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J9" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="J9" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
@@ -5804,38 +7075,52 @@
       <c r="W9" s="4"/>
       <c r="X9" s="4"/>
       <c r="Y9" s="4"/>
-      <c r="Z9" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="AA9" s="5">
+      <c r="Z9" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="AA9" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5">
+      <c r="A10" s="6">
         <v>9.0</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>178</v>
+      <c r="B10" s="6" t="s">
+        <v>169</v>
       </c>
       <c r="C10" s="3">
-        <v>46115.0</v>
-      </c>
-      <c r="D10" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3533333333333335)</f>
+        <v>3.353333333</v>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E10" s="3">
-        <v>46236.0</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="3">
-        <v>46207.0</v>
-      </c>
-      <c r="H10" s="3">
-        <v>46176.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
+      <c r="F10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
+        <v>1.8</v>
+      </c>
+      <c r="G10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
+      <c r="H10" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
       </c>
       <c r="I10" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J10" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
@@ -5851,38 +7136,52 @@
       <c r="W10" s="4"/>
       <c r="X10" s="4"/>
       <c r="Y10" s="4"/>
-      <c r="Z10" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="AA10" s="5">
+      <c r="Z10" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="AA10" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5">
+      <c r="A11" s="6">
         <v>10.0</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="4"/>
+      <c r="B11" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C11" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="D11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E11" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
+      <c r="F11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
       <c r="G11" s="1">
-        <v>4.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="H11" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="I11" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J11" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
@@ -5898,38 +7197,52 @@
       <c r="W11" s="4"/>
       <c r="X11" s="4"/>
       <c r="Y11" s="4"/>
-      <c r="Z11" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="AA11" s="5">
+      <c r="Z11" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="AA11" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5">
+      <c r="A12" s="6">
         <v>11.0</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>220</v>
+      <c r="B12" s="6" t="s">
+        <v>211</v>
       </c>
       <c r="C12" s="3">
-        <v>46057.0</v>
-      </c>
-      <c r="D12" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.153333333333333)</f>
+        <v>4.153333333</v>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E12" s="3">
-        <v>46084.0</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="3">
-        <v>46238.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="F12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
+      <c r="G12" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="H12" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I12" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J12" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="J12" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
@@ -5945,38 +7258,52 @@
       <c r="W12" s="4"/>
       <c r="X12" s="4"/>
       <c r="Y12" s="4"/>
-      <c r="Z12" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="AA12" s="5">
+      <c r="Z12" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="AA12" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5">
+      <c r="A13" s="6">
         <v>12.0</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="4"/>
+      <c r="B13" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C13" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="D13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E13" s="3">
-        <v>46056.0</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="3">
-        <v>46269.0</v>
-      </c>
-      <c r="H13" s="3">
-        <v>46238.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="F13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="G13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="H13" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="I13" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J13" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
@@ -5992,38 +7319,52 @@
       <c r="W13" s="4"/>
       <c r="X13" s="4"/>
       <c r="Y13" s="4"/>
-      <c r="Z13" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="AA13" s="5">
+      <c r="Z13" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="AA13" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5">
+      <c r="A14" s="6">
         <v>13.0</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D14" s="4"/>
+      <c r="B14" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C14" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.986666666666667)</f>
+        <v>3.986666667</v>
+      </c>
+      <c r="D14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E14" s="3">
-        <v>46268.0</v>
-      </c>
-      <c r="F14" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="F14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
       <c r="G14" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>46145.0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>46085.0</v>
-      </c>
-      <c r="J14" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
+      <c r="H14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
+      <c r="I14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="J14" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
@@ -6039,38 +7380,52 @@
       <c r="W14" s="4"/>
       <c r="X14" s="4"/>
       <c r="Y14" s="4"/>
-      <c r="Z14" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="AA14" s="5">
+      <c r="Z14" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="AA14" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5">
+      <c r="A15" s="6">
         <v>14.0</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>226</v>
+      <c r="B15" s="6" t="s">
+        <v>217</v>
       </c>
       <c r="C15" s="3">
-        <v>46025.0</v>
-      </c>
-      <c r="D15" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1133333333333333)</f>
+        <v>3.113333333</v>
+      </c>
+      <c r="D15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E15" s="3">
-        <v>46177.0</v>
-      </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>46116.0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="J15" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
+      <c r="F15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
+      <c r="G15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
+      </c>
+      <c r="I15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="J15" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -6086,38 +7441,52 @@
       <c r="W15" s="4"/>
       <c r="X15" s="4"/>
       <c r="Y15" s="4"/>
-      <c r="Z15" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="AA15" s="5">
+      <c r="Z15" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="AA15" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5">
+      <c r="A16" s="6">
         <v>15.0</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>228</v>
+      <c r="B16" s="6" t="s">
+        <v>219</v>
       </c>
       <c r="C16" s="3">
-        <v>46206.0</v>
-      </c>
-      <c r="D16" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.66)</f>
+        <v>3.66</v>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E16" s="3">
-        <v>46084.0</v>
-      </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="3">
-        <v>46269.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="F16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+      <c r="G16" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="H16" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="I16" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J16" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="J16" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -6133,38 +7502,52 @@
       <c r="W16" s="4"/>
       <c r="X16" s="4"/>
       <c r="Y16" s="4"/>
-      <c r="Z16" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="AA16" s="5">
+      <c r="Z16" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="AA16" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5">
+      <c r="A17" s="6">
         <v>16.0</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>230</v>
+      <c r="B17" s="6" t="s">
+        <v>221</v>
       </c>
       <c r="C17" s="3">
-        <v>46084.0</v>
-      </c>
-      <c r="D17" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3200000000000003)</f>
+        <v>3.32</v>
+      </c>
+      <c r="D17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E17" s="3">
-        <v>46025.0</v>
-      </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="3">
-        <v>46146.0</v>
-      </c>
-      <c r="H17" s="3">
-        <v>46238.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
+      <c r="F17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
+      <c r="G17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="H17" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="I17" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J17" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
@@ -6180,38 +7563,52 @@
       <c r="W17" s="4"/>
       <c r="X17" s="4"/>
       <c r="Y17" s="4"/>
-      <c r="Z17" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="AA17" s="5">
+      <c r="Z17" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="AA17" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5">
+      <c r="A18" s="6">
         <v>17.0</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>232</v>
+      <c r="B18" s="6" t="s">
+        <v>223</v>
       </c>
       <c r="C18" s="3">
-        <v>46237.0</v>
-      </c>
-      <c r="D18" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.78)</f>
+        <v>3.78</v>
+      </c>
+      <c r="D18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E18" s="3">
-        <v>46269.0</v>
-      </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="H18" s="3">
-        <v>46269.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
+      </c>
+      <c r="F18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
+      <c r="G18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="H18" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="I18" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J18" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="J18" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
@@ -6227,38 +7624,52 @@
       <c r="W18" s="4"/>
       <c r="X18" s="4"/>
       <c r="Y18" s="4"/>
-      <c r="Z18" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="AA18" s="5">
+      <c r="Z18" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="AA18" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5">
+      <c r="A19" s="6">
         <v>18.0</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D19" s="4"/>
+      <c r="B19" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="C19" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.33333333333333337)</f>
+        <v>0.3333333333</v>
+      </c>
+      <c r="D19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E19" s="3">
-        <v>46204.0</v>
-      </c>
-      <c r="F19" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
+        <v>1.3</v>
+      </c>
+      <c r="F19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5)</f>
+        <v>0.5</v>
+      </c>
       <c r="G19" s="1">
-        <v>0.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>5.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="I19" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="J19" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
@@ -6274,38 +7685,52 @@
       <c r="W19" s="4"/>
       <c r="X19" s="4"/>
       <c r="Y19" s="4"/>
-      <c r="Z19" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="AA19" s="5">
+      <c r="Z19" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="AA19" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5">
+      <c r="A20" s="6">
         <v>19.0</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>237</v>
+      <c r="B20" s="6" t="s">
+        <v>227</v>
       </c>
       <c r="C20" s="3">
-        <v>46114.0</v>
-      </c>
-      <c r="D20" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4266666666666667)</f>
+        <v>2.426666667</v>
+      </c>
+      <c r="D20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E20" s="3">
-        <v>46025.0</v>
-      </c>
-      <c r="F20" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
+      <c r="F20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
+      </c>
       <c r="G20" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>46177.0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="J20" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
+      <c r="I20" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="J20" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
@@ -6321,38 +7746,52 @@
       <c r="W20" s="4"/>
       <c r="X20" s="4"/>
       <c r="Y20" s="4"/>
-      <c r="Z20" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="AA20" s="5">
+      <c r="Z20" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA20" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5">
+      <c r="A21" s="6">
         <v>20.0</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>239</v>
+      <c r="B21" s="6" t="s">
+        <v>229</v>
       </c>
       <c r="C21" s="3">
-        <v>46176.0</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F21" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6066666666666665)</f>
+        <v>3.606666667</v>
+      </c>
+      <c r="D21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
+      <c r="E21" s="3">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
+      <c r="F21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="G21" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="H21" s="3">
-        <v>46026.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="I21" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="J21" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="J21" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
@@ -6368,38 +7807,52 @@
       <c r="W21" s="4"/>
       <c r="X21" s="4"/>
       <c r="Y21" s="4"/>
-      <c r="Z21" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="AA21" s="5">
+      <c r="Z21" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="AA21" s="6">
         <v>62529.0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5">
+      <c r="A22" s="6">
         <v>21.0</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>241</v>
+      <c r="B22" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="C22" s="3">
-        <v>46176.0</v>
-      </c>
-      <c r="D22" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6333333333333333)</f>
+        <v>3.633333333</v>
+      </c>
+      <c r="D22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.020000000000000004)</f>
+        <v>0.02</v>
+      </c>
       <c r="E22" s="3">
-        <v>46056.0</v>
-      </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="3">
-        <v>46207.0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
+      <c r="F22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+      <c r="G22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="H22" s="1">
-        <v>0.0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>46238.0</v>
-      </c>
-      <c r="J22" s="4"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="J22" s="4">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
+        <v>0.1</v>
+      </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
@@ -6415,10 +7868,10 @@
       <c r="W22" s="4"/>
       <c r="X22" s="4"/>
       <c r="Y22" s="4"/>
-      <c r="Z22" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="AA22" s="5">
+      <c r="Z22" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA22" s="6">
         <v>62529.0</v>
       </c>
     </row>
@@ -6447,6 +7900,18 @@
       <c r="X23" s="4"/>
       <c r="Y23" s="4"/>
     </row>
+    <row r="24">
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="7"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/app_notas.xlsx
+++ b/app_notas.xlsx
@@ -775,8 +775,8 @@
         <v>P2</v>
       </c>
       <c r="E1" s="3" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
-        <v>PQT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT1")</f>
+        <v>PQT1</v>
       </c>
       <c r="F1" s="4" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1CTE")</f>
@@ -819,8 +819,8 @@
         <v>P4</v>
       </c>
       <c r="P1" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
-        <v>PQT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT2")</f>
+        <v>PQT2</v>
       </c>
       <c r="Q1" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PA")</f>
@@ -2587,8 +2587,8 @@
         <v>P2</v>
       </c>
       <c r="E1" s="10" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
-        <v>PQT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT1")</f>
+        <v>PQT1</v>
       </c>
       <c r="F1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CN")</f>
@@ -2627,8 +2627,8 @@
         <v>P4</v>
       </c>
       <c r="O1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
-        <v>PQT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT2")</f>
+        <v>PQT2</v>
       </c>
       <c r="P1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PA")</f>
@@ -4301,8 +4301,8 @@
         <v>P2</v>
       </c>
       <c r="E1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
-        <v>PQT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT1")</f>
+        <v>PQT1</v>
       </c>
       <c r="F1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1CTE")</f>
@@ -4345,8 +4345,8 @@
         <v>P4</v>
       </c>
       <c r="P1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
-        <v>PQT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT2")</f>
+        <v>PQT2</v>
       </c>
       <c r="Q1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PA")</f>
@@ -6248,8 +6248,8 @@
         <v>P2</v>
       </c>
       <c r="E1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
-        <v>PQT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT1")</f>
+        <v>PQT1</v>
       </c>
       <c r="F1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1CTE")</f>
@@ -6284,8 +6284,8 @@
         <v>P4</v>
       </c>
       <c r="N1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
-        <v>PQT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT3")</f>
+        <v>PQT3</v>
       </c>
       <c r="O1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PA")</f>
@@ -7698,8 +7698,8 @@
         <v>P2</v>
       </c>
       <c r="E1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
-        <v>PQT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT1")</f>
+        <v>PQT1</v>
       </c>
       <c r="F1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"1CTE")</f>
@@ -7742,8 +7742,8 @@
         <v>P4</v>
       </c>
       <c r="P1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT")</f>
-        <v>PQT</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT2")</f>
+        <v>PQT2</v>
       </c>
       <c r="Q1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PA")</f>

--- a/app_notas.xlsx
+++ b/app_notas.xlsx
@@ -504,6 +504,9 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
@@ -511,9 +514,6 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -750,10 +750,12 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="4.88"/>
     <col customWidth="1" min="2" max="2" width="30.88"/>
-    <col customWidth="1" min="3" max="16" width="4.88"/>
+    <col customWidth="1" min="3" max="15" width="4.88"/>
+    <col customWidth="1" min="16" max="16" width="6.0"/>
     <col customWidth="1" min="17" max="17" width="5.25"/>
-    <col customWidth="1" min="18" max="18" width="5.5"/>
-    <col customWidth="1" min="19" max="24" width="4.88"/>
+    <col customWidth="1" min="18" max="18" width="6.13"/>
+    <col customWidth="1" min="19" max="19" width="6.0"/>
+    <col customWidth="1" min="20" max="24" width="4.88"/>
     <col customWidth="1" min="25" max="25" width="6.38"/>
     <col customWidth="1" min="26" max="26" width="10.0"/>
     <col customWidth="1" min="27" max="27" width="10.13"/>
@@ -767,7 +769,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1vS2gE-mc1A6CX14zq-8uhU927dLafFRogBm_03E8occ"",""MAT2_A!C1:AA24"")"),"P1")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1vS2gE-mc1A6CX14zq-8uhU927dLafFRogBm_03E8occ"",""MAT2_A!C1:M24"")"),"P1")</f>
         <v>P1</v>
       </c>
       <c r="D1" s="2" t="str">
@@ -811,7 +813,7 @@
         <v>Ta7</v>
       </c>
       <c r="N1" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"P3")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1vS2gE-mc1A6CX14zq-8uhU927dLafFRogBm_03E8occ"",""MAT2_A!N1:AA24"")"),"P3")</f>
         <v>P3</v>
       </c>
       <c r="O1" s="7" t="str">
@@ -918,17 +920,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="N2" s="11"/>
+      <c r="N2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
+      <c r="P2" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
+      <c r="R2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
+      </c>
       <c r="S2" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
-        <v>1.3</v>
-      </c>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
+      <c r="T2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="V2" s="11"/>
       <c r="W2" s="11"/>
       <c r="X2" s="11"/>
@@ -990,17 +1007,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="N3" s="11"/>
+      <c r="N3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
+      </c>
       <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
+      <c r="P3" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
+      <c r="R3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="S3" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
-      </c>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
+      </c>
+      <c r="T3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="U3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="V3" s="11"/>
       <c r="W3" s="11"/>
       <c r="X3" s="11"/>
@@ -1062,17 +1094,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N4" s="11"/>
+      <c r="N4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
+      <c r="P4" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11">
+      <c r="R4" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
+      <c r="S4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="T4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="U4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
+      </c>
       <c r="V4" s="11"/>
       <c r="W4" s="11"/>
       <c r="X4" s="11"/>
@@ -1134,17 +1181,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="N5" s="11"/>
+      <c r="N5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
+      <c r="P5" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
       <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
-      <c r="S5" s="11">
+      <c r="R5" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
+      <c r="S5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="T5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="V5" s="11"/>
       <c r="W5" s="11"/>
       <c r="X5" s="11"/>
@@ -1206,17 +1268,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="11"/>
+      <c r="N6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
       <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
+      <c r="P6" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
+      </c>
       <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
+      <c r="R6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
       <c r="S6" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
-      </c>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
+      </c>
+      <c r="T6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="U6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
+      </c>
       <c r="V6" s="11"/>
       <c r="W6" s="11"/>
       <c r="X6" s="11"/>
@@ -1278,17 +1355,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N7" s="11"/>
+      <c r="N7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.4)</f>
+        <v>0.4</v>
+      </c>
       <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
+      <c r="P7" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
+      </c>
       <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
+      <c r="R7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="S7" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
-        <v>1.4</v>
-      </c>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
+      <c r="T7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
+      <c r="U7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
+      </c>
       <c r="V7" s="11"/>
       <c r="W7" s="11"/>
       <c r="X7" s="11"/>
@@ -1350,17 +1442,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
-      <c r="N8" s="11"/>
+      <c r="N8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
+      <c r="P8" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
+      <c r="R8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
       <c r="S8" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
-        <v>1.4</v>
-      </c>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
+      </c>
+      <c r="T8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="U8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="V8" s="11"/>
       <c r="W8" s="11"/>
       <c r="X8" s="11"/>
@@ -1422,17 +1529,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="N9" s="11"/>
+      <c r="N9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
+      <c r="P9" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
+      <c r="R9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
       <c r="S9" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
-      </c>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="T9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="U9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="V9" s="11"/>
       <c r="W9" s="11"/>
       <c r="X9" s="11"/>
@@ -1494,17 +1616,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N10" s="11"/>
+      <c r="N10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
+      <c r="P10" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
+      <c r="R10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
+        <v>1.2</v>
+      </c>
       <c r="S10" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
-      </c>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
+      <c r="T10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="V10" s="11"/>
       <c r="W10" s="11"/>
       <c r="X10" s="11"/>
@@ -1566,17 +1703,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N11" s="11"/>
+      <c r="N11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
+      </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
+      <c r="P11" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
+      </c>
       <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
+      <c r="R11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
+        <v>1.8</v>
+      </c>
       <c r="S11" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
-        <v>1.6</v>
-      </c>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="T11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="U11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
+      </c>
       <c r="V11" s="11"/>
       <c r="W11" s="11"/>
       <c r="X11" s="11"/>
@@ -1638,17 +1790,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="N12" s="11"/>
+      <c r="N12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
+      <c r="P12" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
+      <c r="R12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="S12" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
-      </c>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="T12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="U12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="V12" s="11"/>
       <c r="W12" s="11"/>
       <c r="X12" s="11"/>
@@ -1710,17 +1877,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N13" s="11"/>
+      <c r="N13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
+      <c r="P13" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
+      <c r="R13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
       <c r="S13" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
-      </c>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
+      </c>
+      <c r="T13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="U13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="V13" s="11"/>
       <c r="W13" s="11"/>
       <c r="X13" s="11"/>
@@ -1782,17 +1964,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N14" s="11"/>
+      <c r="N14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
+      <c r="P14" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
+      <c r="R14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9)</f>
+        <v>0.9</v>
+      </c>
       <c r="S14" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
+      <c r="T14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="U14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="V14" s="11"/>
       <c r="W14" s="11"/>
       <c r="X14" s="11"/>
@@ -1854,17 +2051,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N15" s="11"/>
+      <c r="N15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
+      </c>
       <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
+      <c r="P15" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
+      <c r="R15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
       <c r="S15" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
-        <v>1.6</v>
-      </c>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="T15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="U15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="V15" s="11"/>
       <c r="W15" s="11"/>
       <c r="X15" s="11"/>
@@ -1926,17 +2138,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="N16" s="11"/>
+      <c r="N16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
+      <c r="P16" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
+      <c r="R16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="S16" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
         <v>2.1</v>
       </c>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
+      <c r="T16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="U16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="V16" s="11"/>
       <c r="W16" s="11"/>
       <c r="X16" s="11"/>
@@ -1998,17 +2225,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N17" s="11"/>
+      <c r="N17" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
+      <c r="P17" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
+      <c r="R17" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
       <c r="S17" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
-      </c>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
+      </c>
+      <c r="T17" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U17" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="V17" s="11"/>
       <c r="W17" s="11"/>
       <c r="X17" s="11"/>
@@ -2070,17 +2312,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N18" s="11"/>
+      <c r="N18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
+      <c r="P18" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
+      <c r="R18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1)</f>
+        <v>1.1</v>
+      </c>
       <c r="S18" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
-      </c>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
+      </c>
+      <c r="T18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="U18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="V18" s="11"/>
       <c r="W18" s="11"/>
       <c r="X18" s="11"/>
@@ -2142,17 +2399,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N19" s="11"/>
+      <c r="N19" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
+      <c r="P19" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
+      </c>
       <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="11">
+      <c r="R19" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
         <v>1.7</v>
       </c>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
+      <c r="S19" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
+      </c>
+      <c r="T19" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
+      <c r="U19" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
       <c r="V19" s="11"/>
       <c r="W19" s="11"/>
       <c r="X19" s="11"/>
@@ -2214,17 +2486,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N20" s="11"/>
+      <c r="N20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
+      <c r="P20" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
+      <c r="R20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9)</f>
+        <v>0.9</v>
+      </c>
       <c r="S20" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="T20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="U20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="V20" s="11"/>
       <c r="W20" s="11"/>
       <c r="X20" s="11"/>
@@ -2286,17 +2573,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N21" s="11"/>
+      <c r="N21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
+      <c r="P21" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="Q21" s="11"/>
-      <c r="R21" s="11"/>
+      <c r="R21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
       <c r="S21" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
-      </c>
-      <c r="T21" s="11"/>
-      <c r="U21" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
+      </c>
+      <c r="T21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="U21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
       <c r="V21" s="11"/>
       <c r="W21" s="11"/>
       <c r="X21" s="11"/>
@@ -2358,17 +2660,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N22" s="11"/>
+      <c r="N22" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
+      <c r="P22" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="Q22" s="11"/>
-      <c r="R22" s="11"/>
+      <c r="R22" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="S22" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
-      </c>
-      <c r="T22" s="11"/>
-      <c r="U22" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
+      </c>
+      <c r="T22" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="U22" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="V22" s="11"/>
       <c r="W22" s="11"/>
       <c r="X22" s="11"/>
@@ -2430,17 +2747,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N23" s="11"/>
+      <c r="N23" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
       <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
+      <c r="P23" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="Q23" s="11"/>
-      <c r="R23" s="11"/>
+      <c r="R23" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="S23" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
-      </c>
-      <c r="T23" s="11"/>
-      <c r="U23" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
+      </c>
+      <c r="T23" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="U23" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="V23" s="11"/>
       <c r="W23" s="11"/>
       <c r="X23" s="11"/>
@@ -2502,17 +2834,32 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N24" s="11"/>
+      <c r="N24" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
+      <c r="P24" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="Q24" s="11"/>
-      <c r="R24" s="11"/>
+      <c r="R24" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
+        <v>1.3</v>
+      </c>
       <c r="S24" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="T24" s="11"/>
-      <c r="U24" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
+      </c>
+      <c r="T24" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="U24" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="V24" s="11"/>
       <c r="W24" s="11"/>
       <c r="X24" s="11"/>
@@ -2524,29 +2871,29 @@
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="12"/>
-      <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="12"/>
-      <c r="N25" s="12"/>
-      <c r="O25" s="12"/>
-      <c r="P25" s="12"/>
-      <c r="Q25" s="12"/>
-      <c r="R25" s="12"/>
-      <c r="S25" s="12"/>
-      <c r="T25" s="12"/>
-      <c r="U25" s="12"/>
-      <c r="V25" s="12"/>
-      <c r="W25" s="12"/>
-      <c r="X25" s="12"/>
-      <c r="Y25" s="12"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="13"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="13"/>
+      <c r="R25" s="13"/>
+      <c r="S25" s="13"/>
+      <c r="T25" s="13"/>
+      <c r="U25" s="13"/>
+      <c r="V25" s="13"/>
+      <c r="W25" s="13"/>
+      <c r="X25" s="13"/>
+      <c r="Y25" s="13"/>
     </row>
   </sheetData>
   <drawing r:id="rId2"/>
@@ -2572,10 +2919,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="str">
@@ -2670,20 +3017,20 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ID")</f>
         <v>ID</v>
       </c>
-      <c r="Z1" s="14" t="str">
+      <c r="Z1" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NRC")</f>
         <v>NRC</v>
       </c>
-      <c r="AA1" s="14" t="str">
+      <c r="AA1" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"P1")</f>
         <v>P1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <v>1.0</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>25</v>
       </c>
       <c r="C2" s="10">
@@ -2723,39 +3070,60 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M2" s="11"/>
+      <c r="M2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N2" s="11"/>
-      <c r="O2" s="11"/>
+      <c r="O2" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
       <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
+      <c r="Q2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
+      </c>
       <c r="R2" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
+      </c>
+      <c r="S2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
+      <c r="U2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="V2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W2" s="11"/>
       <c r="X2" s="11"/>
       <c r="Y2" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00194619")</f>
         <v>U00194619</v>
       </c>
-      <c r="Z2" s="14">
+      <c r="Z2" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA2" s="14">
+      <c r="AA2" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13">
+      <c r="A3" s="14">
         <v>2.0</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>26</v>
       </c>
       <c r="C3" s="10">
@@ -2795,39 +3163,60 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M3" s="11"/>
+      <c r="M3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N3" s="11"/>
-      <c r="O3" s="11"/>
+      <c r="O3" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
       <c r="P3" s="11"/>
-      <c r="Q3" s="11"/>
+      <c r="Q3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
       <c r="R3" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
-        <v>0.8</v>
-      </c>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
+      </c>
+      <c r="S3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="T3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="V3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W3" s="11"/>
       <c r="X3" s="11"/>
       <c r="Y3" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00193956")</f>
         <v>U00193956</v>
       </c>
-      <c r="Z3" s="14">
+      <c r="Z3" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA3" s="14">
+      <c r="AA3" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13">
+      <c r="A4" s="14">
         <v>3.0</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="10">
@@ -2870,39 +3259,60 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="M4" s="11"/>
+      <c r="M4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
+      <c r="O4" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
+      <c r="Q4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
       <c r="R4" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
-        <v>1.4</v>
-      </c>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
+      <c r="S4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
+      <c r="U4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="V4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W4" s="11"/>
       <c r="X4" s="11"/>
       <c r="Y4" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00194124")</f>
         <v>U00194124</v>
       </c>
-      <c r="Z4" s="14">
+      <c r="Z4" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA4" s="14">
+      <c r="AA4" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13">
+      <c r="A5" s="14">
         <v>4.0</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>28</v>
       </c>
       <c r="C5" s="10">
@@ -2942,39 +3352,60 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M5" s="11"/>
+      <c r="M5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N5" s="11"/>
-      <c r="O5" s="11"/>
+      <c r="O5" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
       <c r="P5" s="11"/>
-      <c r="Q5" s="11"/>
+      <c r="Q5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
+      </c>
       <c r="R5" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
-      </c>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
+      </c>
+      <c r="S5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="U5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
+      <c r="V5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W5" s="11"/>
       <c r="X5" s="11"/>
       <c r="Y5" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00191934")</f>
         <v>U00191934</v>
       </c>
-      <c r="Z5" s="14">
+      <c r="Z5" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA5" s="14">
+      <c r="AA5" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <v>5.0</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>29</v>
       </c>
       <c r="C6" s="10">
@@ -3017,39 +3448,60 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="M6" s="11"/>
+      <c r="M6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N6" s="11"/>
-      <c r="O6" s="11"/>
+      <c r="O6" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
       <c r="P6" s="11"/>
-      <c r="Q6" s="11"/>
+      <c r="Q6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
       <c r="R6" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
-      </c>
-      <c r="S6" s="11"/>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
+      </c>
+      <c r="S6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="U6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="V6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W6" s="11"/>
       <c r="X6" s="11"/>
       <c r="Y6" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00193915")</f>
         <v>U00193915</v>
       </c>
-      <c r="Z6" s="14">
+      <c r="Z6" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA6" s="14">
+      <c r="AA6" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13">
+      <c r="A7" s="14">
         <v>6.0</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>30</v>
       </c>
       <c r="C7" s="10">
@@ -3092,39 +3544,60 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M7" s="11"/>
+      <c r="M7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N7" s="11"/>
-      <c r="O7" s="11"/>
+      <c r="O7" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="P7" s="11"/>
-      <c r="Q7" s="11"/>
+      <c r="Q7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
+        <v>1.8</v>
+      </c>
       <c r="R7" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
-      </c>
-      <c r="S7" s="11"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
-      <c r="V7" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
+      </c>
+      <c r="S7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="T7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
+      <c r="U7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="V7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W7" s="11"/>
       <c r="X7" s="11"/>
       <c r="Y7" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00193113")</f>
         <v>U00193113</v>
       </c>
-      <c r="Z7" s="14">
+      <c r="Z7" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA7" s="14">
+      <c r="AA7" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13">
+      <c r="A8" s="14">
         <v>7.0</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="10">
@@ -3167,39 +3640,60 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M8" s="11"/>
+      <c r="M8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N8" s="11"/>
-      <c r="O8" s="11"/>
+      <c r="O8" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
+      </c>
       <c r="P8" s="11"/>
-      <c r="Q8" s="11"/>
-      <c r="R8" s="11">
+      <c r="Q8" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
         <v>1.8</v>
       </c>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="11"/>
+      <c r="R8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
+      </c>
+      <c r="S8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
+      <c r="T8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
+      <c r="U8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="V8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W8" s="11"/>
       <c r="X8" s="11"/>
       <c r="Y8" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00192477")</f>
         <v>U00192477</v>
       </c>
-      <c r="Z8" s="14">
+      <c r="Z8" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA8" s="14">
+      <c r="AA8" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13">
+      <c r="A9" s="14">
         <v>8.0</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="10">
@@ -3242,39 +3736,60 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="M9" s="11"/>
+      <c r="M9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N9" s="11"/>
-      <c r="O9" s="11"/>
+      <c r="O9" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P9" s="11"/>
-      <c r="Q9" s="11"/>
+      <c r="Q9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
       <c r="R9" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
-      </c>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
+      </c>
+      <c r="S9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="V9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W9" s="11"/>
       <c r="X9" s="11"/>
       <c r="Y9" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00192526")</f>
         <v>U00192526</v>
       </c>
-      <c r="Z9" s="14">
+      <c r="Z9" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA9" s="14">
+      <c r="AA9" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <v>9.0</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>33</v>
       </c>
       <c r="C10" s="10">
@@ -3317,39 +3832,60 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M10" s="11"/>
+      <c r="M10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N10" s="11"/>
-      <c r="O10" s="11"/>
+      <c r="O10" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P10" s="11"/>
-      <c r="Q10" s="11"/>
+      <c r="Q10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
       <c r="R10" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
-      </c>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
+      </c>
+      <c r="S10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="V10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W10" s="11"/>
       <c r="X10" s="11"/>
       <c r="Y10" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00193149")</f>
         <v>U00193149</v>
       </c>
-      <c r="Z10" s="14">
+      <c r="Z10" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA10" s="14">
+      <c r="AA10" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13">
+      <c r="A11" s="14">
         <v>10.0</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>34</v>
       </c>
       <c r="C11" s="10">
@@ -3392,39 +3928,60 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M11" s="11"/>
+      <c r="M11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
+      <c r="O11" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="P11" s="11"/>
-      <c r="Q11" s="11"/>
-      <c r="R11" s="11">
+      <c r="Q11" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
         <v>1.9</v>
       </c>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="11"/>
+      <c r="R11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
+      </c>
+      <c r="S11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="T11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="U11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="V11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W11" s="11"/>
       <c r="X11" s="11"/>
       <c r="Y11" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00192726")</f>
         <v>U00192726</v>
       </c>
-      <c r="Z11" s="14">
+      <c r="Z11" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA11" s="14">
+      <c r="AA11" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
         <v>2.6</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <v>11.0</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>35</v>
       </c>
       <c r="C12" s="10">
@@ -3464,39 +4021,60 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="M12" s="11"/>
+      <c r="M12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
+      <c r="O12" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
       <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
+      <c r="Q12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
       <c r="R12" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
-      </c>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
+      </c>
+      <c r="S12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="T12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="V12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W12" s="11"/>
       <c r="X12" s="11"/>
       <c r="Y12" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00194037")</f>
         <v>U00194037</v>
       </c>
-      <c r="Z12" s="14">
+      <c r="Z12" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA12" s="14">
+      <c r="AA12" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13">
+      <c r="A13" s="14">
         <v>12.0</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>36</v>
       </c>
       <c r="C13" s="10">
@@ -3539,39 +4117,60 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="M13" s="11"/>
+      <c r="M13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
+      <c r="O13" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
       <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
+      <c r="Q13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
+      </c>
       <c r="R13" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
-      </c>
-      <c r="S13" s="11"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
+      </c>
+      <c r="S13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="U13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
+      <c r="V13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W13" s="11"/>
       <c r="X13" s="11"/>
       <c r="Y13" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00192705")</f>
         <v>U00192705</v>
       </c>
-      <c r="Z13" s="14">
+      <c r="Z13" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA13" s="14">
+      <c r="AA13" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13">
+      <c r="A14" s="14">
         <v>13.0</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>37</v>
       </c>
       <c r="C14" s="10">
@@ -3614,39 +4213,60 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M14" s="11"/>
+      <c r="M14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N14" s="11"/>
-      <c r="O14" s="11"/>
+      <c r="O14" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="P14" s="11"/>
-      <c r="Q14" s="11"/>
+      <c r="Q14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
+        <v>1.8</v>
+      </c>
       <c r="R14" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
-      </c>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
+      </c>
+      <c r="S14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="T14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
+      <c r="U14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="V14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W14" s="11"/>
       <c r="X14" s="11"/>
       <c r="Y14" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00193858")</f>
         <v>U00193858</v>
       </c>
-      <c r="Z14" s="14">
+      <c r="Z14" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA14" s="14">
+      <c r="AA14" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13">
+      <c r="A15" s="14">
         <v>14.0</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>38</v>
       </c>
       <c r="C15" s="10">
@@ -3689,39 +4309,60 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="M15" s="11"/>
+      <c r="M15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
+      <c r="O15" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
       <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
+      <c r="Q15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
+      </c>
       <c r="R15" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
-      </c>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
+      </c>
+      <c r="S15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="T15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="V15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W15" s="11"/>
       <c r="X15" s="11"/>
       <c r="Y15" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00192059")</f>
         <v>U00192059</v>
       </c>
-      <c r="Z15" s="14">
+      <c r="Z15" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA15" s="14">
+      <c r="AA15" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
         <v>2.6</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13">
+      <c r="A16" s="14">
         <v>15.0</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>39</v>
       </c>
       <c r="C16" s="10">
@@ -3761,39 +4402,60 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M16" s="11"/>
+      <c r="M16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
+      <c r="O16" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
       <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
+      <c r="Q16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
       <c r="R16" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
-      </c>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="S16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="T16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="V16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W16" s="11"/>
       <c r="X16" s="11"/>
       <c r="Y16" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00192970")</f>
         <v>U00192970</v>
       </c>
-      <c r="Z16" s="14">
+      <c r="Z16" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA16" s="14">
+      <c r="AA16" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13">
+      <c r="A17" s="14">
         <v>16.0</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="14" t="s">
         <v>40</v>
       </c>
       <c r="C17" s="10">
@@ -3838,10 +4500,7 @@
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
       <c r="Q17" s="11"/>
-      <c r="R17" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6)</f>
-        <v>0.6</v>
-      </c>
+      <c r="R17" s="11"/>
       <c r="S17" s="11"/>
       <c r="T17" s="11"/>
       <c r="U17" s="11"/>
@@ -3852,20 +4511,20 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00193142")</f>
         <v>U00193142</v>
       </c>
-      <c r="Z17" s="14">
+      <c r="Z17" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA17" s="14">
+      <c r="AA17" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
         <v>1.6</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13">
+      <c r="A18" s="14">
         <v>17.0</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="14" t="s">
         <v>41</v>
       </c>
       <c r="C18" s="10">
@@ -3905,39 +4564,60 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="M18" s="11"/>
+      <c r="M18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
+      <c r="O18" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
       <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
+      <c r="Q18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
+      </c>
       <c r="R18" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
-        <v>1.3</v>
-      </c>
-      <c r="S18" s="11"/>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
+      <c r="S18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="T18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="V18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W18" s="11"/>
       <c r="X18" s="11"/>
       <c r="Y18" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00186645")</f>
         <v>U00186645</v>
       </c>
-      <c r="Z18" s="14">
+      <c r="Z18" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA18" s="14">
+      <c r="AA18" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13">
+      <c r="A19" s="14">
         <v>18.0</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="14" t="s">
         <v>42</v>
       </c>
       <c r="C19" s="10">
@@ -3980,39 +4660,60 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M19" s="11"/>
+      <c r="M19" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
+      <c r="O19" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
+      <c r="Q19" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
       <c r="R19" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
-      </c>
-      <c r="S19" s="11"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
+      </c>
+      <c r="S19" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T19" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U19" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="V19" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W19" s="11"/>
       <c r="X19" s="11"/>
       <c r="Y19" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00191929")</f>
         <v>U00191929</v>
       </c>
-      <c r="Z19" s="14">
+      <c r="Z19" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA19" s="14">
+      <c r="AA19" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13">
+      <c r="A20" s="14">
         <v>19.0</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="14" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="10">
@@ -4055,39 +4756,60 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="M20" s="11"/>
+      <c r="M20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
+      <c r="O20" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
+      <c r="Q20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
       <c r="R20" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
-      </c>
-      <c r="S20" s="11"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="S20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
+      <c r="U20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="V20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W20" s="11"/>
       <c r="X20" s="11"/>
       <c r="Y20" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00194227")</f>
         <v>U00194227</v>
       </c>
-      <c r="Z20" s="14">
+      <c r="Z20" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA20" s="14">
+      <c r="AA20" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
         <v>3.4</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13">
+      <c r="A21" s="14">
         <v>20.0</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="14" t="s">
         <v>44</v>
       </c>
       <c r="C21" s="10">
@@ -4127,144 +4849,189 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M21" s="11"/>
+      <c r="M21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N21" s="11"/>
-      <c r="O21" s="11"/>
+      <c r="O21" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="P21" s="11"/>
-      <c r="Q21" s="11"/>
+      <c r="Q21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
       <c r="R21" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
-      </c>
-      <c r="S21" s="11"/>
-      <c r="T21" s="11"/>
-      <c r="U21" s="11"/>
-      <c r="V21" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
+      </c>
+      <c r="S21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
+      <c r="U21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="V21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W21" s="11"/>
       <c r="X21" s="11"/>
       <c r="Y21" s="11" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00194368")</f>
         <v>U00194368</v>
       </c>
-      <c r="Z21" s="14">
+      <c r="Z21" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),55581.0)</f>
         <v>55581</v>
       </c>
-      <c r="AA21" s="14">
+      <c r="AA21" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="15">
+      <c r="C22" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.585)</f>
         <v>3.585</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.59)</f>
         <v>3.59</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.814999999999999)</f>
         <v>3.815</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.233333333333333)</f>
         <v>4.233333333</v>
       </c>
-      <c r="G22" s="15">
+      <c r="G22" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7050000000000005)</f>
         <v>3.705</v>
       </c>
-      <c r="H22" s="15">
+      <c r="H22" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1949999999999985)</f>
         <v>4.195</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I22" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5550000000000006)</f>
         <v>3.555</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9899999999999998)</f>
         <v>3.99</v>
       </c>
-      <c r="K22" s="15">
+      <c r="K22" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7299999999999995)</f>
         <v>3.73</v>
       </c>
-      <c r="L22" s="15">
+      <c r="L22" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.575)</f>
         <v>3.575</v>
       </c>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
-      <c r="R22" s="12"/>
-      <c r="S22" s="12"/>
-      <c r="T22" s="12"/>
-      <c r="U22" s="12"/>
-      <c r="V22" s="12"/>
-      <c r="W22" s="12"/>
-      <c r="X22" s="12"/>
-      <c r="Y22" s="12"/>
-      <c r="Z22" s="14"/>
-      <c r="AA22" s="14"/>
+      <c r="M22" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="N22" s="13"/>
+      <c r="O22" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5894736842105255)</f>
+        <v>4.589473684</v>
+      </c>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.826315789473684)</f>
+        <v>1.826315789</v>
+      </c>
+      <c r="R22" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
+      </c>
+      <c r="S22" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2631578947368425)</f>
+        <v>4.263157895</v>
+      </c>
+      <c r="T22" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.405263157894737)</f>
+        <v>4.405263158</v>
+      </c>
+      <c r="U22" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.610526315789474)</f>
+        <v>4.610526316</v>
+      </c>
+      <c r="V22" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="W22" s="13"/>
+      <c r="X22" s="13"/>
+      <c r="Y22" s="13"/>
+      <c r="Z22" s="15"/>
+      <c r="AA22" s="15"/>
     </row>
     <row r="23">
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="14"/>
-      <c r="R23" s="14"/>
-      <c r="S23" s="14"/>
-      <c r="T23" s="14"/>
-      <c r="U23" s="14"/>
-      <c r="V23" s="14"/>
-      <c r="W23" s="14"/>
-      <c r="X23" s="14"/>
-      <c r="Y23" s="14"/>
-      <c r="Z23" s="14"/>
-      <c r="AA23" s="14"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="15"/>
+      <c r="R23" s="15"/>
+      <c r="S23" s="15"/>
+      <c r="T23" s="15"/>
+      <c r="U23" s="15"/>
+      <c r="V23" s="15"/>
+      <c r="W23" s="15"/>
+      <c r="X23" s="15"/>
+      <c r="Y23" s="15"/>
+      <c r="Z23" s="15"/>
+      <c r="AA23" s="15"/>
     </row>
     <row r="24">
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="14"/>
-      <c r="X24" s="14"/>
-      <c r="Y24" s="14"/>
-      <c r="Z24" s="14"/>
-      <c r="AA24" s="14"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="15"/>
+      <c r="R24" s="15"/>
+      <c r="S24" s="15"/>
+      <c r="T24" s="15"/>
+      <c r="U24" s="15"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="15"/>
+      <c r="Y24" s="15"/>
+      <c r="Z24" s="15"/>
+      <c r="AA24" s="15"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -4286,10 +5053,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="str">
@@ -4384,20 +5151,20 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta13")</f>
         <v>Ta13</v>
       </c>
-      <c r="Z1" s="14" t="str">
+      <c r="Z1" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta14")</f>
         <v>Ta14</v>
       </c>
-      <c r="AA1" s="14" t="str">
+      <c r="AA1" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ID")</f>
         <v>ID</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <v>1.0</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>45</v>
       </c>
       <c r="C2" s="10">
@@ -4444,32 +5211,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N2" s="11"/>
+      <c r="N2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
+      </c>
       <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
+      <c r="P2" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
+      </c>
       <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
+      <c r="R2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
+        <v>1.3</v>
+      </c>
       <c r="S2" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
-        <v>1.4</v>
-      </c>
-      <c r="T2" s="11"/>
-      <c r="U2" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+      <c r="T2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
+      </c>
+      <c r="U2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="V2" s="11"/>
       <c r="W2" s="11"/>
       <c r="X2" s="11"/>
       <c r="Y2" s="11"/>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="14" t="str">
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00186151")</f>
         <v>U00186151</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13">
+      <c r="A3" s="14">
         <v>2.0</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>46</v>
       </c>
       <c r="C3" s="10">
@@ -4516,32 +5298,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N3" s="11"/>
+      <c r="N3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
+      <c r="P3" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
       <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
+      <c r="R3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
+      </c>
       <c r="S3" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
-      </c>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="T3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="U3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="V3" s="11"/>
       <c r="W3" s="11"/>
       <c r="X3" s="11"/>
       <c r="Y3" s="11"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14" t="str">
+      <c r="Z3" s="15"/>
+      <c r="AA3" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00190844")</f>
         <v>U00190844</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13">
+      <c r="A4" s="14">
         <v>3.0</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>47</v>
       </c>
       <c r="C4" s="10">
@@ -4588,32 +5385,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N4" s="11"/>
+      <c r="N4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5)</f>
+        <v>0.5</v>
+      </c>
       <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
+      <c r="P4" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
+      <c r="R4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1)</f>
+        <v>1.1</v>
+      </c>
       <c r="S4" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="T4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="V4" s="11"/>
       <c r="W4" s="11"/>
       <c r="X4" s="11"/>
       <c r="Y4" s="11"/>
-      <c r="Z4" s="14"/>
-      <c r="AA4" s="14" t="str">
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00189302")</f>
         <v>U00189302</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13">
+      <c r="A5" s="14">
         <v>4.0</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>48</v>
       </c>
       <c r="C5" s="10">
@@ -4660,37 +5472,52 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N5" s="11"/>
+      <c r="N5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
+      <c r="P5" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
+      <c r="R5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="S5" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
-      </c>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
+      </c>
+      <c r="T5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="V5" s="11"/>
       <c r="W5" s="11"/>
       <c r="X5" s="11"/>
       <c r="Y5" s="11"/>
-      <c r="Z5" s="14"/>
-      <c r="AA5" s="14" t="str">
+      <c r="Z5" s="15"/>
+      <c r="AA5" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00189715")</f>
         <v>U00189715</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <v>5.0</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>49</v>
       </c>
       <c r="C6" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
-        <v>0.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="D6" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -4701,15 +5528,21 @@
         <v>1.6</v>
       </c>
       <c r="F6" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="G6" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.1)</f>
-        <v>0.1</v>
-      </c>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="J6" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
@@ -4726,32 +5559,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N6" s="11"/>
+      <c r="N6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
+      <c r="P6" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="Q6" s="11"/>
-      <c r="R6" s="11"/>
+      <c r="R6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.3)</f>
+        <v>0.3</v>
+      </c>
       <c r="S6" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
-        <v>0.8</v>
-      </c>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
+        <v>1.8</v>
+      </c>
+      <c r="T6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="U6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="V6" s="11"/>
       <c r="W6" s="11"/>
       <c r="X6" s="11"/>
       <c r="Y6" s="11"/>
-      <c r="Z6" s="14"/>
-      <c r="AA6" s="14" t="str">
+      <c r="Z6" s="15"/>
+      <c r="AA6" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00187449")</f>
         <v>U00187449</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13">
+      <c r="A7" s="14">
         <v>6.0</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>50</v>
       </c>
       <c r="C7" s="10">
@@ -4798,32 +5646,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N7" s="11"/>
+      <c r="N7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
+      <c r="P7" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
       <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
+      <c r="R7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
+      </c>
       <c r="S7" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
-      </c>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
+      </c>
+      <c r="T7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="U7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="V7" s="11"/>
       <c r="W7" s="11"/>
       <c r="X7" s="11"/>
       <c r="Y7" s="11"/>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="14" t="str">
+      <c r="Z7" s="15"/>
+      <c r="AA7" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00190475")</f>
         <v>U00190475</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13">
+      <c r="A8" s="14">
         <v>7.0</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>51</v>
       </c>
       <c r="C8" s="10">
@@ -4870,32 +5733,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N8" s="11"/>
+      <c r="N8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
+      <c r="P8" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
+      <c r="R8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
       <c r="S8" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
-      </c>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
+      </c>
+      <c r="T8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="U8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="V8" s="11"/>
       <c r="W8" s="11"/>
       <c r="X8" s="11"/>
       <c r="Y8" s="11"/>
-      <c r="Z8" s="14"/>
-      <c r="AA8" s="14" t="str">
+      <c r="Z8" s="15"/>
+      <c r="AA8" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00190980")</f>
         <v>U00190980</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13">
+      <c r="A9" s="14">
         <v>8.0</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>52</v>
       </c>
       <c r="C9" s="10">
@@ -4942,32 +5820,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N9" s="11"/>
+      <c r="N9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
+      <c r="P9" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11">
+      <c r="R9" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
       </c>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+      <c r="S9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
+      </c>
+      <c r="T9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="V9" s="11"/>
       <c r="W9" s="11"/>
       <c r="X9" s="11"/>
       <c r="Y9" s="11"/>
-      <c r="Z9" s="14"/>
-      <c r="AA9" s="14" t="str">
+      <c r="Z9" s="15"/>
+      <c r="AA9" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00188393")</f>
         <v>U00188393</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <v>9.0</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>53</v>
       </c>
       <c r="C10" s="10">
@@ -5014,32 +5907,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N10" s="11"/>
+      <c r="N10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
+      </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
+      <c r="P10" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
+      <c r="R10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
       <c r="S10" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
-      </c>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
+        <v>3.1</v>
+      </c>
+      <c r="T10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="V10" s="11"/>
       <c r="W10" s="11"/>
       <c r="X10" s="11"/>
       <c r="Y10" s="11"/>
-      <c r="Z10" s="14"/>
-      <c r="AA10" s="14" t="str">
+      <c r="Z10" s="15"/>
+      <c r="AA10" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00190951")</f>
         <v>U00190951</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13">
+      <c r="A11" s="14">
         <v>10.0</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>54</v>
       </c>
       <c r="C11" s="10">
@@ -5086,32 +5994,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N11" s="11"/>
+      <c r="N11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
+      <c r="P11" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
+      <c r="R11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
+      </c>
       <c r="S11" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
-      </c>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
+      </c>
+      <c r="T11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
       <c r="V11" s="11"/>
       <c r="W11" s="11"/>
       <c r="X11" s="11"/>
       <c r="Y11" s="11"/>
-      <c r="Z11" s="14"/>
-      <c r="AA11" s="14" t="str">
+      <c r="Z11" s="15"/>
+      <c r="AA11" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00190971")</f>
         <v>U00190971</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <v>11.0</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>55</v>
       </c>
       <c r="C12" s="10">
@@ -5158,32 +6081,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N12" s="11"/>
+      <c r="N12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
+      <c r="P12" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
       <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
+      <c r="R12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
       <c r="S12" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
-      </c>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
+      </c>
+      <c r="T12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="U12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
       <c r="V12" s="11"/>
       <c r="W12" s="11"/>
       <c r="X12" s="11"/>
       <c r="Y12" s="11"/>
-      <c r="Z12" s="14"/>
-      <c r="AA12" s="14" t="str">
+      <c r="Z12" s="15"/>
+      <c r="AA12" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00190952")</f>
         <v>U00190952</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13">
+      <c r="A13" s="14">
         <v>12.0</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>56</v>
       </c>
       <c r="C13" s="10">
@@ -5230,32 +6168,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="N13" s="11"/>
+      <c r="N13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
+      <c r="P13" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11">
+      <c r="R13" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+      <c r="S13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="T13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
+      </c>
       <c r="V13" s="11"/>
       <c r="W13" s="11"/>
       <c r="X13" s="11"/>
       <c r="Y13" s="11"/>
-      <c r="Z13" s="14"/>
-      <c r="AA13" s="14" t="str">
+      <c r="Z13" s="15"/>
+      <c r="AA13" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00189506")</f>
         <v>U00189506</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13">
+      <c r="A14" s="14">
         <v>13.0</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>57</v>
       </c>
       <c r="C14" s="10">
@@ -5302,32 +6255,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
       </c>
-      <c r="N14" s="11"/>
+      <c r="N14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
+      <c r="P14" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
+      <c r="R14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="S14" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6)</f>
         <v>0.6</v>
       </c>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+      <c r="T14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="U14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="V14" s="11"/>
       <c r="W14" s="11"/>
       <c r="X14" s="11"/>
       <c r="Y14" s="11"/>
-      <c r="Z14" s="14"/>
-      <c r="AA14" s="14" t="str">
+      <c r="Z14" s="15"/>
+      <c r="AA14" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00190855")</f>
         <v>U00190855</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13">
+      <c r="A15" s="14">
         <v>14.0</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>58</v>
       </c>
       <c r="C15" s="10">
@@ -5374,32 +6342,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N15" s="11"/>
+      <c r="N15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
+      <c r="P15" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
+      <c r="R15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
       <c r="S15" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
-      </c>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
+        <v>3.1</v>
+      </c>
+      <c r="T15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="U15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="V15" s="11"/>
       <c r="W15" s="11"/>
       <c r="X15" s="11"/>
       <c r="Y15" s="11"/>
-      <c r="Z15" s="14"/>
-      <c r="AA15" s="14" t="str">
+      <c r="Z15" s="15"/>
+      <c r="AA15" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00188572")</f>
         <v>U00188572</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13">
+      <c r="A16" s="14">
         <v>15.0</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>59</v>
       </c>
       <c r="C16" s="10">
@@ -5446,32 +6429,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="N16" s="11"/>
+      <c r="N16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
+      <c r="P16" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
+      <c r="R16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
+        <v>1.8</v>
+      </c>
       <c r="S16" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
-      </c>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
+      </c>
+      <c r="T16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="U16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="V16" s="11"/>
       <c r="W16" s="11"/>
       <c r="X16" s="11"/>
       <c r="Y16" s="11"/>
-      <c r="Z16" s="14"/>
-      <c r="AA16" s="14" t="str">
+      <c r="Z16" s="15"/>
+      <c r="AA16" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00190921")</f>
         <v>U00190921</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13">
+      <c r="A17" s="14">
         <v>16.0</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="14" t="s">
         <v>60</v>
       </c>
       <c r="C17" s="10">
@@ -5518,32 +6516,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="N17" s="11"/>
+      <c r="N17" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
+      <c r="P17" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
+      </c>
       <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
+      <c r="R17" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
       <c r="S17" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
+        <v>3.1</v>
+      </c>
+      <c r="T17" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
+      <c r="U17" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="V17" s="11"/>
       <c r="W17" s="11"/>
       <c r="X17" s="11"/>
       <c r="Y17" s="11"/>
-      <c r="Z17" s="14"/>
-      <c r="AA17" s="14" t="str">
+      <c r="Z17" s="15"/>
+      <c r="AA17" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00190037")</f>
         <v>U00190037</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13">
+      <c r="A18" s="14">
         <v>17.0</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="14" t="s">
         <v>61</v>
       </c>
       <c r="C18" s="10">
@@ -5590,32 +6603,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N18" s="11"/>
+      <c r="N18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
+      <c r="P18" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
+      <c r="R18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
       <c r="S18" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
-      </c>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
+      </c>
+      <c r="T18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="U18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="V18" s="11"/>
       <c r="W18" s="11"/>
       <c r="X18" s="11"/>
       <c r="Y18" s="11"/>
-      <c r="Z18" s="14"/>
-      <c r="AA18" s="14" t="str">
+      <c r="Z18" s="15"/>
+      <c r="AA18" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00190913")</f>
         <v>U00190913</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13">
+      <c r="A19" s="14">
         <v>18.0</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="14" t="s">
         <v>62</v>
       </c>
       <c r="C19" s="10">
@@ -5662,32 +6690,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N19" s="11"/>
+      <c r="N19" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
+      <c r="P19" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
+      <c r="R19" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="S19" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.6)</f>
         <v>0.6</v>
       </c>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
+      <c r="T19" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="U19" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="V19" s="11"/>
       <c r="W19" s="11"/>
       <c r="X19" s="11"/>
       <c r="Y19" s="11"/>
-      <c r="Z19" s="14"/>
-      <c r="AA19" s="14" t="str">
+      <c r="Z19" s="15"/>
+      <c r="AA19" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00189207")</f>
         <v>U00189207</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13">
+      <c r="A20" s="14">
         <v>19.0</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="14" t="s">
         <v>63</v>
       </c>
       <c r="C20" s="10">
@@ -5734,32 +6777,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N20" s="11"/>
+      <c r="N20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.2)</f>
+        <v>0.2</v>
+      </c>
       <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="11">
+      <c r="P20" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
         <v>2.3</v>
       </c>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
+      <c r="Q20" s="11"/>
+      <c r="R20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5)</f>
+        <v>0.5</v>
+      </c>
+      <c r="S20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="T20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="U20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="V20" s="11"/>
       <c r="W20" s="11"/>
       <c r="X20" s="11"/>
       <c r="Y20" s="11"/>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14" t="str">
+      <c r="Z20" s="15"/>
+      <c r="AA20" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00190960")</f>
         <v>U00190960</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13">
+      <c r="A21" s="14">
         <v>20.0</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="14" t="s">
         <v>64</v>
       </c>
       <c r="C21" s="10">
@@ -5806,32 +6864,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N21" s="11"/>
+      <c r="N21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
+        <v>0.8</v>
+      </c>
       <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
+      <c r="P21" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="Q21" s="11"/>
-      <c r="R21" s="11"/>
+      <c r="R21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
+        <v>1.2</v>
+      </c>
       <c r="S21" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9)</f>
-        <v>0.9</v>
-      </c>
-      <c r="T21" s="11"/>
-      <c r="U21" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
+      <c r="T21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="U21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="V21" s="11"/>
       <c r="W21" s="11"/>
       <c r="X21" s="11"/>
       <c r="Y21" s="11"/>
-      <c r="Z21" s="14"/>
-      <c r="AA21" s="14" t="str">
+      <c r="Z21" s="15"/>
+      <c r="AA21" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00189475")</f>
         <v>U00189475</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13">
+      <c r="A22" s="14">
         <v>21.0</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="14" t="s">
         <v>65</v>
       </c>
       <c r="C22" s="10">
@@ -5878,32 +6951,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N22" s="11"/>
+      <c r="N22" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
+      </c>
       <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
+      <c r="P22" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
       <c r="Q22" s="11"/>
-      <c r="R22" s="11"/>
+      <c r="R22" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="S22" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
-      </c>
-      <c r="T22" s="11"/>
-      <c r="U22" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="T22" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="U22" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="V22" s="11"/>
       <c r="W22" s="11"/>
       <c r="X22" s="11"/>
       <c r="Y22" s="11"/>
-      <c r="Z22" s="14"/>
-      <c r="AA22" s="14" t="str">
+      <c r="Z22" s="15"/>
+      <c r="AA22" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00190866")</f>
         <v>U00190866</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13">
+      <c r="A23" s="14">
         <v>22.0</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="14" t="s">
         <v>66</v>
       </c>
       <c r="C23" s="10">
@@ -5950,32 +7038,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N23" s="11"/>
+      <c r="N23" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
+      <c r="P23" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q23" s="11"/>
-      <c r="R23" s="11"/>
-      <c r="S23" s="11">
+      <c r="R23" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
       </c>
-      <c r="T23" s="11"/>
-      <c r="U23" s="11"/>
+      <c r="S23" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
+      </c>
+      <c r="T23" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U23" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="V23" s="11"/>
       <c r="W23" s="11"/>
       <c r="X23" s="11"/>
       <c r="Y23" s="11"/>
-      <c r="Z23" s="14"/>
-      <c r="AA23" s="14" t="str">
+      <c r="Z23" s="15"/>
+      <c r="AA23" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00188702")</f>
         <v>U00188702</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13">
+      <c r="A24" s="14">
         <v>23.0</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="14" t="s">
         <v>67</v>
       </c>
       <c r="C24" s="10">
@@ -6022,32 +7125,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="N24" s="11"/>
+      <c r="N24" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="O24" s="11"/>
-      <c r="P24" s="11"/>
+      <c r="P24" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="Q24" s="11"/>
-      <c r="R24" s="11"/>
+      <c r="R24" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="S24" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
-      </c>
-      <c r="T24" s="11"/>
-      <c r="U24" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="T24" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U24" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="V24" s="11"/>
       <c r="W24" s="11"/>
       <c r="X24" s="11"/>
       <c r="Y24" s="11"/>
-      <c r="Z24" s="14"/>
-      <c r="AA24" s="14" t="str">
+      <c r="Z24" s="15"/>
+      <c r="AA24" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00189620")</f>
         <v>U00189620</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13">
+      <c r="A25" s="14">
         <v>24.0</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="14" t="s">
         <v>68</v>
       </c>
       <c r="C25" s="10">
@@ -6094,32 +7212,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N25" s="11"/>
+      <c r="N25" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
       <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
+      <c r="P25" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="Q25" s="11"/>
-      <c r="R25" s="11"/>
+      <c r="R25" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
       <c r="S25" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
-      </c>
-      <c r="T25" s="11"/>
-      <c r="U25" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
+      </c>
+      <c r="T25" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U25" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="V25" s="11"/>
       <c r="W25" s="11"/>
       <c r="X25" s="11"/>
       <c r="Y25" s="11"/>
-      <c r="Z25" s="14"/>
-      <c r="AA25" s="14" t="str">
+      <c r="Z25" s="15"/>
+      <c r="AA25" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00079391")</f>
         <v>U00079391</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13">
+      <c r="A26" s="14">
         <v>25.0</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="14" t="s">
         <v>69</v>
       </c>
       <c r="C26" s="10">
@@ -6166,23 +7299,38 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N26" s="11"/>
+      <c r="N26" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
+      <c r="P26" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
       <c r="Q26" s="11"/>
-      <c r="R26" s="11"/>
+      <c r="R26" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="S26" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
-      </c>
-      <c r="T26" s="11"/>
-      <c r="U26" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="T26" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="U26" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="V26" s="11"/>
       <c r="W26" s="11"/>
       <c r="X26" s="11"/>
       <c r="Y26" s="11"/>
-      <c r="Z26" s="14"/>
-      <c r="AA26" s="14" t="str">
+      <c r="Z26" s="15"/>
+      <c r="AA26" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00190937")</f>
         <v>U00190937</v>
       </c>
@@ -6233,10 +7381,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="str">
@@ -6284,8 +7432,8 @@
         <v>P4</v>
       </c>
       <c r="N1" s="1" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT3")</f>
-        <v>PQT3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PQT2")</f>
+        <v>PQT2</v>
       </c>
       <c r="O1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PA")</f>
@@ -6331,20 +7479,20 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ID")</f>
         <v>ID</v>
       </c>
-      <c r="Z1" s="14" t="str">
+      <c r="Z1" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"NRC")</f>
         <v>NRC</v>
       </c>
-      <c r="AA1" s="14" t="str">
+      <c r="AA1" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"P1")</f>
         <v>P1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <v>1.0</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>70</v>
       </c>
       <c r="C2" s="10">
@@ -6383,18 +7531,36 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="L2" s="11"/>
+      <c r="L2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
+      <c r="N2" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
+      </c>
       <c r="O2" s="11"/>
-      <c r="P2" s="11"/>
+      <c r="P2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
+      </c>
       <c r="Q2" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
-      </c>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
+      <c r="R2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="S2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="T2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U2" s="11"/>
       <c r="V2" s="11"/>
       <c r="W2" s="11"/>
@@ -6403,20 +7569,20 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00167708")</f>
         <v>U00167708</v>
       </c>
-      <c r="Z2" s="14">
+      <c r="Z2" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63507.0)</f>
         <v>63507</v>
       </c>
-      <c r="AA2" s="14">
+      <c r="AA2" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13">
+      <c r="A3" s="14">
         <v>2.0</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>71</v>
       </c>
       <c r="C3" s="10">
@@ -6455,18 +7621,36 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="L3" s="11"/>
+      <c r="L3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
       <c r="M3" s="11"/>
-      <c r="N3" s="11"/>
+      <c r="N3" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
       <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
+      <c r="P3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
+        <v>1.4</v>
+      </c>
       <c r="Q3" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
-      </c>
-      <c r="R3" s="11"/>
-      <c r="S3" s="11"/>
-      <c r="T3" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
+      </c>
+      <c r="R3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
+      <c r="S3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="T3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U3" s="11"/>
       <c r="V3" s="11"/>
       <c r="W3" s="11"/>
@@ -6475,20 +7659,20 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00178362")</f>
         <v>U00178362</v>
       </c>
-      <c r="Z3" s="14">
+      <c r="Z3" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63507.0)</f>
         <v>63507</v>
       </c>
-      <c r="AA3" s="14">
+      <c r="AA3" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13">
+      <c r="A4" s="14">
         <v>3.0</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>72</v>
       </c>
       <c r="C4" s="10">
@@ -6527,18 +7711,36 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="L4" s="11"/>
+      <c r="L4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
+      </c>
       <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
+      <c r="N4" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
+      <c r="P4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
+        <v>1.8</v>
+      </c>
       <c r="Q4" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
-      </c>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
+      </c>
+      <c r="R4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="S4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="T4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U4" s="11"/>
       <c r="V4" s="11"/>
       <c r="W4" s="11"/>
@@ -6547,20 +7749,20 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00144436")</f>
         <v>U00144436</v>
       </c>
-      <c r="Z4" s="14">
+      <c r="Z4" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63507.0)</f>
         <v>63507</v>
       </c>
-      <c r="AA4" s="14">
+      <c r="AA4" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.55)</f>
         <v>2.55</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13">
+      <c r="A5" s="14">
         <v>4.0</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>73</v>
       </c>
       <c r="C5" s="10">
@@ -6599,18 +7801,36 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="L5" s="11"/>
+      <c r="L5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
+      </c>
       <c r="M5" s="11"/>
-      <c r="N5" s="11"/>
+      <c r="N5" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
+      </c>
       <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
+      <c r="P5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
+        <v>1.3</v>
+      </c>
       <c r="Q5" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
-        <v>1.6</v>
-      </c>
-      <c r="R5" s="11"/>
-      <c r="S5" s="11"/>
-      <c r="T5" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
+      <c r="R5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="S5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="T5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U5" s="11"/>
       <c r="V5" s="11"/>
       <c r="W5" s="11"/>
@@ -6619,20 +7839,20 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00186154")</f>
         <v>U00186154</v>
       </c>
-      <c r="Z5" s="14">
+      <c r="Z5" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63507.0)</f>
         <v>63507</v>
       </c>
-      <c r="AA5" s="14">
+      <c r="AA5" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <v>5.0</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>74</v>
       </c>
       <c r="C6" s="10">
@@ -6671,18 +7891,36 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="11"/>
+      <c r="L6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
       <c r="M6" s="11"/>
-      <c r="N6" s="11"/>
+      <c r="N6" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
+      </c>
       <c r="O6" s="11"/>
-      <c r="P6" s="11"/>
+      <c r="P6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
+        <v>1.2</v>
+      </c>
       <c r="Q6" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
-      </c>
-      <c r="R6" s="11"/>
-      <c r="S6" s="11"/>
-      <c r="T6" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
+      <c r="R6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="S6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
+      <c r="T6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
       <c r="W6" s="11"/>
@@ -6691,20 +7929,20 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00179741")</f>
         <v>U00179741</v>
       </c>
-      <c r="Z6" s="14">
+      <c r="Z6" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63507.0)</f>
         <v>63507</v>
       </c>
-      <c r="AA6" s="14">
+      <c r="AA6" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13">
+      <c r="A7" s="14">
         <v>6.0</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>75</v>
       </c>
       <c r="C7" s="10">
@@ -6743,18 +7981,36 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="L7" s="11"/>
+      <c r="L7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
       <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
+      <c r="N7" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
+      <c r="P7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
       <c r="Q7" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
-      </c>
-      <c r="R7" s="11"/>
-      <c r="S7" s="11"/>
-      <c r="T7" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
+      </c>
+      <c r="R7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
+      <c r="S7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="T7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U7" s="11"/>
       <c r="V7" s="11"/>
       <c r="W7" s="11"/>
@@ -6763,20 +8019,20 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00183448")</f>
         <v>U00183448</v>
       </c>
-      <c r="Z7" s="14">
+      <c r="Z7" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63507.0)</f>
         <v>63507</v>
       </c>
-      <c r="AA7" s="14">
+      <c r="AA7" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13">
+      <c r="A8" s="14">
         <v>7.0</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>76</v>
       </c>
       <c r="C8" s="10">
@@ -6815,18 +8071,36 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="L8" s="11"/>
+      <c r="L8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
+      <c r="N8" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
+      </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
-      <c r="Q8" s="11">
+      <c r="P8" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="R8" s="11"/>
-      <c r="S8" s="11"/>
-      <c r="T8" s="11"/>
+      <c r="Q8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="R8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="S8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
+      <c r="T8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U8" s="11"/>
       <c r="V8" s="11"/>
       <c r="W8" s="11"/>
@@ -6835,20 +8109,20 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00177993")</f>
         <v>U00177993</v>
       </c>
-      <c r="Z8" s="14">
+      <c r="Z8" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63507.0)</f>
         <v>63507</v>
       </c>
-      <c r="AA8" s="14">
+      <c r="AA8" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13">
+      <c r="A9" s="14">
         <v>8.0</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>77</v>
       </c>
       <c r="C9" s="10">
@@ -6887,18 +8161,36 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="L9" s="11"/>
+      <c r="L9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
       <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
+      <c r="N9" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
+      <c r="P9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="Q9" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
-      </c>
-      <c r="R9" s="11"/>
-      <c r="S9" s="11"/>
-      <c r="T9" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="R9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="S9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="T9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U9" s="11"/>
       <c r="V9" s="11"/>
       <c r="W9" s="11"/>
@@ -6907,20 +8199,20 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00186962")</f>
         <v>U00186962</v>
       </c>
-      <c r="Z9" s="14">
+      <c r="Z9" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63507.0)</f>
         <v>63507</v>
       </c>
-      <c r="AA9" s="14">
+      <c r="AA9" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <v>9.0</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>78</v>
       </c>
       <c r="C10" s="10">
@@ -6959,18 +8251,36 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="L10" s="11"/>
+      <c r="L10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
       <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
+      <c r="N10" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
+        <v>3.1</v>
+      </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
+      <c r="P10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
+      </c>
       <c r="Q10" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7)</f>
-        <v>0.7</v>
-      </c>
-      <c r="R10" s="11"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
+      </c>
+      <c r="R10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="S10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="T10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U10" s="11"/>
       <c r="V10" s="11"/>
       <c r="W10" s="11"/>
@@ -6979,20 +8289,20 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00183439")</f>
         <v>U00183439</v>
       </c>
-      <c r="Z10" s="14">
+      <c r="Z10" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63507.0)</f>
         <v>63507</v>
       </c>
-      <c r="AA10" s="14">
+      <c r="AA10" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13">
+      <c r="A11" s="14">
         <v>10.0</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>79</v>
       </c>
       <c r="C11" s="10">
@@ -7031,18 +8341,36 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
         <v>2</v>
       </c>
-      <c r="L11" s="11"/>
+      <c r="L11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
+        <v>3.1</v>
+      </c>
       <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
+      <c r="N11" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
+      </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
+      <c r="P11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
+        <v>1.8</v>
+      </c>
       <c r="Q11" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
-        <v>1.4</v>
-      </c>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
+      <c r="R11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="S11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="T11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U11" s="11"/>
       <c r="V11" s="11"/>
       <c r="W11" s="11"/>
@@ -7051,20 +8379,20 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00186689")</f>
         <v>U00186689</v>
       </c>
-      <c r="Z11" s="14">
+      <c r="Z11" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63507.0)</f>
         <v>63507</v>
       </c>
-      <c r="AA11" s="14">
+      <c r="AA11" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
         <v>1.8</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <v>11.0</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>80</v>
       </c>
       <c r="C12" s="10">
@@ -7108,12 +8436,15 @@
       <c r="N12" s="11"/>
       <c r="O12" s="11"/>
       <c r="P12" s="11"/>
-      <c r="Q12" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
+      <c r="Q12" s="11"/>
+      <c r="R12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="S12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="T12" s="11"/>
       <c r="U12" s="11"/>
       <c r="V12" s="11"/>
@@ -7123,20 +8454,20 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00180170")</f>
         <v>U00180170</v>
       </c>
-      <c r="Z12" s="14">
+      <c r="Z12" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63507.0)</f>
         <v>63507</v>
       </c>
-      <c r="AA12" s="14">
+      <c r="AA12" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13">
+      <c r="A13" s="14">
         <v>12.0</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>81</v>
       </c>
       <c r="C13" s="10">
@@ -7179,13 +8510,22 @@
       <c r="M13" s="11"/>
       <c r="N13" s="11"/>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
+      <c r="P13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="Q13" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
         <v>0.8</v>
       </c>
-      <c r="R13" s="11"/>
-      <c r="S13" s="11"/>
+      <c r="R13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="S13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="T13" s="11"/>
       <c r="U13" s="11"/>
       <c r="V13" s="11"/>
@@ -7195,164 +8535,200 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00187627")</f>
         <v>U00187627</v>
       </c>
-      <c r="Z13" s="14">
+      <c r="Z13" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63507.0)</f>
         <v>63507</v>
       </c>
-      <c r="AA13" s="14">
+      <c r="AA13" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
         <v>3.4</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13">
+      <c r="A14" s="14">
         <v>13.0</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>82</v>
       </c>
       <c r="C14" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
-        <v>3.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
       </c>
       <c r="D14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
+      </c>
+      <c r="E14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="F14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
+      </c>
+      <c r="G14" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
+      <c r="H14" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
       </c>
-      <c r="E14" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
-        <v>3.4</v>
-      </c>
-      <c r="F14" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
-        <v>3.5</v>
-      </c>
-      <c r="G14" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
-      </c>
-      <c r="H14" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
-      </c>
       <c r="I14" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="J14" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
       <c r="K14" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
-        <v>5</v>
-      </c>
-      <c r="L14" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="L14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
       <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
+      <c r="N14" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
+      <c r="P14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
+      </c>
       <c r="Q14" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
-      </c>
-      <c r="R14" s="11"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
+      </c>
+      <c r="R14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="S14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="T14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="U14" s="11"/>
       <c r="V14" s="11"/>
       <c r="W14" s="11"/>
       <c r="X14" s="11"/>
       <c r="Y14" s="11" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00186511")</f>
-        <v>U00186511</v>
-      </c>
-      <c r="Z14" s="14">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00186798")</f>
+        <v>U00186798</v>
+      </c>
+      <c r="Z14" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63507.0)</f>
         <v>63507</v>
       </c>
-      <c r="AA14" s="14">
+      <c r="AA14" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13">
+      <c r="A15" s="14">
         <v>14.0</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>83</v>
       </c>
       <c r="C15" s="10">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
-        <v>4.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
       </c>
       <c r="D15" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
-        <v>3.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="E15" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="F15" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
-        <v>4.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="G15" s="1">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
+      </c>
+      <c r="H15" s="1">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
       </c>
-      <c r="H15" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
-        <v>3.5</v>
-      </c>
       <c r="I15" s="1">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
       </c>
       <c r="J15" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
       <c r="K15" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
-      </c>
-      <c r="L15" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="L15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
       <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
+      <c r="N15" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
+      </c>
       <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
+      <c r="P15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
       <c r="Q15" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="R15" s="11"/>
-      <c r="S15" s="11"/>
-      <c r="T15" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
+      <c r="R15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="S15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="T15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U15" s="11"/>
       <c r="V15" s="11"/>
       <c r="W15" s="11"/>
       <c r="X15" s="11"/>
       <c r="Y15" s="11" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00186798")</f>
-        <v>U00186798</v>
-      </c>
-      <c r="Z15" s="14">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00186511")</f>
+        <v>U00186511</v>
+      </c>
+      <c r="Z15" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63507.0)</f>
         <v>63507</v>
       </c>
-      <c r="AA15" s="14">
+      <c r="AA15" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13">
+      <c r="A16" s="14">
         <v>15.0</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>84</v>
       </c>
       <c r="C16" s="10">
@@ -7391,18 +8767,36 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="L16" s="11"/>
+      <c r="L16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
+      <c r="N16" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
+      <c r="P16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
       <c r="Q16" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
-      </c>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="R16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
+      <c r="S16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
+      <c r="T16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="U16" s="11"/>
       <c r="V16" s="11"/>
       <c r="W16" s="11"/>
@@ -7411,11 +8805,11 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00182742")</f>
         <v>U00182742</v>
       </c>
-      <c r="Z16" s="14">
+      <c r="Z16" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),63507.0)</f>
         <v>63507</v>
       </c>
-      <c r="AA16" s="14">
+      <c r="AA16" s="15">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
@@ -7457,211 +8851,229 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2666666666666666)</f>
         <v>3.266666667</v>
       </c>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="14"/>
-      <c r="R17" s="14"/>
-      <c r="S17" s="14"/>
-      <c r="T17" s="14"/>
-      <c r="U17" s="14"/>
-      <c r="V17" s="14"/>
-      <c r="W17" s="14"/>
-      <c r="X17" s="14"/>
-      <c r="Y17" s="14"/>
-      <c r="Z17" s="14"/>
-      <c r="AA17" s="14"/>
+      <c r="L17" s="16">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1846153846153844)</f>
+        <v>3.184615385</v>
+      </c>
+      <c r="M17" s="15"/>
+      <c r="N17" s="16">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.430769230769231)</f>
+        <v>3.430769231</v>
+      </c>
+      <c r="O17" s="15"/>
+      <c r="P17" s="16">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5357142857142858)</f>
+        <v>1.535714286</v>
+      </c>
+      <c r="Q17" s="16">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4785714285714286)</f>
+        <v>2.478571429</v>
+      </c>
+      <c r="R17" s="16">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3866666666666663)</f>
+        <v>3.386666667</v>
+      </c>
+      <c r="S17" s="16">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8666666666666667)</f>
+        <v>1.866666667</v>
+      </c>
+      <c r="T17" s="15"/>
+      <c r="U17" s="15"/>
+      <c r="V17" s="15"/>
+      <c r="W17" s="15"/>
+      <c r="X17" s="15"/>
+      <c r="Y17" s="15"/>
+      <c r="Z17" s="15"/>
+      <c r="AA17" s="15"/>
     </row>
     <row r="18">
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
-      <c r="U18" s="14"/>
-      <c r="V18" s="14"/>
-      <c r="W18" s="14"/>
-      <c r="X18" s="14"/>
-      <c r="Y18" s="14"/>
-      <c r="Z18" s="14"/>
-      <c r="AA18" s="14"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="15"/>
+      <c r="O18" s="15"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="15"/>
+      <c r="R18" s="15"/>
+      <c r="S18" s="15"/>
+      <c r="T18" s="15"/>
+      <c r="U18" s="15"/>
+      <c r="V18" s="15"/>
+      <c r="W18" s="15"/>
+      <c r="X18" s="15"/>
+      <c r="Y18" s="15"/>
+      <c r="Z18" s="15"/>
+      <c r="AA18" s="15"/>
     </row>
     <row r="19">
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="14"/>
-      <c r="S19" s="14"/>
-      <c r="T19" s="14"/>
-      <c r="U19" s="14"/>
-      <c r="V19" s="14"/>
-      <c r="W19" s="14"/>
-      <c r="X19" s="14"/>
-      <c r="Y19" s="14"/>
-      <c r="Z19" s="14"/>
-      <c r="AA19" s="14"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="15"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="15"/>
+      <c r="R19" s="15"/>
+      <c r="S19" s="15"/>
+      <c r="T19" s="15"/>
+      <c r="U19" s="15"/>
+      <c r="V19" s="15"/>
+      <c r="W19" s="15"/>
+      <c r="X19" s="15"/>
+      <c r="Y19" s="15"/>
+      <c r="Z19" s="15"/>
+      <c r="AA19" s="15"/>
     </row>
     <row r="20">
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14"/>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14"/>
-      <c r="S20" s="14"/>
-      <c r="T20" s="14"/>
-      <c r="U20" s="14"/>
-      <c r="V20" s="14"/>
-      <c r="W20" s="14"/>
-      <c r="X20" s="14"/>
-      <c r="Y20" s="14"/>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="15"/>
+      <c r="O20" s="15"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="15"/>
+      <c r="R20" s="15"/>
+      <c r="S20" s="15"/>
+      <c r="T20" s="15"/>
+      <c r="U20" s="15"/>
+      <c r="V20" s="15"/>
+      <c r="W20" s="15"/>
+      <c r="X20" s="15"/>
+      <c r="Y20" s="15"/>
+      <c r="Z20" s="15"/>
+      <c r="AA20" s="15"/>
     </row>
     <row r="21">
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="14"/>
-      <c r="S21" s="14"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="14"/>
-      <c r="V21" s="14"/>
-      <c r="W21" s="14"/>
-      <c r="X21" s="14"/>
-      <c r="Y21" s="14"/>
-      <c r="Z21" s="14"/>
-      <c r="AA21" s="14"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="15"/>
+      <c r="R21" s="15"/>
+      <c r="S21" s="15"/>
+      <c r="T21" s="15"/>
+      <c r="U21" s="15"/>
+      <c r="V21" s="15"/>
+      <c r="W21" s="15"/>
+      <c r="X21" s="15"/>
+      <c r="Y21" s="15"/>
+      <c r="Z21" s="15"/>
+      <c r="AA21" s="15"/>
     </row>
     <row r="22">
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="14"/>
-      <c r="R22" s="14"/>
-      <c r="S22" s="14"/>
-      <c r="T22" s="14"/>
-      <c r="U22" s="14"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="14"/>
-      <c r="X22" s="14"/>
-      <c r="Y22" s="14"/>
-      <c r="Z22" s="14"/>
-      <c r="AA22" s="14"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="15"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="15"/>
+      <c r="R22" s="15"/>
+      <c r="S22" s="15"/>
+      <c r="T22" s="15"/>
+      <c r="U22" s="15"/>
+      <c r="V22" s="15"/>
+      <c r="W22" s="15"/>
+      <c r="X22" s="15"/>
+      <c r="Y22" s="15"/>
+      <c r="Z22" s="15"/>
+      <c r="AA22" s="15"/>
     </row>
     <row r="23">
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="14"/>
-      <c r="R23" s="14"/>
-      <c r="S23" s="14"/>
-      <c r="T23" s="14"/>
-      <c r="U23" s="14"/>
-      <c r="V23" s="14"/>
-      <c r="W23" s="14"/>
-      <c r="X23" s="14"/>
-      <c r="Y23" s="14"/>
-      <c r="Z23" s="14"/>
-      <c r="AA23" s="14"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="15"/>
+      <c r="R23" s="15"/>
+      <c r="S23" s="15"/>
+      <c r="T23" s="15"/>
+      <c r="U23" s="15"/>
+      <c r="V23" s="15"/>
+      <c r="W23" s="15"/>
+      <c r="X23" s="15"/>
+      <c r="Y23" s="15"/>
+      <c r="Z23" s="15"/>
+      <c r="AA23" s="15"/>
     </row>
     <row r="24">
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="14"/>
-      <c r="X24" s="14"/>
-      <c r="Y24" s="14"/>
-      <c r="Z24" s="14"/>
-      <c r="AA24" s="14"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="15"/>
+      <c r="R24" s="15"/>
+      <c r="S24" s="15"/>
+      <c r="T24" s="15"/>
+      <c r="U24" s="15"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="15"/>
+      <c r="Y24" s="15"/>
+      <c r="Z24" s="15"/>
+      <c r="AA24" s="15"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -7683,10 +9095,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="str">
@@ -7781,20 +9193,20 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta13")</f>
         <v>Ta13</v>
       </c>
-      <c r="Z1" s="14" t="str">
+      <c r="Z1" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta14")</f>
         <v>Ta14</v>
       </c>
-      <c r="AA1" s="14" t="str">
+      <c r="AA1" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ID")</f>
         <v>ID</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13">
+      <c r="A2" s="14">
         <v>1.0</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>85</v>
       </c>
       <c r="C2" s="10">
@@ -7856,17 +9268,17 @@
       <c r="W2" s="11"/>
       <c r="X2" s="11"/>
       <c r="Y2" s="11"/>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="14" t="str">
+      <c r="Z2" s="15"/>
+      <c r="AA2" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00190130")</f>
         <v>U00190130</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13">
+      <c r="A3" s="14">
         <v>2.0</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="14" t="s">
         <v>86</v>
       </c>
       <c r="C3" s="10">
@@ -7913,32 +9325,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N3" s="11"/>
+      <c r="N3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="O3" s="11"/>
-      <c r="P3" s="11"/>
+      <c r="P3" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Q3" s="11"/>
-      <c r="R3" s="11"/>
+      <c r="R3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
       <c r="S3" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
-        <v>1.5</v>
-      </c>
-      <c r="T3" s="11"/>
-      <c r="U3" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
+      </c>
+      <c r="T3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
       <c r="V3" s="11"/>
       <c r="W3" s="11"/>
       <c r="X3" s="11"/>
       <c r="Y3" s="11"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14" t="str">
+      <c r="Z3" s="15"/>
+      <c r="AA3" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00190358")</f>
         <v>U00190358</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13">
+      <c r="A4" s="14">
         <v>3.0</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="14" t="s">
         <v>87</v>
       </c>
       <c r="C4" s="10">
@@ -7985,32 +9412,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N4" s="11"/>
+      <c r="N4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
       <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
+      <c r="P4" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
+      <c r="R4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
       <c r="S4" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
+      </c>
+      <c r="T4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="U4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="V4" s="11"/>
       <c r="W4" s="11"/>
       <c r="X4" s="11"/>
       <c r="Y4" s="11"/>
-      <c r="Z4" s="14"/>
-      <c r="AA4" s="14" t="str">
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00190086")</f>
         <v>U00190086</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13">
+      <c r="A5" s="14">
         <v>4.0</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>88</v>
       </c>
       <c r="C5" s="10">
@@ -8057,32 +9499,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N5" s="11"/>
+      <c r="N5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
       <c r="O5" s="11"/>
-      <c r="P5" s="11"/>
+      <c r="P5" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
       <c r="Q5" s="11"/>
-      <c r="R5" s="11"/>
+      <c r="R5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
+      </c>
       <c r="S5" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
-      </c>
-      <c r="T5" s="11"/>
-      <c r="U5" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="T5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
+      </c>
+      <c r="U5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="V5" s="11"/>
       <c r="W5" s="11"/>
       <c r="X5" s="11"/>
       <c r="Y5" s="11"/>
-      <c r="Z5" s="14"/>
-      <c r="AA5" s="14" t="str">
+      <c r="Z5" s="15"/>
+      <c r="AA5" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00186584")</f>
         <v>U00186584</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <v>5.0</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>89</v>
       </c>
       <c r="C6" s="10">
@@ -8144,17 +9601,17 @@
       <c r="W6" s="11"/>
       <c r="X6" s="11"/>
       <c r="Y6" s="11"/>
-      <c r="Z6" s="14"/>
-      <c r="AA6" s="14" t="str">
+      <c r="Z6" s="15"/>
+      <c r="AA6" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00143077")</f>
         <v>U00143077</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13">
+      <c r="A7" s="14">
         <v>6.0</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>90</v>
       </c>
       <c r="C7" s="10">
@@ -8201,32 +9658,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="N7" s="11"/>
+      <c r="N7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.2)</f>
+        <v>0.2</v>
+      </c>
       <c r="O7" s="11"/>
-      <c r="P7" s="11"/>
+      <c r="P7" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
       <c r="Q7" s="11"/>
-      <c r="R7" s="11"/>
+      <c r="R7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.5)</f>
+        <v>0.5</v>
+      </c>
       <c r="S7" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
-        <v>1.6</v>
-      </c>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
+      </c>
+      <c r="T7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="U7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="V7" s="11"/>
       <c r="W7" s="11"/>
       <c r="X7" s="11"/>
       <c r="Y7" s="11"/>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="14" t="str">
+      <c r="Z7" s="15"/>
+      <c r="AA7" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00189998")</f>
         <v>U00189998</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13">
+      <c r="A8" s="14">
         <v>7.0</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>91</v>
       </c>
       <c r="C8" s="10">
@@ -8273,32 +9745,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N8" s="11"/>
+      <c r="N8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="O8" s="11"/>
-      <c r="P8" s="11"/>
+      <c r="P8" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="Q8" s="11"/>
-      <c r="R8" s="11"/>
+      <c r="R8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="S8" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
-        <v>1.4</v>
-      </c>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
+      <c r="T8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="U8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="V8" s="11"/>
       <c r="W8" s="11"/>
       <c r="X8" s="11"/>
       <c r="Y8" s="11"/>
-      <c r="Z8" s="14"/>
-      <c r="AA8" s="14" t="str">
+      <c r="Z8" s="15"/>
+      <c r="AA8" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00189341")</f>
         <v>U00189341</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13">
+      <c r="A9" s="14">
         <v>8.0</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>92</v>
       </c>
       <c r="C9" s="10">
@@ -8345,32 +9832,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N9" s="11"/>
+      <c r="N9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="O9" s="11"/>
-      <c r="P9" s="11"/>
+      <c r="P9" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="Q9" s="11"/>
-      <c r="R9" s="11"/>
+      <c r="R9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="S9" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
-      </c>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
+      </c>
+      <c r="T9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="U9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="V9" s="11"/>
       <c r="W9" s="11"/>
       <c r="X9" s="11"/>
       <c r="Y9" s="11"/>
-      <c r="Z9" s="14"/>
-      <c r="AA9" s="14" t="str">
+      <c r="Z9" s="15"/>
+      <c r="AA9" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00190156")</f>
         <v>U00190156</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13">
+      <c r="A10" s="14">
         <v>9.0</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>73</v>
       </c>
       <c r="C10" s="10">
@@ -8417,32 +9919,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
-      <c r="N10" s="11"/>
+      <c r="N10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
+      </c>
       <c r="O10" s="11"/>
-      <c r="P10" s="11"/>
+      <c r="P10" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
       <c r="Q10" s="11"/>
-      <c r="R10" s="11"/>
+      <c r="R10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
+        <v>1.4</v>
+      </c>
       <c r="S10" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
-        <v>1.3</v>
-      </c>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
+      <c r="T10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
+      <c r="U10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="V10" s="11"/>
       <c r="W10" s="11"/>
       <c r="X10" s="11"/>
       <c r="Y10" s="11"/>
-      <c r="Z10" s="14"/>
-      <c r="AA10" s="14" t="str">
+      <c r="Z10" s="15"/>
+      <c r="AA10" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00186154")</f>
         <v>U00186154</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13">
+      <c r="A11" s="14">
         <v>10.0</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>93</v>
       </c>
       <c r="C11" s="10">
@@ -8489,32 +10006,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N11" s="11"/>
+      <c r="N11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="O11" s="11"/>
-      <c r="P11" s="11"/>
+      <c r="P11" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="Q11" s="11"/>
-      <c r="R11" s="11"/>
-      <c r="S11" s="11">
+      <c r="R11" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
         <v>2.4</v>
       </c>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
+      <c r="S11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="T11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
+      <c r="U11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="V11" s="11"/>
       <c r="W11" s="11"/>
       <c r="X11" s="11"/>
       <c r="Y11" s="11"/>
-      <c r="Z11" s="14"/>
-      <c r="AA11" s="14" t="str">
+      <c r="Z11" s="15"/>
+      <c r="AA11" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00171125")</f>
         <v>U00171125</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <v>11.0</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="14" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="10">
@@ -8561,32 +10093,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N12" s="11"/>
+      <c r="N12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
+      <c r="P12" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
+      <c r="R12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="S12" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
-      </c>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
+        <v>3.1</v>
+      </c>
+      <c r="T12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="U12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="V12" s="11"/>
       <c r="W12" s="11"/>
       <c r="X12" s="11"/>
       <c r="Y12" s="11"/>
-      <c r="Z12" s="14"/>
-      <c r="AA12" s="14" t="str">
+      <c r="Z12" s="15"/>
+      <c r="AA12" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00189659")</f>
         <v>U00189659</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13">
+      <c r="A13" s="14">
         <v>12.0</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="14" t="s">
         <v>95</v>
       </c>
       <c r="C13" s="10">
@@ -8633,32 +10180,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N13" s="11"/>
+      <c r="N13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
+      </c>
       <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
+      <c r="P13" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="Q13" s="11"/>
-      <c r="R13" s="11"/>
+      <c r="R13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
+      </c>
       <c r="S13" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
-      </c>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
+      </c>
+      <c r="T13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="U13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
       <c r="V13" s="11"/>
       <c r="W13" s="11"/>
       <c r="X13" s="11"/>
       <c r="Y13" s="11"/>
-      <c r="Z13" s="14"/>
-      <c r="AA13" s="14" t="str">
+      <c r="Z13" s="15"/>
+      <c r="AA13" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00189679")</f>
         <v>U00189679</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13">
+      <c r="A14" s="14">
         <v>13.0</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="14" t="s">
         <v>96</v>
       </c>
       <c r="C14" s="10">
@@ -8705,32 +10267,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="N14" s="11"/>
+      <c r="N14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
+      </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="11"/>
+      <c r="P14" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
+      </c>
       <c r="Q14" s="11"/>
-      <c r="R14" s="11"/>
+      <c r="R14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
       <c r="S14" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
+        <v>3.1</v>
+      </c>
+      <c r="T14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
+      </c>
+      <c r="U14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
       <c r="V14" s="11"/>
       <c r="W14" s="11"/>
       <c r="X14" s="11"/>
       <c r="Y14" s="11"/>
-      <c r="Z14" s="14"/>
-      <c r="AA14" s="14" t="str">
+      <c r="Z14" s="15"/>
+      <c r="AA14" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00189517")</f>
         <v>U00189517</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13">
+      <c r="A15" s="14">
         <v>14.0</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>97</v>
       </c>
       <c r="C15" s="10">
@@ -8777,32 +10354,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N15" s="11"/>
+      <c r="N15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
       <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
+      <c r="P15" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
       <c r="Q15" s="11"/>
-      <c r="R15" s="11"/>
+      <c r="R15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
+        <v>1.2</v>
+      </c>
       <c r="S15" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
-      </c>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="T15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="U15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
+      </c>
       <c r="V15" s="11"/>
       <c r="W15" s="11"/>
       <c r="X15" s="11"/>
       <c r="Y15" s="11"/>
-      <c r="Z15" s="14"/>
-      <c r="AA15" s="14" t="str">
+      <c r="Z15" s="15"/>
+      <c r="AA15" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00188432")</f>
         <v>U00188432</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13">
+      <c r="A16" s="14">
         <v>15.0</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>98</v>
       </c>
       <c r="C16" s="10">
@@ -8849,32 +10441,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
       </c>
-      <c r="N16" s="11"/>
+      <c r="N16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
+      </c>
       <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
+      <c r="P16" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
       <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11">
+      <c r="R16" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
         <v>1.4</v>
       </c>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
+      <c r="S16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
+      <c r="T16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
+      <c r="U16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="V16" s="11"/>
       <c r="W16" s="11"/>
       <c r="X16" s="11"/>
       <c r="Y16" s="11"/>
-      <c r="Z16" s="14"/>
-      <c r="AA16" s="14" t="str">
+      <c r="Z16" s="15"/>
+      <c r="AA16" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00145546")</f>
         <v>U00145546</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13">
+      <c r="A17" s="14">
         <v>16.0</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="14" t="s">
         <v>99</v>
       </c>
       <c r="C17" s="10">
@@ -8921,32 +10528,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="N17" s="11"/>
+      <c r="N17" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
       <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
+      <c r="P17" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7)</f>
+        <v>0.7</v>
+      </c>
       <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
+      <c r="R17" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
+        <v>1.2</v>
+      </c>
       <c r="S17" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
-      </c>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
+      <c r="T17" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
+        <v>1.3</v>
+      </c>
+      <c r="U17" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="V17" s="11"/>
       <c r="W17" s="11"/>
       <c r="X17" s="11"/>
       <c r="Y17" s="11"/>
-      <c r="Z17" s="14"/>
-      <c r="AA17" s="14" t="str">
+      <c r="Z17" s="15"/>
+      <c r="AA17" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00170700")</f>
         <v>U00170700</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13">
+      <c r="A18" s="14">
         <v>17.0</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="14" t="s">
         <v>100</v>
       </c>
       <c r="C18" s="10">
@@ -8993,32 +10615,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N18" s="11"/>
+      <c r="N18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
       <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
+      <c r="P18" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="Q18" s="11"/>
-      <c r="R18" s="11"/>
+      <c r="R18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7)</f>
+        <v>0.7</v>
+      </c>
       <c r="S18" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
-      </c>
-      <c r="T18" s="11"/>
-      <c r="U18" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
+      </c>
+      <c r="T18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
+      <c r="U18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="V18" s="11"/>
       <c r="W18" s="11"/>
       <c r="X18" s="11"/>
       <c r="Y18" s="11"/>
-      <c r="Z18" s="14"/>
-      <c r="AA18" s="14" t="str">
+      <c r="Z18" s="15"/>
+      <c r="AA18" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00194322")</f>
         <v>U00194322</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13">
+      <c r="A19" s="14">
         <v>18.0</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="14" t="s">
         <v>101</v>
       </c>
       <c r="C19" s="10">
@@ -9080,17 +10717,17 @@
       <c r="W19" s="11"/>
       <c r="X19" s="11"/>
       <c r="Y19" s="11"/>
-      <c r="Z19" s="14"/>
-      <c r="AA19" s="14" t="str">
+      <c r="Z19" s="15"/>
+      <c r="AA19" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00190611")</f>
         <v>U00190611</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="13">
+      <c r="A20" s="14">
         <v>19.0</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="14" t="s">
         <v>102</v>
       </c>
       <c r="C20" s="10">
@@ -9137,32 +10774,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="N20" s="11"/>
+      <c r="N20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
+      <c r="P20" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
+      <c r="R20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
+      </c>
       <c r="S20" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1)</f>
-        <v>1.1</v>
-      </c>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
+      <c r="T20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="U20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="V20" s="11"/>
       <c r="W20" s="11"/>
       <c r="X20" s="11"/>
       <c r="Y20" s="11"/>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14" t="str">
+      <c r="Z20" s="15"/>
+      <c r="AA20" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00190571")</f>
         <v>U00190571</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13">
+      <c r="A21" s="14">
         <v>20.0</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="14" t="s">
         <v>103</v>
       </c>
       <c r="C21" s="10">
@@ -9209,32 +10861,47 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="N21" s="11"/>
+      <c r="N21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
+      </c>
       <c r="O21" s="11"/>
-      <c r="P21" s="11"/>
+      <c r="P21" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="Q21" s="11"/>
-      <c r="R21" s="11"/>
+      <c r="R21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
+        <v>1.3</v>
+      </c>
       <c r="S21" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
-        <v>1.4</v>
-      </c>
-      <c r="T21" s="11"/>
-      <c r="U21" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
+      </c>
+      <c r="T21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
+      </c>
+      <c r="U21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="V21" s="11"/>
       <c r="W21" s="11"/>
       <c r="X21" s="11"/>
       <c r="Y21" s="11"/>
-      <c r="Z21" s="14"/>
-      <c r="AA21" s="14" t="str">
+      <c r="Z21" s="15"/>
+      <c r="AA21" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00195213")</f>
         <v>U00195213</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13">
+      <c r="A22" s="14">
         <v>21.0</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="14" t="s">
         <v>104</v>
       </c>
       <c r="C22" s="10">
@@ -9281,110 +10948,146 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="N22" s="11"/>
+      <c r="N22" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
+      </c>
       <c r="O22" s="11"/>
-      <c r="P22" s="11"/>
+      <c r="P22" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
       <c r="Q22" s="11"/>
-      <c r="R22" s="11"/>
+      <c r="R22" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
+      </c>
       <c r="S22" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
-        <v>1.6</v>
-      </c>
-      <c r="T22" s="11"/>
-      <c r="U22" s="11"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
+      </c>
+      <c r="T22" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="U22" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="V22" s="11"/>
       <c r="W22" s="11"/>
       <c r="X22" s="11"/>
       <c r="Y22" s="11"/>
-      <c r="Z22" s="14"/>
-      <c r="AA22" s="14" t="str">
+      <c r="Z22" s="15"/>
+      <c r="AA22" s="15" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00184452")</f>
         <v>U00184452</v>
       </c>
     </row>
     <row r="23">
-      <c r="C23" s="15">
+      <c r="C23" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4809523809523806)</f>
         <v>3.480952381</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.576190476190476)</f>
         <v>2.576190476</v>
       </c>
-      <c r="E23" s="15">
+      <c r="E23" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5619047619047617)</f>
         <v>3.561904762</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1809523809523808)</f>
         <v>3.180952381</v>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7285714285714286)</f>
         <v>3.728571429</v>
       </c>
-      <c r="H23" s="15">
+      <c r="H23" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8714285714285706)</f>
         <v>3.871428571</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I23" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7428571428571424)</f>
         <v>2.742857143</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J23" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8857142857142852)</f>
         <v>2.885714286</v>
       </c>
-      <c r="K23" s="15">
+      <c r="K23" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5952380952380953)</f>
         <v>2.595238095</v>
       </c>
-      <c r="L23" s="15">
+      <c r="L23" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4476190476190474)</f>
         <v>2.447619048</v>
       </c>
-      <c r="M23" s="11"/>
-      <c r="N23" s="11"/>
+      <c r="M23" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9904761904761905)</f>
+        <v>3.99047619</v>
+      </c>
+      <c r="N23" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.144444444444444)</f>
+        <v>3.144444444</v>
+      </c>
       <c r="O23" s="11"/>
-      <c r="P23" s="11"/>
+      <c r="P23" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.377777777777778)</f>
+        <v>3.377777778</v>
+      </c>
       <c r="Q23" s="11"/>
-      <c r="R23" s="11"/>
-      <c r="S23" s="11"/>
-      <c r="T23" s="11"/>
-      <c r="U23" s="11"/>
+      <c r="R23" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6277777777777778)</f>
+        <v>1.627777778</v>
+      </c>
+      <c r="S23" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.266666666666667)</f>
+        <v>2.266666667</v>
+      </c>
+      <c r="T23" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9444444444444446)</f>
+        <v>3.944444444</v>
+      </c>
+      <c r="U23" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.761111111111111)</f>
+        <v>2.761111111</v>
+      </c>
       <c r="V23" s="11"/>
       <c r="W23" s="11"/>
       <c r="X23" s="11"/>
       <c r="Y23" s="11"/>
-      <c r="Z23" s="14"/>
-      <c r="AA23" s="14"/>
+      <c r="Z23" s="15"/>
+      <c r="AA23" s="15"/>
     </row>
     <row r="24">
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="14"/>
-      <c r="X24" s="14"/>
-      <c r="Y24" s="14"/>
-      <c r="Z24" s="14"/>
-      <c r="AA24" s="14"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="15"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="15"/>
+      <c r="Q24" s="15"/>
+      <c r="R24" s="15"/>
+      <c r="S24" s="15"/>
+      <c r="T24" s="15"/>
+      <c r="U24" s="15"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="15"/>
+      <c r="Y24" s="15"/>
+      <c r="Z24" s="15"/>
+      <c r="AA24" s="15"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/app_notas.xlsx
+++ b/app_notas.xlsx
@@ -3070,10 +3070,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M2" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M2" s="11"/>
       <c r="N2" s="11"/>
       <c r="O2" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -3081,12 +3078,12 @@
       </c>
       <c r="P2" s="11"/>
       <c r="Q2" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
-        <v>1.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7)</f>
+        <v>0.7</v>
       </c>
       <c r="R2" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="S2" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3163,10 +3160,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M3" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M3" s="11"/>
       <c r="N3" s="11"/>
       <c r="O3" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
@@ -3174,12 +3168,12 @@
       </c>
       <c r="P3" s="11"/>
       <c r="Q3" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="R3" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
+        <v>1.3</v>
       </c>
       <c r="S3" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -3259,10 +3253,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="M4" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M4" s="11"/>
       <c r="N4" s="11"/>
       <c r="O4" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -3270,12 +3261,12 @@
       </c>
       <c r="P4" s="11"/>
       <c r="Q4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
+      </c>
+      <c r="R4" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
         <v>1.9</v>
-      </c>
-      <c r="R4" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
       </c>
       <c r="S4" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3352,10 +3343,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M5" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M5" s="11"/>
       <c r="N5" s="11"/>
       <c r="O5" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
@@ -3363,12 +3351,12 @@
       </c>
       <c r="P5" s="11"/>
       <c r="Q5" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
+        <v>0.8</v>
       </c>
       <c r="R5" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
       </c>
       <c r="S5" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3448,10 +3436,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="M6" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M6" s="11"/>
       <c r="N6" s="11"/>
       <c r="O6" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
@@ -3459,12 +3444,12 @@
       </c>
       <c r="P6" s="11"/>
       <c r="Q6" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="R6" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
       </c>
       <c r="S6" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3544,10 +3529,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M7" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M7" s="11"/>
       <c r="N7" s="11"/>
       <c r="O7" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
@@ -3555,12 +3537,12 @@
       </c>
       <c r="P7" s="11"/>
       <c r="Q7" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9)</f>
+        <v>0.9</v>
       </c>
       <c r="R7" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="S7" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -3640,10 +3622,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M8" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M8" s="11"/>
       <c r="N8" s="11"/>
       <c r="O8" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
@@ -3651,12 +3630,12 @@
       </c>
       <c r="P8" s="11"/>
       <c r="Q8" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9)</f>
+        <v>0.9</v>
       </c>
       <c r="R8" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
-        <v>2.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="S8" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
@@ -3736,10 +3715,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="M9" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M9" s="11"/>
       <c r="N9" s="11"/>
       <c r="O9" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3747,12 +3723,12 @@
       </c>
       <c r="P9" s="11"/>
       <c r="Q9" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="R9" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
-        <v>3.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
       </c>
       <c r="S9" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3832,10 +3808,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M10" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M10" s="11"/>
       <c r="N10" s="11"/>
       <c r="O10" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3843,12 +3816,12 @@
       </c>
       <c r="P10" s="11"/>
       <c r="Q10" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="R10" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="S10" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3928,10 +3901,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M11" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M11" s="11"/>
       <c r="N11" s="11"/>
       <c r="O11" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -3939,12 +3909,12 @@
       </c>
       <c r="P11" s="11"/>
       <c r="Q11" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="R11" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="S11" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -4021,10 +3991,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="M12" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M12" s="11"/>
       <c r="N12" s="11"/>
       <c r="O12" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
@@ -4032,12 +3999,12 @@
       </c>
       <c r="P12" s="11"/>
       <c r="Q12" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="R12" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
-        <v>2.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="S12" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -4117,10 +4084,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="M13" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M13" s="11"/>
       <c r="N13" s="11"/>
       <c r="O13" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
@@ -4128,12 +4092,12 @@
       </c>
       <c r="P13" s="11"/>
       <c r="Q13" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
+        <v>0.8</v>
       </c>
       <c r="R13" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
-        <v>2.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="S13" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4213,10 +4177,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M14" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M14" s="11"/>
       <c r="N14" s="11"/>
       <c r="O14" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
@@ -4224,12 +4185,12 @@
       </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9)</f>
+        <v>0.9</v>
       </c>
       <c r="R14" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="S14" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -4309,10 +4270,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="M15" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M15" s="11"/>
       <c r="N15" s="11"/>
       <c r="O15" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
@@ -4320,12 +4278,12 @@
       </c>
       <c r="P15" s="11"/>
       <c r="Q15" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
+        <v>0.8</v>
       </c>
       <c r="R15" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
-        <v>2.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="S15" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4402,10 +4360,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M16" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M16" s="11"/>
       <c r="N16" s="11"/>
       <c r="O16" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
@@ -4413,12 +4368,12 @@
       </c>
       <c r="P16" s="11"/>
       <c r="Q16" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="R16" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
       </c>
       <c r="S16" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -4564,10 +4519,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="M18" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M18" s="11"/>
       <c r="N18" s="11"/>
       <c r="O18" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
@@ -4575,12 +4527,12 @@
       </c>
       <c r="P18" s="11"/>
       <c r="Q18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
+        <v>0.8</v>
+      </c>
+      <c r="R18" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
         <v>1.7</v>
-      </c>
-      <c r="R18" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
       </c>
       <c r="S18" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4660,10 +4612,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M19" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M19" s="11"/>
       <c r="N19" s="11"/>
       <c r="O19" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4671,12 +4620,12 @@
       </c>
       <c r="P19" s="11"/>
       <c r="Q19" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="R19" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
-        <v>3.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
       </c>
       <c r="S19" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4756,10 +4705,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="M20" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M20" s="11"/>
       <c r="N20" s="11"/>
       <c r="O20" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -4767,12 +4713,12 @@
       </c>
       <c r="P20" s="11"/>
       <c r="Q20" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="R20" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
       </c>
       <c r="S20" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4849,10 +4795,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M21" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M21" s="11"/>
       <c r="N21" s="11"/>
       <c r="O21" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -4860,12 +4803,12 @@
       </c>
       <c r="P21" s="11"/>
       <c r="Q21" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="R21" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
       </c>
       <c r="S21" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4939,10 +4882,7 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.575)</f>
         <v>3.575</v>
       </c>
-      <c r="M22" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
-      </c>
+      <c r="M22" s="13"/>
       <c r="N22" s="13"/>
       <c r="O22" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5894736842105255)</f>
@@ -4950,12 +4890,12 @@
       </c>
       <c r="P22" s="13"/>
       <c r="Q22" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.826315789473684)</f>
-        <v>1.826315789</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9263157894736843)</f>
+        <v>0.9263157895</v>
       </c>
       <c r="R22" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.357894736842105)</f>
+        <v>2.357894737</v>
       </c>
       <c r="S22" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2631578947368425)</f>

--- a/app_notas.xlsx
+++ b/app_notas.xlsx
@@ -7832,8 +7832,8 @@
         <v>0</v>
       </c>
       <c r="L6" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="M6" s="11"/>
       <c r="N6" s="12">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="O6" s="11"/>
       <c r="P6" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
-        <v>1.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
+        <v>1.3</v>
       </c>
       <c r="Q6" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="R6" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -8792,8 +8792,8 @@
         <v>3.266666667</v>
       </c>
       <c r="L17" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1846153846153844)</f>
-        <v>3.184615385</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.223076923076923)</f>
+        <v>3.223076923</v>
       </c>
       <c r="M17" s="15"/>
       <c r="N17" s="16">
@@ -8802,12 +8802,12 @@
       </c>
       <c r="O17" s="15"/>
       <c r="P17" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5357142857142858)</f>
-        <v>1.535714286</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.542857142857143)</f>
+        <v>1.542857143</v>
       </c>
       <c r="Q17" s="16">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4785714285714286)</f>
-        <v>2.478571429</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.485714285714286)</f>
+        <v>2.485714286</v>
       </c>
       <c r="R17" s="16">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3866666666666663)</f>

--- a/app_notas.xlsx
+++ b/app_notas.xlsx
@@ -3070,7 +3070,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M2" s="11"/>
+      <c r="M2" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="N2" s="11"/>
       <c r="O2" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -3078,12 +3081,12 @@
       </c>
       <c r="P2" s="11"/>
       <c r="Q2" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7)</f>
-        <v>0.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="R2" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
+        <v>3.1</v>
       </c>
       <c r="S2" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3160,7 +3163,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M3" s="11"/>
+      <c r="M3" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N3" s="11"/>
       <c r="O3" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
@@ -3168,12 +3174,12 @@
       </c>
       <c r="P3" s="11"/>
       <c r="Q3" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
       </c>
       <c r="R3" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
-        <v>1.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
       </c>
       <c r="S3" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -3253,7 +3259,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="M4" s="11"/>
+      <c r="M4" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="N4" s="11"/>
       <c r="O4" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -3261,12 +3270,12 @@
       </c>
       <c r="P4" s="11"/>
       <c r="Q4" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="R4" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="S4" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3343,7 +3352,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M5" s="11"/>
+      <c r="M5" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="N5" s="11"/>
       <c r="O5" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
@@ -3351,12 +3363,12 @@
       </c>
       <c r="P5" s="11"/>
       <c r="Q5" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
-        <v>0.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="R5" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
       </c>
       <c r="S5" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3436,7 +3448,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="M6" s="11"/>
+      <c r="M6" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
+      </c>
       <c r="N6" s="11"/>
       <c r="O6" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
@@ -3444,12 +3459,12 @@
       </c>
       <c r="P6" s="11"/>
       <c r="Q6" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="R6" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="S6" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3529,7 +3544,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M7" s="11"/>
+      <c r="M7" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="N7" s="11"/>
       <c r="O7" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
@@ -3537,12 +3555,12 @@
       </c>
       <c r="P7" s="11"/>
       <c r="Q7" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9)</f>
-        <v>0.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="R7" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
       </c>
       <c r="S7" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -3622,7 +3640,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M8" s="11"/>
+      <c r="M8" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
+      </c>
       <c r="N8" s="11"/>
       <c r="O8" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
@@ -3630,12 +3651,12 @@
       </c>
       <c r="P8" s="11"/>
       <c r="Q8" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9)</f>
-        <v>0.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
       </c>
       <c r="R8" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
       </c>
       <c r="S8" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
@@ -3715,7 +3736,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="M9" s="11"/>
+      <c r="M9" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="N9" s="11"/>
       <c r="O9" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3723,12 +3747,12 @@
       </c>
       <c r="P9" s="11"/>
       <c r="Q9" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="R9" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
       </c>
       <c r="S9" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3808,7 +3832,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M10" s="11"/>
+      <c r="M10" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N10" s="11"/>
       <c r="O10" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3816,12 +3843,12 @@
       </c>
       <c r="P10" s="11"/>
       <c r="Q10" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
       </c>
       <c r="R10" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
       </c>
       <c r="S10" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3901,7 +3928,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M11" s="11"/>
+      <c r="M11" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="N11" s="11"/>
       <c r="O11" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -3909,12 +3939,12 @@
       </c>
       <c r="P11" s="11"/>
       <c r="Q11" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="R11" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
       </c>
       <c r="S11" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -3991,7 +4021,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="M12" s="11"/>
+      <c r="M12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="N12" s="11"/>
       <c r="O12" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
@@ -3999,12 +4032,12 @@
       </c>
       <c r="P12" s="11"/>
       <c r="Q12" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
-      </c>
-      <c r="R12" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
         <v>2.2</v>
+      </c>
+      <c r="R12" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
       </c>
       <c r="S12" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -4084,7 +4117,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="M13" s="11"/>
+      <c r="M13" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
       <c r="N13" s="11"/>
       <c r="O13" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
@@ -4092,12 +4128,12 @@
       </c>
       <c r="P13" s="11"/>
       <c r="Q13" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
-        <v>0.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="R13" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
       </c>
       <c r="S13" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4177,7 +4213,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="M14" s="11"/>
+      <c r="M14" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="N14" s="11"/>
       <c r="O14" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
@@ -4185,12 +4224,12 @@
       </c>
       <c r="P14" s="11"/>
       <c r="Q14" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9)</f>
-        <v>0.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
       </c>
       <c r="R14" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
       </c>
       <c r="S14" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -4270,7 +4309,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="M15" s="11"/>
+      <c r="M15" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="N15" s="11"/>
       <c r="O15" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
@@ -4278,12 +4320,12 @@
       </c>
       <c r="P15" s="11"/>
       <c r="Q15" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
-        <v>0.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
       </c>
       <c r="R15" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
       </c>
       <c r="S15" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4360,7 +4402,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M16" s="11"/>
+      <c r="M16" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
+      </c>
       <c r="N16" s="11"/>
       <c r="O16" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
@@ -4368,12 +4413,12 @@
       </c>
       <c r="P16" s="11"/>
       <c r="Q16" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="R16" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="S16" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -4519,24 +4564,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="M18" s="11"/>
+      <c r="M18" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="N18" s="11"/>
       <c r="O18" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="P18" s="11"/>
       <c r="Q18" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.8)</f>
-        <v>0.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
       </c>
       <c r="R18" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="S18" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="T18" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4612,7 +4660,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M19" s="11"/>
+      <c r="M19" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="N19" s="11"/>
       <c r="O19" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4620,12 +4671,12 @@
       </c>
       <c r="P19" s="11"/>
       <c r="Q19" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="R19" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
       </c>
       <c r="S19" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4705,7 +4756,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="M20" s="11"/>
+      <c r="M20" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="N20" s="11"/>
       <c r="O20" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -4713,12 +4767,12 @@
       </c>
       <c r="P20" s="11"/>
       <c r="Q20" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="R20" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="S20" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4795,7 +4849,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="M21" s="11"/>
+      <c r="M21" s="11">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="N21" s="11"/>
       <c r="O21" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -4803,12 +4860,12 @@
       </c>
       <c r="P21" s="11"/>
       <c r="Q21" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
-        <v>1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="R21" s="11">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
       </c>
       <c r="S21" s="11">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4882,24 +4939,27 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.575)</f>
         <v>3.575</v>
       </c>
-      <c r="M22" s="13"/>
+      <c r="M22" s="12">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9578947368421047)</f>
+        <v>3.957894737</v>
+      </c>
       <c r="N22" s="13"/>
       <c r="O22" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5894736842105255)</f>
-        <v>4.589473684</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.652631578947368)</f>
+        <v>4.652631579</v>
       </c>
       <c r="P22" s="13"/>
       <c r="Q22" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9263157894736843)</f>
-        <v>0.9263157895</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.126315789473684)</f>
+        <v>2.126315789</v>
       </c>
       <c r="R22" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.357894736842105)</f>
-        <v>2.357894737</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9526315789473685)</f>
+        <v>2.952631579</v>
       </c>
       <c r="S22" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2631578947368425)</f>
-        <v>4.263157895</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.526315789473684)</f>
+        <v>4.526315789</v>
       </c>
       <c r="T22" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.405263157894737)</f>

--- a/app_notas.xlsx
+++ b/app_notas.xlsx
@@ -959,8 +959,8 @@
         <v>3</v>
       </c>
       <c r="O2" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="P2" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -971,12 +971,12 @@
         <v>4.1</v>
       </c>
       <c r="R2" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
-        <v>2.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="S2" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
-        <v>2.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="T2" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -986,7 +986,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="V2" s="13"/>
+      <c r="V2" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W2" s="13"/>
       <c r="X2" s="13"/>
       <c r="Y2" s="13"/>
@@ -1052,8 +1055,8 @@
         <v>3.7</v>
       </c>
       <c r="O3" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
       </c>
       <c r="P3" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -1064,12 +1067,12 @@
         <v>4.2</v>
       </c>
       <c r="R3" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
       </c>
       <c r="S3" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
       </c>
       <c r="T3" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -1079,7 +1082,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="V3" s="13"/>
+      <c r="V3" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
       <c r="Y3" s="13"/>
@@ -1145,24 +1151,24 @@
         <v>5</v>
       </c>
       <c r="O4" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="P4" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="Q4" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R4" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="S4" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
-        <v>4.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="T4" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -1172,7 +1178,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
       </c>
-      <c r="V4" s="13"/>
+      <c r="V4" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W4" s="13"/>
       <c r="X4" s="13"/>
       <c r="Y4" s="13"/>
@@ -1238,24 +1247,24 @@
         <v>4.8</v>
       </c>
       <c r="O5" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="P5" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Q5" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
       <c r="R5" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="S5" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="T5" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -1265,7 +1274,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
-      <c r="V5" s="13"/>
+      <c r="V5" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W5" s="13"/>
       <c r="X5" s="13"/>
       <c r="Y5" s="13"/>
@@ -1331,8 +1343,8 @@
         <v>4.9</v>
       </c>
       <c r="O6" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="P6" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
@@ -1343,12 +1355,12 @@
         <v>3.8</v>
       </c>
       <c r="R6" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
-        <v>3.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="S6" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
       </c>
       <c r="T6" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -1358,7 +1370,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
         <v>3.4</v>
       </c>
-      <c r="V6" s="13"/>
+      <c r="V6" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="W6" s="13"/>
       <c r="X6" s="13"/>
       <c r="Y6" s="13"/>
@@ -1424,24 +1439,24 @@
         <v>0.4</v>
       </c>
       <c r="O7" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="P7" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="Q7" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
       <c r="R7" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="S7" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
       </c>
       <c r="T7" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
@@ -1451,7 +1466,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
         <v>4.1</v>
       </c>
-      <c r="V7" s="13"/>
+      <c r="V7" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W7" s="13"/>
       <c r="X7" s="13"/>
       <c r="Y7" s="13"/>
@@ -1517,25 +1535,25 @@
         <v>5</v>
       </c>
       <c r="O8" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
       </c>
       <c r="P8" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="Q8" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R8" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
+      </c>
+      <c r="S8" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
         <v>3.3</v>
       </c>
-      <c r="S8" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
-        <v>3.1</v>
-      </c>
       <c r="T8" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -1544,7 +1562,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="V8" s="13"/>
+      <c r="V8" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W8" s="13"/>
       <c r="X8" s="13"/>
       <c r="Y8" s="13"/>
@@ -1610,24 +1631,24 @@
         <v>4.6</v>
       </c>
       <c r="O9" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="P9" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="Q9" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R9" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="S9" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="T9" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
@@ -1637,7 +1658,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="V9" s="13"/>
+      <c r="V9" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="W9" s="13"/>
       <c r="X9" s="13"/>
       <c r="Y9" s="13"/>
@@ -1703,24 +1727,24 @@
         <v>2.3</v>
       </c>
       <c r="O10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="P10" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="Q10" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
         <v>4.1</v>
       </c>
       <c r="R10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
+        <v>3.1</v>
       </c>
       <c r="S10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="T10" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -1730,7 +1754,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="V10" s="13"/>
+      <c r="V10" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="W10" s="13"/>
       <c r="X10" s="13"/>
       <c r="Y10" s="13"/>
@@ -1796,24 +1823,24 @@
         <v>3.4</v>
       </c>
       <c r="O11" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="P11" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
-        <v>4.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="Q11" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
         <v>4.1</v>
       </c>
       <c r="R11" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
-        <v>2.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="S11" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="T11" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
@@ -1823,7 +1850,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
         <v>3.9</v>
       </c>
-      <c r="V11" s="13"/>
+      <c r="V11" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W11" s="13"/>
       <c r="X11" s="13"/>
       <c r="Y11" s="13"/>
@@ -1889,24 +1919,24 @@
         <v>5</v>
       </c>
       <c r="O12" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="P12" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="Q12" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R12" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="S12" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="T12" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -1916,7 +1946,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="V12" s="13"/>
+      <c r="V12" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W12" s="13"/>
       <c r="X12" s="13"/>
       <c r="Y12" s="13"/>
@@ -1982,24 +2015,24 @@
         <v>4</v>
       </c>
       <c r="O13" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.2)</f>
+        <v>1.2</v>
       </c>
       <c r="P13" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="Q13" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
       <c r="R13" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="S13" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="T13" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -2009,7 +2042,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="V13" s="13"/>
+      <c r="V13" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W13" s="13"/>
       <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
@@ -2075,24 +2111,24 @@
         <v>3</v>
       </c>
       <c r="O14" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
       </c>
       <c r="P14" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="Q14" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R14" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
       </c>
       <c r="S14" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="T14" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2102,7 +2138,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="V14" s="13"/>
+      <c r="V14" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W14" s="13"/>
       <c r="X14" s="13"/>
       <c r="Y14" s="13"/>
@@ -2168,8 +2207,8 @@
         <v>3.2</v>
       </c>
       <c r="O15" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.9)</f>
+        <v>0.9</v>
       </c>
       <c r="P15" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -2180,13 +2219,13 @@
         <v>4</v>
       </c>
       <c r="R15" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
-        <v>2.7</v>
-      </c>
-      <c r="S15" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
+      <c r="S15" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="T15" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -2195,7 +2234,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="V15" s="13"/>
+      <c r="V15" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="W15" s="13"/>
       <c r="X15" s="13"/>
       <c r="Y15" s="13"/>
@@ -2288,7 +2330,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="V16" s="13"/>
+      <c r="V16" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="W16" s="13"/>
       <c r="X16" s="13"/>
       <c r="Y16" s="13"/>
@@ -2354,8 +2399,8 @@
         <v>4</v>
       </c>
       <c r="O17" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="P17" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -2366,12 +2411,12 @@
         <v>4.1</v>
       </c>
       <c r="R17" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
       </c>
       <c r="S17" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
       </c>
       <c r="T17" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -2381,7 +2426,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="V17" s="13"/>
+      <c r="V17" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
       <c r="Y17" s="13"/>
@@ -2447,24 +2495,24 @@
         <v>3.5</v>
       </c>
       <c r="O18" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="P18" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="Q18" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R18" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="S18" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="T18" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -2474,7 +2522,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="V18" s="13"/>
+      <c r="V18" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W18" s="13"/>
       <c r="X18" s="13"/>
       <c r="Y18" s="13"/>
@@ -2540,24 +2591,24 @@
         <v>3</v>
       </c>
       <c r="O19" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
       </c>
       <c r="P19" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
-        <v>4.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="Q19" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R19" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="S19" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="T19" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
@@ -2567,7 +2618,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="V19" s="13"/>
+      <c r="V19" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
       <c r="Y19" s="13"/>
@@ -2633,25 +2687,25 @@
         <v>3</v>
       </c>
       <c r="O20" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="P20" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="Q20" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R20" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
-      </c>
-      <c r="S20" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
+      <c r="S20" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
       <c r="T20" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -2660,7 +2714,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="V20" s="13"/>
+      <c r="V20" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="W20" s="13"/>
       <c r="X20" s="13"/>
       <c r="Y20" s="13"/>
@@ -2726,8 +2783,8 @@
         <v>4.8</v>
       </c>
       <c r="O21" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="P21" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -2738,12 +2795,12 @@
         <v>4.1</v>
       </c>
       <c r="R21" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
+      </c>
+      <c r="S21" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
-      </c>
-      <c r="S21" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
-        <v>3.1</v>
       </c>
       <c r="T21" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -2753,7 +2810,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
-      <c r="V21" s="13"/>
+      <c r="V21" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="W21" s="13"/>
       <c r="X21" s="13"/>
       <c r="Y21" s="13"/>
@@ -2819,8 +2879,8 @@
         <v>5</v>
       </c>
       <c r="O22" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="P22" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -2831,12 +2891,12 @@
         <v>4.3</v>
       </c>
       <c r="R22" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="S22" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
-        <v>4.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="T22" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -2846,7 +2906,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="V22" s="13"/>
+      <c r="V22" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="W22" s="13"/>
       <c r="X22" s="13"/>
       <c r="Y22" s="13"/>
@@ -2912,24 +2975,24 @@
         <v>3.6</v>
       </c>
       <c r="O23" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="P23" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="Q23" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R23" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="S23" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
-        <v>3.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="T23" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -2939,7 +3002,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
       </c>
-      <c r="V23" s="13"/>
+      <c r="V23" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W23" s="13"/>
       <c r="X23" s="13"/>
       <c r="Y23" s="13"/>
@@ -3005,8 +3071,8 @@
         <v>1</v>
       </c>
       <c r="O24" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="P24" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -3017,13 +3083,13 @@
         <v>4.3</v>
       </c>
       <c r="R24" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
-      </c>
-      <c r="S24" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
         <v>3.1</v>
       </c>
+      <c r="S24" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
       <c r="T24" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -3032,7 +3098,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="V24" s="13"/>
+      <c r="V24" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
+      </c>
       <c r="W24" s="13"/>
       <c r="X24" s="13"/>
       <c r="Y24" s="13"/>
@@ -3247,24 +3316,24 @@
         <v>5</v>
       </c>
       <c r="N2" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="O2" s="14">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="P2" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="Q2" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
       </c>
-      <c r="P2" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
-      </c>
-      <c r="Q2" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
-      </c>
       <c r="R2" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
-        <v>3.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
       </c>
       <c r="S2" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3286,7 +3355,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="X2" s="13"/>
+      <c r="X2" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Y2" s="13" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00194619")</f>
         <v>U00194619</v>
@@ -3349,24 +3421,24 @@
         <v>3</v>
       </c>
       <c r="N3" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="O3" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
-        <v>3.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="P3" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
       <c r="Q3" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="R3" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
       </c>
       <c r="S3" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -3385,10 +3457,13 @@
         <v>5</v>
       </c>
       <c r="W3" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="X3" s="13"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="X3" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Y3" s="13" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00193956")</f>
         <v>U00193956</v>
@@ -3454,8 +3529,8 @@
         <v>4.5</v>
       </c>
       <c r="N4" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="O4" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -3466,12 +3541,12 @@
         <v>4.7</v>
       </c>
       <c r="Q4" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
+      </c>
+      <c r="R4" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
         <v>3.3</v>
-      </c>
-      <c r="R4" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
       </c>
       <c r="S4" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3493,7 +3568,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="X4" s="13"/>
+      <c r="X4" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="Y4" s="13" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00194124")</f>
         <v>U00194124</v>
@@ -3556,24 +3634,24 @@
         <v>5</v>
       </c>
       <c r="N5" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="O5" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="P5" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
       </c>
       <c r="Q5" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="R5" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
-        <v>4.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="S5" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3595,7 +3673,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="X5" s="13"/>
+      <c r="X5" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
+      </c>
       <c r="Y5" s="13" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00191934")</f>
         <v>U00191934</v>
@@ -3661,8 +3742,8 @@
         <v>4.1</v>
       </c>
       <c r="N6" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="O6" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
@@ -3673,12 +3754,12 @@
         <v>4.5</v>
       </c>
       <c r="Q6" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
-        <v>3.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="R6" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
-        <v>3.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="S6" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3700,7 +3781,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="X6" s="13"/>
+      <c r="X6" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Y6" s="13" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00193915")</f>
         <v>U00193915</v>
@@ -3766,8 +3850,8 @@
         <v>3.5</v>
       </c>
       <c r="N7" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
       </c>
       <c r="O7" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
@@ -3778,12 +3862,12 @@
         <v>4.5</v>
       </c>
       <c r="Q7" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="R7" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="S7" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -3805,7 +3889,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="X7" s="13"/>
+      <c r="X7" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="Y7" s="13" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00193113")</f>
         <v>U00193113</v>
@@ -3871,24 +3958,24 @@
         <v>3.9</v>
       </c>
       <c r="N8" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
+        <v>1.9</v>
       </c>
       <c r="O8" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="P8" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
       <c r="Q8" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
       </c>
       <c r="R8" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
       </c>
       <c r="S8" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
@@ -3910,7 +3997,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="X8" s="13"/>
+      <c r="X8" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Y8" s="13" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00192477")</f>
         <v>U00192477</v>
@@ -3976,8 +4066,8 @@
         <v>5</v>
       </c>
       <c r="N9" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="O9" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -3988,12 +4078,12 @@
         <v>4.7</v>
       </c>
       <c r="Q9" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
-        <v>3.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="R9" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
-        <v>4.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="S9" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4015,7 +4105,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="X9" s="13"/>
+      <c r="X9" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Y9" s="13" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00192526")</f>
         <v>U00192526</v>
@@ -4081,8 +4174,8 @@
         <v>3</v>
       </c>
       <c r="N10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="O10" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4093,12 +4186,12 @@
         <v>4.5</v>
       </c>
       <c r="Q10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="R10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
-        <v>3.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="S10" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4120,7 +4213,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="X10" s="13"/>
+      <c r="X10" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Y10" s="13" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00193149")</f>
         <v>U00193149</v>
@@ -4186,8 +4282,8 @@
         <v>3.5</v>
       </c>
       <c r="N11" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
+        <v>2.1</v>
       </c>
       <c r="O11" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -4198,12 +4294,12 @@
         <v>4.3</v>
       </c>
       <c r="Q11" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="R11" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
       </c>
       <c r="S11" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -4225,7 +4321,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="X11" s="13"/>
+      <c r="X11" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Y11" s="13" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00192726")</f>
         <v>U00192726</v>
@@ -4288,8 +4387,8 @@
         <v>4</v>
       </c>
       <c r="N12" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="O12" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
@@ -4300,12 +4399,12 @@
         <v>4.4</v>
       </c>
       <c r="Q12" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="R12" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
       </c>
       <c r="S12" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -4327,7 +4426,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="X12" s="13"/>
+      <c r="X12" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
+      </c>
       <c r="Y12" s="13" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00194037")</f>
         <v>U00194037</v>
@@ -4393,8 +4495,8 @@
         <v>3.8</v>
       </c>
       <c r="N13" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="O13" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
@@ -4405,12 +4507,12 @@
         <v>4.6</v>
       </c>
       <c r="Q13" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
       </c>
       <c r="R13" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
       </c>
       <c r="S13" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4432,7 +4534,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="X13" s="13"/>
+      <c r="X13" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="Y13" s="13" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00192705")</f>
         <v>U00192705</v>
@@ -4498,24 +4603,24 @@
         <v>2.5</v>
       </c>
       <c r="N14" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="O14" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="P14" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
         <v>4.7</v>
       </c>
       <c r="Q14" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
-      </c>
-      <c r="R14" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
+      </c>
+      <c r="R14" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="S14" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -4537,7 +4642,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="X14" s="13"/>
+      <c r="X14" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
+      </c>
       <c r="Y14" s="13" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00193858")</f>
         <v>U00193858</v>
@@ -4603,24 +4711,24 @@
         <v>2.5</v>
       </c>
       <c r="N15" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="O15" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
-      </c>
-      <c r="P15" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
-      </c>
-      <c r="Q15" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
         <v>2.5</v>
       </c>
+      <c r="O15" s="14">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
+      <c r="P15" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="Q15" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
+      </c>
       <c r="R15" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
-        <v>3.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="S15" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -4642,7 +4750,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="X15" s="13"/>
+      <c r="X15" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Y15" s="13" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00192059")</f>
         <v>U00192059</v>
@@ -4705,8 +4816,8 @@
         <v>3.9</v>
       </c>
       <c r="N16" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="O16" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
@@ -4717,12 +4828,12 @@
         <v>4.5</v>
       </c>
       <c r="Q16" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
-        <v>3.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="R16" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
-        <v>3.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="S16" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -4744,7 +4855,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="X16" s="13"/>
+      <c r="X16" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Y16" s="13" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00192970")</f>
         <v>U00192970</v>
@@ -4876,8 +4990,8 @@
         <v>3</v>
       </c>
       <c r="N18" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="O18" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
@@ -4888,12 +5002,12 @@
         <v>4.7</v>
       </c>
       <c r="Q18" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="R18" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="S18" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4915,7 +5029,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="X18" s="13"/>
+      <c r="X18" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
       <c r="Y18" s="13" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00186645")</f>
         <v>U00186645</v>
@@ -4981,8 +5098,8 @@
         <v>5</v>
       </c>
       <c r="N19" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="O19" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -4993,12 +5110,12 @@
         <v>4.7</v>
       </c>
       <c r="Q19" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
-        <v>3.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="R19" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
-        <v>4.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="S19" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -5020,7 +5137,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="X19" s="13"/>
+      <c r="X19" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="Y19" s="13" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00191929")</f>
         <v>U00191929</v>
@@ -5086,24 +5206,24 @@
         <v>5</v>
       </c>
       <c r="N20" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
+        <v>1.6</v>
       </c>
       <c r="O20" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="P20" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
       <c r="Q20" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
-      </c>
-      <c r="R20" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
         <v>3.7</v>
+      </c>
+      <c r="R20" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
       </c>
       <c r="S20" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -5125,7 +5245,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="X20" s="13"/>
+      <c r="X20" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="Y20" s="13" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00194227")</f>
         <v>U00194227</v>
@@ -5188,8 +5311,8 @@
         <v>5</v>
       </c>
       <c r="N21" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="O21" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -5200,12 +5323,12 @@
         <v>4.5</v>
       </c>
       <c r="Q21" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
-        <v>3.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="R21" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
-        <v>4.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="S21" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -5227,7 +5350,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="X21" s="13"/>
+      <c r="X21" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="Y21" s="13" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"U00194368")</f>
         <v>U00194368</v>
@@ -5287,24 +5413,24 @@
         <v>3.957894737</v>
       </c>
       <c r="N22" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1315789473684212)</f>
+        <v>3.131578947</v>
       </c>
       <c r="O22" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.563157894736841)</f>
-        <v>4.563157895</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.636842105263158)</f>
+        <v>4.636842105</v>
       </c>
       <c r="P22" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5473684210526315)</f>
         <v>4.547368421</v>
       </c>
       <c r="Q22" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0157894736842104)</f>
-        <v>3.015789474</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.96842105263158)</f>
+        <v>3.968421053</v>
       </c>
       <c r="R22" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4000000000000004)</f>
-        <v>3.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8684210526315796)</f>
+        <v>3.868421053</v>
       </c>
       <c r="S22" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.526315789473684)</f>
@@ -5323,10 +5449,13 @@
         <v>5</v>
       </c>
       <c r="W22" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.157894736842105)</f>
-        <v>4.157894737</v>
-      </c>
-      <c r="X22" s="15"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.421052631578948)</f>
+        <v>4.421052632</v>
+      </c>
+      <c r="X22" s="14">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.742105263157894)</f>
+        <v>4.742105263</v>
+      </c>
       <c r="Y22" s="15"/>
       <c r="Z22" s="19"/>
       <c r="AA22" s="19"/>
@@ -5568,24 +5697,24 @@
         <v>1.6</v>
       </c>
       <c r="O2" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="P2" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
-        <v>3.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Q2" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R2" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
       </c>
       <c r="S2" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
       </c>
       <c r="T2" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
@@ -5595,7 +5724,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="V2" s="13"/>
+      <c r="V2" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W2" s="13"/>
       <c r="X2" s="13"/>
       <c r="Y2" s="13"/>
@@ -5661,24 +5793,24 @@
         <v>4</v>
       </c>
       <c r="O3" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="P3" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="Q3" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
       <c r="R3" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
       </c>
       <c r="S3" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
-        <v>3.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
       </c>
       <c r="T3" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -5688,7 +5820,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="V3" s="13"/>
+      <c r="V3" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
       <c r="Y3" s="13"/>
@@ -5754,21 +5889,24 @@
         <v>0.5</v>
       </c>
       <c r="O4" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
       </c>
       <c r="P4" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
-      </c>
-      <c r="Q4" s="13"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="Q4" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
       <c r="R4" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1)</f>
-        <v>1.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="S4" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="T4" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -5778,7 +5916,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="V4" s="13"/>
+      <c r="V4" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W4" s="13"/>
       <c r="X4" s="13"/>
       <c r="Y4" s="13"/>
@@ -5844,24 +5985,24 @@
         <v>3.5</v>
       </c>
       <c r="O5" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
       </c>
       <c r="P5" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Q5" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R5" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
-      </c>
-      <c r="S5" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
         <v>3.4</v>
+      </c>
+      <c r="S5" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
       </c>
       <c r="T5" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -5871,7 +6012,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
       </c>
-      <c r="V5" s="13"/>
+      <c r="V5" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W5" s="13"/>
       <c r="X5" s="13"/>
       <c r="Y5" s="13"/>
@@ -5944,14 +6088,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="13"/>
+      <c r="Q6" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
       <c r="R6" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.3)</f>
-        <v>0.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.1)</f>
+        <v>1.1</v>
       </c>
       <c r="S6" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="T6" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -5961,7 +6108,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="V6" s="13"/>
+      <c r="V6" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="W6" s="13"/>
       <c r="X6" s="13"/>
       <c r="Y6" s="13"/>
@@ -6027,24 +6177,24 @@
         <v>2.5</v>
       </c>
       <c r="O7" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="P7" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Q7" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
       <c r="R7" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="S7" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="T7" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -6054,7 +6204,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="V7" s="13"/>
+      <c r="V7" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W7" s="13"/>
       <c r="X7" s="13"/>
       <c r="Y7" s="13"/>
@@ -6120,8 +6273,8 @@
         <v>4</v>
       </c>
       <c r="O8" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="P8" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
@@ -6132,12 +6285,12 @@
         <v>4.3</v>
       </c>
       <c r="R8" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="S8" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
       </c>
       <c r="T8" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -6147,7 +6300,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
       </c>
-      <c r="V8" s="13"/>
+      <c r="V8" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="W8" s="13"/>
       <c r="X8" s="13"/>
       <c r="Y8" s="13"/>
@@ -6213,8 +6369,8 @@
         <v>5</v>
       </c>
       <c r="O9" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="P9" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -6225,12 +6381,12 @@
         <v>4.5</v>
       </c>
       <c r="R9" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
-        <v>3.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="S9" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
-        <v>4.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="T9" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -6240,7 +6396,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="V9" s="13"/>
+      <c r="V9" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W9" s="13"/>
       <c r="X9" s="13"/>
       <c r="Y9" s="13"/>
@@ -6306,24 +6465,24 @@
         <v>3.2</v>
       </c>
       <c r="O10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="P10" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Q10" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="S10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
-        <v>3.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="T10" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -6333,7 +6492,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="V10" s="13"/>
+      <c r="V10" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W10" s="13"/>
       <c r="X10" s="13"/>
       <c r="Y10" s="13"/>
@@ -6399,8 +6561,8 @@
         <v>2.3</v>
       </c>
       <c r="O11" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="P11" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -6411,12 +6573,12 @@
         <v>4.3</v>
       </c>
       <c r="R11" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
       </c>
       <c r="S11" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="T11" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -6426,7 +6588,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="V11" s="13"/>
+      <c r="V11" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="W11" s="13"/>
       <c r="X11" s="13"/>
       <c r="Y11" s="13"/>
@@ -6492,24 +6657,24 @@
         <v>3.5</v>
       </c>
       <c r="O12" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
       </c>
       <c r="P12" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="Q12" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R12" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
-      </c>
-      <c r="S12" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
         <v>3.2</v>
+      </c>
+      <c r="S12" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="T12" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
@@ -6519,7 +6684,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="V12" s="13"/>
+      <c r="V12" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="W12" s="13"/>
       <c r="X12" s="13"/>
       <c r="Y12" s="13"/>
@@ -6585,24 +6753,24 @@
         <v>3.5</v>
       </c>
       <c r="O13" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="P13" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Q13" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
       <c r="R13" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
       </c>
       <c r="S13" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
-        <v>3.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="T13" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -6612,7 +6780,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
         <v>4.1</v>
       </c>
-      <c r="V13" s="13"/>
+      <c r="V13" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W13" s="13"/>
       <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
@@ -6677,7 +6848,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O14" s="13"/>
+      <c r="O14" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="P14" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -6699,7 +6873,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="V14" s="13"/>
+      <c r="V14" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="W14" s="13"/>
       <c r="X14" s="13"/>
       <c r="Y14" s="13"/>
@@ -6765,24 +6942,24 @@
         <v>4.7</v>
       </c>
       <c r="O15" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="P15" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Q15" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
       <c r="R15" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="S15" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
-        <v>3.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
       </c>
       <c r="T15" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -6792,7 +6969,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="V15" s="13"/>
+      <c r="V15" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W15" s="13"/>
       <c r="X15" s="13"/>
       <c r="Y15" s="13"/>
@@ -6858,24 +7038,24 @@
         <v>3</v>
       </c>
       <c r="O16" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="P16" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="Q16" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R16" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
-        <v>2.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="S16" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="T16" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -6885,7 +7065,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="V16" s="13"/>
+      <c r="V16" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W16" s="13"/>
       <c r="X16" s="13"/>
       <c r="Y16" s="13"/>
@@ -6951,24 +7134,24 @@
         <v>4.8</v>
       </c>
       <c r="O17" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
       </c>
       <c r="P17" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="Q17" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
       <c r="R17" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="S17" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
-        <v>3.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
       </c>
       <c r="T17" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
@@ -6978,7 +7161,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="V17" s="13"/>
+      <c r="V17" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
       <c r="Y17" s="13"/>
@@ -7044,24 +7230,24 @@
         <v>4.8</v>
       </c>
       <c r="O18" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="P18" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
-        <v>4.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="Q18" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R18" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="S18" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="T18" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
@@ -7071,7 +7257,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="V18" s="13"/>
+      <c r="V18" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W18" s="13"/>
       <c r="X18" s="13"/>
       <c r="Y18" s="13"/>
@@ -7136,7 +7325,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="O19" s="13"/>
+      <c r="O19" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="P19" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
@@ -7155,7 +7347,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="V19" s="13"/>
+      <c r="V19" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
       <c r="Y19" s="13"/>
@@ -7221,24 +7416,24 @@
         <v>4.2</v>
       </c>
       <c r="O20" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="P20" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="Q20" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R20" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="S20" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
-        <v>3.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="T20" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -7248,7 +7443,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="V20" s="13"/>
+      <c r="V20" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="W20" s="13"/>
       <c r="X20" s="13"/>
       <c r="Y20" s="13"/>
@@ -7314,8 +7512,8 @@
         <v>3.8</v>
       </c>
       <c r="O21" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="P21" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
@@ -7326,12 +7524,12 @@
         <v>4.3</v>
       </c>
       <c r="R21" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="S21" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="T21" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -7341,7 +7539,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="V21" s="13"/>
+      <c r="V21" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="W21" s="13"/>
       <c r="X21" s="13"/>
       <c r="Y21" s="13"/>
@@ -7407,25 +7608,25 @@
         <v>3.4</v>
       </c>
       <c r="O22" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="P22" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="Q22" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R22" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
-      </c>
-      <c r="S22" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
         <v>3.4</v>
       </c>
+      <c r="S22" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
+      </c>
       <c r="T22" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
@@ -7434,7 +7635,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="V22" s="13"/>
+      <c r="V22" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W22" s="13"/>
       <c r="X22" s="13"/>
       <c r="Y22" s="13"/>
@@ -7500,8 +7704,8 @@
         <v>5</v>
       </c>
       <c r="O23" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="P23" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -7512,12 +7716,12 @@
         <v>4.5</v>
       </c>
       <c r="R23" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
-        <v>3.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="S23" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
-        <v>4.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="T23" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -7527,7 +7731,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="V23" s="13"/>
+      <c r="V23" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W23" s="13"/>
       <c r="X23" s="13"/>
       <c r="Y23" s="13"/>
@@ -7593,8 +7800,8 @@
         <v>3.5</v>
       </c>
       <c r="O24" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
+        <v>2.4</v>
       </c>
       <c r="P24" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -7605,12 +7812,12 @@
         <v>4.3</v>
       </c>
       <c r="R24" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
       </c>
       <c r="S24" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="T24" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -7620,7 +7827,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="V24" s="13"/>
+      <c r="V24" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="W24" s="13"/>
       <c r="X24" s="13"/>
       <c r="Y24" s="13"/>
@@ -7686,21 +7896,24 @@
         <v>3.8</v>
       </c>
       <c r="O25" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
+        <v>2.2</v>
       </c>
       <c r="P25" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
-      </c>
-      <c r="Q25" s="13"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="Q25" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
       <c r="R25" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
       </c>
       <c r="S25" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
       </c>
       <c r="T25" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -7710,7 +7923,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="V25" s="13"/>
+      <c r="V25" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W25" s="13"/>
       <c r="X25" s="13"/>
       <c r="Y25" s="13"/>
@@ -7776,24 +7992,24 @@
         <v>5</v>
       </c>
       <c r="O26" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="P26" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
-        <v>4.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Q26" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R26" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="S26" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
-        <v>4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="T26" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
@@ -7803,7 +8019,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="V26" s="13"/>
+      <c r="V26" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W26" s="13"/>
       <c r="X26" s="13"/>
       <c r="Y26" s="13"/>
@@ -8005,8 +8224,8 @@
         <v>3</v>
       </c>
       <c r="M2" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="N2" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
@@ -8014,12 +8233,12 @@
       </c>
       <c r="O2" s="13"/>
       <c r="P2" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
-        <v>1.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="Q2" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
       </c>
       <c r="R2" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -8098,8 +8317,8 @@
         <v>2.1</v>
       </c>
       <c r="M3" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="N3" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
@@ -8107,12 +8326,12 @@
       </c>
       <c r="O3" s="13"/>
       <c r="P3" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.4)</f>
-        <v>1.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="Q3" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
+        <v>3.1</v>
       </c>
       <c r="R3" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -8191,8 +8410,8 @@
         <v>2.8</v>
       </c>
       <c r="M4" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="N4" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -8200,12 +8419,12 @@
       </c>
       <c r="O4" s="13"/>
       <c r="P4" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="Q4" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="R4" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -8377,8 +8596,8 @@
         <v>2.4</v>
       </c>
       <c r="M6" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
       </c>
       <c r="N6" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
@@ -8386,12 +8605,12 @@
       </c>
       <c r="O6" s="13"/>
       <c r="P6" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
-        <v>1.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
+        <v>2.6</v>
       </c>
       <c r="Q6" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="R6" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -8470,8 +8689,8 @@
         <v>3.6</v>
       </c>
       <c r="M7" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="N7" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
@@ -8479,12 +8698,12 @@
       </c>
       <c r="O7" s="13"/>
       <c r="P7" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.9)</f>
-        <v>1.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="Q7" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="R7" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
@@ -8749,8 +8968,8 @@
         <v>3.6</v>
       </c>
       <c r="M10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="N10" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
@@ -8758,12 +8977,12 @@
       </c>
       <c r="O10" s="13"/>
       <c r="P10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
-        <v>1.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="Q10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
-        <v>1.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="R10" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
@@ -8842,8 +9061,8 @@
         <v>3.1</v>
       </c>
       <c r="M11" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="N11" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
@@ -8851,12 +9070,12 @@
       </c>
       <c r="O11" s="13"/>
       <c r="P11" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8)</f>
-        <v>1.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
       </c>
       <c r="Q11" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
       </c>
       <c r="R11" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
@@ -9010,8 +9229,8 @@
         <v>4.2</v>
       </c>
       <c r="M13" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
       </c>
       <c r="N13" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
@@ -9019,12 +9238,12 @@
       </c>
       <c r="O13" s="13"/>
       <c r="P13" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
-        <v>1.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
+        <v>2.9</v>
       </c>
       <c r="Q13" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="R13" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -9289,8 +9508,8 @@
         <v>3.223076923</v>
       </c>
       <c r="M16" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7692307692307692)</f>
-        <v>1.769230769</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.323076923076924)</f>
+        <v>4.323076923</v>
       </c>
       <c r="N16" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.430769230769231)</f>
@@ -9298,12 +9517,12 @@
       </c>
       <c r="O16" s="13"/>
       <c r="P16" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.207692307692308)</f>
-        <v>2.207692308</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9692307692307693)</f>
+        <v>2.969230769</v>
       </c>
       <c r="Q16" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8923076923076922)</f>
-        <v>2.892307692</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2615384615384615)</f>
+        <v>3.261538462</v>
       </c>
       <c r="R16" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6285714285714286)</f>
@@ -9799,8 +10018,8 @@
         <v>3.5</v>
       </c>
       <c r="O3" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
       </c>
       <c r="P3" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -9811,12 +10030,12 @@
         <v>4.3</v>
       </c>
       <c r="R3" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="S3" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="T3" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -9826,7 +10045,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
-      <c r="V3" s="13"/>
+      <c r="V3" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W3" s="13"/>
       <c r="X3" s="13"/>
       <c r="Y3" s="13"/>
@@ -9892,25 +10114,25 @@
         <v>4.3</v>
       </c>
       <c r="O4" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="P4" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
-        <v>4.8</v>
-      </c>
-      <c r="Q4" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
-        <v>4.5</v>
-      </c>
-      <c r="R4" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
-      </c>
-      <c r="S4" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
         <v>3.6</v>
       </c>
+      <c r="P4" s="14">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="Q4" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
+      <c r="R4" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
+      </c>
+      <c r="S4" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
+      </c>
       <c r="T4" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
@@ -9919,7 +10141,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="V4" s="13"/>
+      <c r="V4" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
+        <v>4</v>
+      </c>
       <c r="W4" s="13"/>
       <c r="X4" s="13"/>
       <c r="Y4" s="13"/>
@@ -9985,8 +10210,8 @@
         <v>2.4</v>
       </c>
       <c r="O5" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
       </c>
       <c r="P5" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
@@ -9997,12 +10222,12 @@
         <v>4.2</v>
       </c>
       <c r="R5" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
-      </c>
-      <c r="S5" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
+      </c>
+      <c r="S5" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
+        <v>3.1</v>
       </c>
       <c r="T5" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
@@ -10012,7 +10237,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="V5" s="13"/>
+      <c r="V5" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="W5" s="13"/>
       <c r="X5" s="13"/>
       <c r="Y5" s="13"/>
@@ -10237,24 +10465,24 @@
         <v>3.5</v>
       </c>
       <c r="O8" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
+        <v>1.7</v>
       </c>
       <c r="P8" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
+        <v>4.9</v>
       </c>
       <c r="Q8" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
       <c r="R8" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="S8" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
+        <v>3.1</v>
       </c>
       <c r="T8" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -10264,7 +10492,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="V8" s="13"/>
+      <c r="V8" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W8" s="13"/>
       <c r="X8" s="13"/>
       <c r="Y8" s="13"/>
@@ -10357,7 +10588,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="V9" s="13"/>
+      <c r="V9" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="W9" s="13"/>
       <c r="X9" s="13"/>
       <c r="Y9" s="13"/>
@@ -10419,38 +10653,41 @@
         <v>3</v>
       </c>
       <c r="N10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
-        <v>3.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
       </c>
       <c r="O10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
       </c>
       <c r="P10" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.1)</f>
-        <v>2.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Q10" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
       <c r="R10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
       </c>
       <c r="S10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="T10" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
       <c r="U10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
-      </c>
-      <c r="V10" s="13"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
+      <c r="V10" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W10" s="13"/>
       <c r="X10" s="13"/>
       <c r="Y10" s="13"/>
@@ -10516,24 +10753,24 @@
         <v>4.7</v>
       </c>
       <c r="O11" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="P11" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Q11" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
       <c r="R11" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="S11" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
-        <v>4.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="T11" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
@@ -10543,7 +10780,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
-      <c r="V11" s="13"/>
+      <c r="V11" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W11" s="13"/>
       <c r="X11" s="13"/>
       <c r="Y11" s="13"/>
@@ -10609,8 +10849,8 @@
         <v>3.5</v>
       </c>
       <c r="O12" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="P12" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -10621,12 +10861,12 @@
         <v>0</v>
       </c>
       <c r="R12" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
+        <v>2.3</v>
       </c>
       <c r="S12" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
-        <v>3.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="T12" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -10636,7 +10876,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
         <v>4.5</v>
       </c>
-      <c r="V12" s="13"/>
+      <c r="V12" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="W12" s="13"/>
       <c r="X12" s="13"/>
       <c r="Y12" s="13"/>
@@ -10702,24 +10945,24 @@
         <v>2.3</v>
       </c>
       <c r="O13" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="P13" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
-        <v>4.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Q13" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
         <v>4.2</v>
       </c>
       <c r="R13" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
       </c>
       <c r="S13" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="T13" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -10729,7 +10972,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="V13" s="13"/>
+      <c r="V13" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W13" s="13"/>
       <c r="X13" s="13"/>
       <c r="Y13" s="13"/>
@@ -10795,24 +11041,24 @@
         <v>3.9</v>
       </c>
       <c r="O14" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="P14" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
-        <v>4.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="Q14" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
       <c r="R14" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="S14" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
-        <v>3.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
+        <v>4.3</v>
       </c>
       <c r="T14" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
@@ -10822,7 +11068,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="V14" s="13"/>
+      <c r="V14" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W14" s="13"/>
       <c r="X14" s="13"/>
       <c r="Y14" s="13"/>
@@ -10888,24 +11137,24 @@
         <v>2.4</v>
       </c>
       <c r="O15" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.0)</f>
+        <v>1</v>
       </c>
       <c r="P15" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
+        <v>4.4</v>
       </c>
       <c r="Q15" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R15" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
+        <v>2.8</v>
       </c>
       <c r="S15" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="T15" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -10915,7 +11164,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="V15" s="13"/>
+      <c r="V15" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="W15" s="13"/>
       <c r="X15" s="13"/>
       <c r="Y15" s="13"/>
@@ -11008,7 +11260,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="V16" s="13"/>
+      <c r="V16" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
+        <v>0</v>
+      </c>
       <c r="W16" s="13"/>
       <c r="X16" s="13"/>
       <c r="Y16" s="13"/>
@@ -11074,24 +11329,24 @@
         <v>3.6</v>
       </c>
       <c r="O17" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="P17" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.7)</f>
-        <v>0.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="Q17" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
         <v>4.9</v>
       </c>
       <c r="R17" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="S17" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="T17" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
@@ -11101,7 +11356,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="V17" s="13"/>
+      <c r="V17" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
       <c r="Y17" s="13"/>
@@ -11167,24 +11425,24 @@
         <v>2.4</v>
       </c>
       <c r="O18" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
+        <v>1.5</v>
       </c>
       <c r="P18" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="Q18" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R18" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.6)</f>
-        <v>1.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
+        <v>2.5</v>
       </c>
       <c r="S18" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
+        <v>3.1</v>
       </c>
       <c r="T18" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -11194,7 +11452,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="V18" s="13"/>
+      <c r="V18" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W18" s="13"/>
       <c r="X18" s="13"/>
       <c r="Y18" s="13"/>
@@ -11329,8 +11590,8 @@
         <v>3.5</v>
       </c>
       <c r="O20" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
+        <v>1.3</v>
       </c>
       <c r="P20" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
@@ -11341,12 +11602,12 @@
         <v>4.3</v>
       </c>
       <c r="R20" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="S20" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
+        <v>2.7</v>
       </c>
       <c r="T20" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -11356,7 +11617,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
         <v>4.6</v>
       </c>
-      <c r="V20" s="13"/>
+      <c r="V20" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="W20" s="13"/>
       <c r="X20" s="13"/>
       <c r="Y20" s="13"/>
@@ -11422,24 +11686,24 @@
         <v>2.7</v>
       </c>
       <c r="O21" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.3)</f>
+        <v>1.3</v>
       </c>
       <c r="P21" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="Q21" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R21" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
-        <v>2.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
+        <v>3.1</v>
       </c>
       <c r="S21" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="T21" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
@@ -11449,7 +11713,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="V21" s="13"/>
+      <c r="V21" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="W21" s="13"/>
       <c r="X21" s="13"/>
       <c r="Y21" s="13"/>
@@ -11515,24 +11782,24 @@
         <v>3.4</v>
       </c>
       <c r="O22" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
+        <v>2</v>
       </c>
       <c r="P22" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="Q22" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="R22" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="S22" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="T22" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -11542,7 +11809,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
         <v>0</v>
       </c>
-      <c r="V22" s="13"/>
+      <c r="V22" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="W22" s="13"/>
       <c r="X22" s="13"/>
       <c r="Y22" s="13"/>
@@ -11598,38 +11868,41 @@
         <v>3.99047619</v>
       </c>
       <c r="N23" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.144444444444444)</f>
-        <v>3.144444444</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.161111111111111)</f>
+        <v>3.161111111</v>
       </c>
       <c r="O23" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.8666666666666667)</f>
+        <v>1.866666667</v>
       </c>
       <c r="P23" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.377777777777778)</f>
-        <v>3.377777778</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2666666666666675)</f>
+        <v>4.266666667</v>
       </c>
       <c r="Q23" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6833333333333322)</f>
         <v>3.683333333</v>
       </c>
       <c r="R23" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.361111111111111)</f>
-        <v>2.361111111</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0999999999999996)</f>
+        <v>3.1</v>
       </c>
       <c r="S23" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8499999999999996)</f>
-        <v>2.85</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2111111111111104)</f>
+        <v>3.211111111</v>
       </c>
       <c r="T23" s="14">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9444444444444446)</f>
         <v>3.944444444</v>
       </c>
       <c r="U23" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.761111111111111)</f>
-        <v>2.761111111</v>
-      </c>
-      <c r="V23" s="13"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0388888888888888)</f>
+        <v>3.038888889</v>
+      </c>
+      <c r="V23" s="14">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8529411764705883)</f>
+        <v>3.852941176</v>
+      </c>
       <c r="W23" s="13"/>
       <c r="X23" s="13"/>
       <c r="Y23" s="13"/>

--- a/app_notas.xlsx
+++ b/app_notas.xlsx
@@ -882,22 +882,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta10")</f>
         <v>Ta10</v>
       </c>
-      <c r="W1" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta11")</f>
-        <v>Ta11</v>
-      </c>
-      <c r="X1" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta12")</f>
-        <v>Ta12</v>
-      </c>
-      <c r="Y1" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta13")</f>
-        <v>Ta13</v>
-      </c>
-      <c r="Z1" s="10" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta14")</f>
-        <v>Ta14</v>
-      </c>
+      <c r="W1" s="7"/>
+      <c r="X1" s="7"/>
+      <c r="Y1" s="7"/>
+      <c r="Z1" s="10"/>
       <c r="AA1" s="1" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ID")</f>
         <v>ID</v>
@@ -5620,22 +5608,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta10")</f>
         <v>Ta10</v>
       </c>
-      <c r="W1" s="17" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta11")</f>
-        <v>Ta11</v>
-      </c>
-      <c r="X1" s="17" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta12")</f>
-        <v>Ta12</v>
-      </c>
-      <c r="Y1" s="17" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta13")</f>
-        <v>Ta13</v>
-      </c>
-      <c r="Z1" s="21" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta14")</f>
-        <v>Ta14</v>
-      </c>
+      <c r="W1" s="17"/>
+      <c r="X1" s="17"/>
+      <c r="Y1" s="17"/>
+      <c r="Z1" s="21"/>
       <c r="AA1" s="21" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ID")</f>
         <v>ID</v>
@@ -9869,22 +9845,10 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta10")</f>
         <v>Ta10</v>
       </c>
-      <c r="W1" s="17" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta11")</f>
-        <v>Ta11</v>
-      </c>
-      <c r="X1" s="17" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta12")</f>
-        <v>Ta12</v>
-      </c>
-      <c r="Y1" s="17" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta13")</f>
-        <v>Ta13</v>
-      </c>
-      <c r="Z1" s="21" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"Ta14")</f>
-        <v>Ta14</v>
-      </c>
+      <c r="W1" s="17"/>
+      <c r="X1" s="17"/>
+      <c r="Y1" s="17"/>
+      <c r="Z1" s="21"/>
       <c r="AA1" s="21" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ID")</f>
         <v>ID</v>

--- a/app_notas.xlsx
+++ b/app_notas.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
   <si>
     <t>No</t>
   </si>
@@ -293,51 +293,6 @@
     <t>VARGAS CASTELLANOS, VALERIA</t>
   </si>
   <si>
-    <t>AGUDELO FLOREZ, DANIEL F.</t>
-  </si>
-  <si>
-    <t>CADENA LOPEZ, ANDRES J.</t>
-  </si>
-  <si>
-    <t>CESPEDES URIBE, MARIA J.</t>
-  </si>
-  <si>
-    <t>CORREA TORO, YULIETH D.</t>
-  </si>
-  <si>
-    <t>EL FEGHALI PEREZ, MICHAEL C.</t>
-  </si>
-  <si>
-    <t>ESCOBAR ESPINOSA, WENDY J.</t>
-  </si>
-  <si>
-    <t>GALLO FLOREZ, DANIELA</t>
-  </si>
-  <si>
-    <t>PLATA DIAZ, MARIAN S.</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ DIAZ, DANIEL A.</t>
-  </si>
-  <si>
-    <t>SIERRA OREJARENA, JUAN F.</t>
-  </si>
-  <si>
-    <t>SUAREZ JIMENEZ, MARIANA</t>
-  </si>
-  <si>
-    <t>TORRES RONDON, DALTON Y.</t>
-  </si>
-  <si>
-    <t>VILLARRUEL NARVAEZ, MARIA J.</t>
-  </si>
-  <si>
-    <t>VILLAMIZAR MUÑOZ, JENNIFER L.</t>
-  </si>
-  <si>
-    <t>VIVIESCAS DIAZ, MARIA J.</t>
-  </si>
-  <si>
     <t>ACOSTA YARURO, SOFIA</t>
   </si>
   <si>
@@ -360,6 +315,9 @@
   </si>
   <si>
     <t>CHANAGA REINA, SANTIAGO D.</t>
+  </si>
+  <si>
+    <t>CORREA TORO, YULIETH D.</t>
   </si>
   <si>
     <t>GAMBOA VESGA, ALEJANDRO</t>
@@ -485,7 +443,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -548,7 +506,6 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -8057,11 +8014,12 @@
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>1</v>
+      <c r="B1" s="16" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1vS2gE-mc1A6CX14zq-8uhU927dLafFRogBm_03E8occ"",""EST2!b1:AA15"")"),"NOMBRE")</f>
+        <v>NOMBRE</v>
       </c>
       <c r="C1" s="17" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("IMPORTRANGE(""1vS2gE-mc1A6CX14zq-8uhU927dLafFRogBm_03E8occ"",""EST2!C1:AA24"")"),"P1")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"P1")</f>
         <v>P1</v>
       </c>
       <c r="D1" s="17" t="str">
@@ -8156,8 +8114,9 @@
       <c r="A2" s="20">
         <v>1.0</v>
       </c>
-      <c r="B2" s="20" t="s">
-        <v>70</v>
+      <c r="B2" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"AGUDELO FLOREZ, DANIEL F.")</f>
+        <v>AGUDELO FLOREZ, DANIEL F.</v>
       </c>
       <c r="C2" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
@@ -8207,14 +8166,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
         <v>3.3</v>
       </c>
-      <c r="O2" s="13"/>
+      <c r="O2" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="P2" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
       </c>
       <c r="Q2" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
-        <v>2.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="R2" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -8249,8 +8211,9 @@
       <c r="A3" s="20">
         <v>2.0</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>71</v>
+      <c r="B3" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CADENA LOPEZ, ANDRES J.")</f>
+        <v>CADENA LOPEZ, ANDRES J.</v>
       </c>
       <c r="C3" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -8300,14 +8263,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
         <v>3.8</v>
       </c>
-      <c r="O3" s="13"/>
+      <c r="O3" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="P3" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.5)</f>
-        <v>2.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="Q3" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
-        <v>3.1</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
       </c>
       <c r="R3" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -8342,8 +8308,9 @@
       <c r="A4" s="20">
         <v>3.0</v>
       </c>
-      <c r="B4" s="20" t="s">
-        <v>72</v>
+      <c r="B4" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CESPEDES URIBE, MARIA J.")</f>
+        <v>CESPEDES URIBE, MARIA J.</v>
       </c>
       <c r="C4" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
@@ -8393,14 +8360,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
         <v>4.8</v>
       </c>
-      <c r="O4" s="13"/>
+      <c r="O4" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
+        <v>4.5</v>
+      </c>
       <c r="P4" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
+        <v>4.1</v>
       </c>
       <c r="Q4" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
-        <v>3.5</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
       </c>
       <c r="R4" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -8435,8 +8405,9 @@
       <c r="A5" s="20">
         <v>4.0</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>73</v>
+      <c r="B5" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"CORREA TORO, YULIETH D.")</f>
+        <v>CORREA TORO, YULIETH D.</v>
       </c>
       <c r="C5" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
@@ -8486,14 +8457,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.7)</f>
         <v>2.7</v>
       </c>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
-      </c>
-      <c r="Q5" s="13">
+      <c r="O5" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
         <v>3</v>
+      </c>
+      <c r="P5" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
+        <v>3.4</v>
+      </c>
+      <c r="Q5" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="R5" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
@@ -8528,8 +8502,9 @@
       <c r="A6" s="20">
         <v>5.0</v>
       </c>
-      <c r="B6" s="20" t="s">
-        <v>74</v>
+      <c r="B6" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"EL FEGHALI PEREZ, MICHAEL C.")</f>
+        <v>EL FEGHALI PEREZ, MICHAEL C.</v>
       </c>
       <c r="C6" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
@@ -8579,14 +8554,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
         <v>2.9</v>
       </c>
-      <c r="O6" s="13"/>
+      <c r="O6" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="P6" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.6)</f>
-        <v>2.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="Q6" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
-        <v>3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
+        <v>3.5</v>
       </c>
       <c r="R6" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -8621,8 +8599,9 @@
       <c r="A7" s="20">
         <v>6.0</v>
       </c>
-      <c r="B7" s="20" t="s">
-        <v>75</v>
+      <c r="B7" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"ESCOBAR ESPINOSA, WENDY J.")</f>
+        <v>ESCOBAR ESPINOSA, WENDY J.</v>
       </c>
       <c r="C7" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
@@ -8672,14 +8651,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="O7" s="13"/>
+      <c r="O7" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="P7" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
       </c>
       <c r="Q7" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
-        <v>3.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="R7" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
@@ -8714,8 +8696,9 @@
       <c r="A8" s="20">
         <v>7.0</v>
       </c>
-      <c r="B8" s="20" t="s">
-        <v>76</v>
+      <c r="B8" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"GALLO FLOREZ, DANIELA")</f>
+        <v>GALLO FLOREZ, DANIELA</v>
       </c>
       <c r="C8" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -8765,14 +8748,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
         <v>4.4</v>
       </c>
-      <c r="O8" s="13"/>
+      <c r="O8" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P8" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
-        <v>3.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="Q8" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="R8" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
@@ -8807,8 +8793,9 @@
       <c r="A9" s="20">
         <v>8.0</v>
       </c>
-      <c r="B9" s="20" t="s">
-        <v>77</v>
+      <c r="B9" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"PLATA DIAZ, MARIAN S.")</f>
+        <v>PLATA DIAZ, MARIAN S.</v>
       </c>
       <c r="C9" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.4)</f>
@@ -8858,14 +8845,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
-      <c r="O9" s="13"/>
+      <c r="O9" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
       <c r="P9" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.9)</f>
+        <v>3.9</v>
       </c>
       <c r="Q9" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
-        <v>3.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
+        <v>4.2</v>
       </c>
       <c r="R9" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
@@ -8900,8 +8890,9 @@
       <c r="A10" s="20">
         <v>9.0</v>
       </c>
-      <c r="B10" s="20" t="s">
-        <v>78</v>
+      <c r="B10" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"RODRIGUEZ DIAZ, DANIEL A.")</f>
+        <v>RODRIGUEZ DIAZ, DANIEL A.</v>
       </c>
       <c r="C10" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
@@ -8940,33 +8931,36 @@
         <v>0</v>
       </c>
       <c r="L10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
-        <v>3.6</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="M10" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
         <v>5</v>
       </c>
       <c r="N10" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
-        <v>3.1</v>
-      </c>
-      <c r="O10" s="13"/>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
+      </c>
+      <c r="O10" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
-        <v>3.2</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
       </c>
       <c r="Q10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.3)</f>
-        <v>2.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="R10" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
         <v>4.3</v>
       </c>
       <c r="S10" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
-        <v>0</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
       </c>
       <c r="T10" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -8993,8 +8987,9 @@
       <c r="A11" s="20">
         <v>10.0</v>
       </c>
-      <c r="B11" s="20" t="s">
-        <v>79</v>
+      <c r="B11" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SIERRA OREJARENA, JUAN F.")</f>
+        <v>SIERRA OREJARENA, JUAN F.</v>
       </c>
       <c r="C11" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.2)</f>
@@ -9044,14 +9039,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.1)</f>
         <v>4.1</v>
       </c>
-      <c r="O11" s="13"/>
+      <c r="O11" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.6)</f>
+        <v>4.6</v>
+      </c>
       <c r="P11" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
+        <v>3.7</v>
       </c>
       <c r="Q11" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8)</f>
-        <v>2.8</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
+        <v>3.3</v>
       </c>
       <c r="R11" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
@@ -9086,8 +9084,9 @@
       <c r="A12" s="20">
         <v>11.0</v>
       </c>
-      <c r="B12" s="20" t="s">
-        <v>80</v>
+      <c r="B12" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"SUAREZ JIMENEZ, MARIANA")</f>
+        <v>SUAREZ JIMENEZ, MARIANA</v>
       </c>
       <c r="C12" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -9161,8 +9160,9 @@
       <c r="A13" s="20">
         <v>12.0</v>
       </c>
-      <c r="B13" s="20" t="s">
-        <v>81</v>
+      <c r="B13" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLAMIZAR MUÑOZ, JENNIFER L.")</f>
+        <v>VILLAMIZAR MUÑOZ, JENNIFER L.</v>
       </c>
       <c r="C13" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
@@ -9212,14 +9212,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.5)</f>
         <v>1.5</v>
       </c>
-      <c r="O13" s="13"/>
-      <c r="P13" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
-      </c>
-      <c r="Q13" s="13">
+      <c r="O13" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.5)</f>
         <v>3.5</v>
+      </c>
+      <c r="P13" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
+        <v>3.6</v>
+      </c>
+      <c r="Q13" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
+        <v>3.8</v>
       </c>
       <c r="R13" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.5)</f>
@@ -9254,8 +9257,9 @@
       <c r="A14" s="20">
         <v>13.0</v>
       </c>
-      <c r="B14" s="20" t="s">
-        <v>82</v>
+      <c r="B14" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VILLARRUEL NARVAEZ, MARIA J.")</f>
+        <v>VILLARRUEL NARVAEZ, MARIA J.</v>
       </c>
       <c r="C14" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
@@ -9305,14 +9309,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),1.7)</f>
         <v>1.7</v>
       </c>
-      <c r="O14" s="13"/>
+      <c r="O14" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
+      </c>
       <c r="P14" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
-        <v>2.4</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.0)</f>
+        <v>3</v>
       </c>
       <c r="Q14" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9)</f>
-        <v>2.9</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
+        <v>3.2</v>
       </c>
       <c r="R14" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.0)</f>
@@ -9347,8 +9354,9 @@
       <c r="A15" s="20">
         <v>14.0</v>
       </c>
-      <c r="B15" s="20" t="s">
-        <v>83</v>
+      <c r="B15" s="19" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),"VIVIESCAS DIAZ, MARIA J.")</f>
+        <v>VIVIESCAS DIAZ, MARIA J.</v>
       </c>
       <c r="C15" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -9398,14 +9406,17 @@
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
         <v>4</v>
       </c>
-      <c r="O15" s="13"/>
+      <c r="O15" s="13">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
+        <v>5</v>
+      </c>
       <c r="P15" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
-        <v>3.7</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.7)</f>
+        <v>4.7</v>
       </c>
       <c r="Q15" s="13">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.3)</f>
-        <v>4.3</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.8)</f>
+        <v>4.8</v>
       </c>
       <c r="R15" s="13">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
@@ -9437,307 +9448,29 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.650000000000001)</f>
-        <v>3.65</v>
-      </c>
-      <c r="D16" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3000000000000003)</f>
-        <v>3.3</v>
-      </c>
-      <c r="E16" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.121428571428571)</f>
-        <v>3.121428571</v>
-      </c>
-      <c r="F16" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3642857142857143)</f>
-        <v>3.364285714</v>
-      </c>
-      <c r="G16" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.685714285714286)</f>
-        <v>2.685714286</v>
-      </c>
-      <c r="H16" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.807142857142857)</f>
-        <v>3.807142857</v>
-      </c>
-      <c r="I16" s="12">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.442857142857143)</f>
-        <v>2.442857143</v>
-      </c>
-      <c r="J16" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.421428571428571)</f>
-        <v>3.421428571</v>
-      </c>
-      <c r="K16" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1785714285714284)</f>
-        <v>3.178571429</v>
-      </c>
-      <c r="L16" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.223076923076923)</f>
-        <v>3.223076923</v>
-      </c>
-      <c r="M16" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.323076923076924)</f>
-        <v>4.323076923</v>
-      </c>
-      <c r="N16" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.430769230769231)</f>
-        <v>3.430769231</v>
-      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="13"/>
       <c r="O16" s="13"/>
-      <c r="P16" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.9692307692307693)</f>
-        <v>2.969230769</v>
-      </c>
-      <c r="Q16" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2615384615384615)</f>
-        <v>3.261538462</v>
-      </c>
-      <c r="R16" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6285714285714286)</f>
-        <v>3.628571429</v>
-      </c>
-      <c r="S16" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.0)</f>
-        <v>2</v>
-      </c>
-      <c r="T16" s="14">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.230769230769231)</f>
-        <v>4.230769231</v>
-      </c>
+      <c r="P16" s="13"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="13"/>
+      <c r="S16" s="13"/>
+      <c r="T16" s="13"/>
       <c r="U16" s="13"/>
       <c r="V16" s="13"/>
       <c r="W16" s="13"/>
       <c r="X16" s="13"/>
       <c r="Y16" s="13"/>
-      <c r="Z16" s="19"/>
-      <c r="AA16" s="22">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.8464285714285715)</f>
-        <v>2.846428571</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
-      <c r="S17" s="19"/>
-      <c r="T17" s="19"/>
-      <c r="U17" s="19"/>
-      <c r="V17" s="19"/>
-      <c r="W17" s="19"/>
-      <c r="X17" s="19"/>
-      <c r="Y17" s="19"/>
-      <c r="Z17" s="19"/>
-      <c r="AA17" s="19"/>
-    </row>
-    <row r="18">
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="19"/>
-      <c r="S18" s="19"/>
-      <c r="T18" s="19"/>
-      <c r="U18" s="19"/>
-      <c r="V18" s="19"/>
-      <c r="W18" s="19"/>
-      <c r="X18" s="19"/>
-      <c r="Y18" s="19"/>
-      <c r="Z18" s="19"/>
-      <c r="AA18" s="19"/>
-    </row>
-    <row r="19">
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="19"/>
-      <c r="S19" s="19"/>
-      <c r="T19" s="19"/>
-      <c r="U19" s="19"/>
-      <c r="V19" s="19"/>
-      <c r="W19" s="19"/>
-      <c r="X19" s="19"/>
-      <c r="Y19" s="19"/>
-      <c r="Z19" s="19"/>
-      <c r="AA19" s="19"/>
-    </row>
-    <row r="20">
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="19"/>
-      <c r="S20" s="19"/>
-      <c r="T20" s="19"/>
-      <c r="U20" s="19"/>
-      <c r="V20" s="19"/>
-      <c r="W20" s="19"/>
-      <c r="X20" s="19"/>
-      <c r="Y20" s="19"/>
-      <c r="Z20" s="19"/>
-      <c r="AA20" s="19"/>
-    </row>
-    <row r="21">
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="19"/>
-      <c r="T21" s="19"/>
-      <c r="U21" s="19"/>
-      <c r="V21" s="19"/>
-      <c r="W21" s="19"/>
-      <c r="X21" s="19"/>
-      <c r="Y21" s="19"/>
-      <c r="Z21" s="19"/>
-      <c r="AA21" s="19"/>
-    </row>
-    <row r="22">
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="19"/>
-      <c r="I22" s="19"/>
-      <c r="J22" s="19"/>
-      <c r="K22" s="19"/>
-      <c r="L22" s="19"/>
-      <c r="M22" s="19"/>
-      <c r="N22" s="19"/>
-      <c r="O22" s="19"/>
-      <c r="P22" s="19"/>
-      <c r="Q22" s="19"/>
-      <c r="R22" s="19"/>
-      <c r="S22" s="19"/>
-      <c r="T22" s="19"/>
-      <c r="U22" s="19"/>
-      <c r="V22" s="19"/>
-      <c r="W22" s="19"/>
-      <c r="X22" s="19"/>
-      <c r="Y22" s="19"/>
-      <c r="Z22" s="19"/>
-      <c r="AA22" s="19"/>
-    </row>
-    <row r="23">
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="L23" s="19"/>
-      <c r="M23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="19"/>
-      <c r="S23" s="19"/>
-      <c r="T23" s="19"/>
-      <c r="U23" s="19"/>
-      <c r="V23" s="19"/>
-      <c r="W23" s="19"/>
-      <c r="X23" s="19"/>
-      <c r="Y23" s="19"/>
-      <c r="Z23" s="19"/>
-      <c r="AA23" s="19"/>
-    </row>
-    <row r="24">
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
-      <c r="R24" s="19"/>
-      <c r="S24" s="19"/>
-      <c r="T24" s="19"/>
-      <c r="U24" s="19"/>
-      <c r="V24" s="19"/>
-      <c r="W24" s="19"/>
-      <c r="X24" s="19"/>
-      <c r="Y24" s="19"/>
-      <c r="Z24" s="19"/>
-      <c r="AA24" s="19"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -9859,7 +9592,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C2" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.2)</f>
@@ -9931,7 +9664,7 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="C3" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
@@ -10027,7 +9760,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="C4" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -10123,7 +9856,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C5" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -10219,7 +9952,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C6" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
@@ -10288,7 +10021,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C7" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
@@ -10378,7 +10111,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="C8" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
@@ -10474,7 +10207,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C9" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.9)</f>
@@ -10570,7 +10303,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C10" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.4)</f>
@@ -10666,7 +10399,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C11" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -10762,7 +10495,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C12" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.2)</f>
@@ -10858,7 +10591,7 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C13" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),5.0)</f>
@@ -10954,7 +10687,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C14" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),4.0)</f>
@@ -11050,7 +10783,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="C15" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.1)</f>
@@ -11146,7 +10879,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C16" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.7)</f>
@@ -11242,7 +10975,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="C17" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.3)</f>
@@ -11338,7 +11071,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="C18" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.8)</f>
@@ -11434,7 +11167,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C19" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),0.3)</f>
@@ -11503,7 +11236,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="C20" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),2.4)</f>
@@ -11599,7 +11332,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="C21" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
@@ -11695,7 +11428,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="C22" s="12">
         <f>IFERROR(__xludf.DUMMYFUNCTION("""COMPUTED_VALUE"""),3.6)</f>
